--- a/src/assets/downloads/LZK-Rechner_Pkw_V1.3.xlsx
+++ b/src/assets/downloads/LZK-Rechner_Pkw_V1.3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20414"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20415"/>
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifeu2.sharepoint.com/sites/DBUBeschaffungBerlin/Freigegebene Dokumente/General/Folgeprojekt/03_Arbeitsdokumente/A4 - Aktualisierung der Instrumente aus Basisprojekt/LZK-Rechner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1221" documentId="13_ncr:1_{3372B5DA-C386-4B74-B09A-B44627B6D7C7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0ED608E-3289-4B16-9857-845B593FF496}"/>
+  <xr:revisionPtr revIDLastSave="1224" documentId="13_ncr:1_{3372B5DA-C386-4B74-B09A-B44627B6D7C7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{15FA5D02-E4AC-479E-94D4-7CA04E4DDCD5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="887" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1155,9 +1155,6 @@
     </r>
   </si>
   <si>
-    <t>Ladeverhalten Elektroauto</t>
-  </si>
-  <si>
     <t>Ergänzende Angaben für Elektrofahrzeuge:</t>
   </si>
   <si>
@@ -3295,6 +3292,9 @@
   </si>
   <si>
     <t>https://www.nachhaltige-oeffentliche-pkw-beschaffung.de/assets/downloads/LZK-Rechner_Fahrzeuge_Dokumentation.pdf</t>
+  </si>
+  <si>
+    <t>Ladeverhalten Elektrofahrzeug</t>
   </si>
 </sst>
 </file>
@@ -5497,6 +5497,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
@@ -5531,15 +5540,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -12365,8 +12365,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9067589" y="2388870"/>
-          <a:ext cx="1630074" cy="963295"/>
+          <a:off x="9090449" y="2428875"/>
+          <a:ext cx="1631979" cy="976630"/>
           <a:chOff x="8390255" y="2565400"/>
           <a:chExt cx="1643409" cy="965200"/>
         </a:xfrm>
@@ -13970,7 +13970,7 @@
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
       <c r="J2" s="268" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
@@ -13992,17 +13992,17 @@
       <c r="J4" s="115"/>
     </row>
     <row r="5" spans="2:10" ht="149.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="370" t="s">
-        <v>469</v>
-      </c>
-      <c r="C5" s="370"/>
-      <c r="D5" s="370"/>
-      <c r="E5" s="370"/>
-      <c r="F5" s="370"/>
-      <c r="G5" s="370"/>
-      <c r="H5" s="370"/>
-      <c r="I5" s="370"/>
-      <c r="J5" s="370"/>
+      <c r="B5" s="373" t="s">
+        <v>468</v>
+      </c>
+      <c r="C5" s="373"/>
+      <c r="D5" s="373"/>
+      <c r="E5" s="373"/>
+      <c r="F5" s="373"/>
+      <c r="G5" s="373"/>
+      <c r="H5" s="373"/>
+      <c r="I5" s="373"/>
+      <c r="J5" s="373"/>
     </row>
     <row r="6" spans="2:10" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="245"/>
@@ -14040,13 +14040,13 @@
     <row r="9" spans="2:10" ht="52.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D9" s="245"/>
       <c r="E9" s="245"/>
-      <c r="F9" s="371" t="s">
-        <v>427</v>
-      </c>
-      <c r="G9" s="371"/>
-      <c r="H9" s="371"/>
-      <c r="I9" s="371"/>
-      <c r="J9" s="371"/>
+      <c r="F9" s="374" t="s">
+        <v>426</v>
+      </c>
+      <c r="G9" s="374"/>
+      <c r="H9" s="374"/>
+      <c r="I9" s="374"/>
+      <c r="J9" s="374"/>
     </row>
     <row r="10" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" s="245"/>
@@ -14060,31 +14060,31 @@
     <row r="11" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="245"/>
       <c r="E11" s="245"/>
-      <c r="F11" s="372" t="s">
-        <v>442</v>
-      </c>
-      <c r="G11" s="373"/>
-      <c r="H11" s="373"/>
-      <c r="I11" s="373"/>
-      <c r="J11" s="373"/>
+      <c r="F11" s="375" t="s">
+        <v>441</v>
+      </c>
+      <c r="G11" s="376"/>
+      <c r="H11" s="376"/>
+      <c r="I11" s="376"/>
+      <c r="J11" s="376"/>
     </row>
     <row r="12" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D12" s="245"/>
       <c r="E12" s="245"/>
-      <c r="F12" s="373"/>
-      <c r="G12" s="373"/>
-      <c r="H12" s="373"/>
-      <c r="I12" s="373"/>
-      <c r="J12" s="373"/>
+      <c r="F12" s="376"/>
+      <c r="G12" s="376"/>
+      <c r="H12" s="376"/>
+      <c r="I12" s="376"/>
+      <c r="J12" s="376"/>
     </row>
     <row r="13" spans="2:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D13" s="245"/>
       <c r="E13" s="245"/>
-      <c r="F13" s="373"/>
-      <c r="G13" s="373"/>
-      <c r="H13" s="373"/>
-      <c r="I13" s="373"/>
-      <c r="J13" s="373"/>
+      <c r="F13" s="376"/>
+      <c r="G13" s="376"/>
+      <c r="H13" s="376"/>
+      <c r="I13" s="376"/>
+      <c r="J13" s="376"/>
     </row>
     <row r="14" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D14" s="245"/>
@@ -14098,22 +14098,22 @@
     <row r="15" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="245"/>
       <c r="E15" s="245"/>
-      <c r="F15" s="374" t="s">
+      <c r="F15" s="377" t="s">
         <v>2</v>
       </c>
-      <c r="G15" s="375"/>
-      <c r="H15" s="375"/>
-      <c r="I15" s="375"/>
-      <c r="J15" s="375"/>
+      <c r="G15" s="378"/>
+      <c r="H15" s="378"/>
+      <c r="I15" s="378"/>
+      <c r="J15" s="378"/>
     </row>
     <row r="16" spans="2:10" ht="73.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D16" s="245"/>
       <c r="E16" s="245"/>
-      <c r="F16" s="375"/>
-      <c r="G16" s="375"/>
-      <c r="H16" s="375"/>
-      <c r="I16" s="375"/>
-      <c r="J16" s="375"/>
+      <c r="F16" s="378"/>
+      <c r="G16" s="378"/>
+      <c r="H16" s="378"/>
+      <c r="I16" s="378"/>
+      <c r="J16" s="378"/>
     </row>
     <row r="17" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D17" s="245"/>
@@ -14127,13 +14127,13 @@
     <row r="18" spans="2:10" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D18" s="245"/>
       <c r="E18" s="245"/>
-      <c r="F18" s="376" t="s">
+      <c r="F18" s="379" t="s">
         <v>3</v>
       </c>
-      <c r="G18" s="377"/>
-      <c r="H18" s="377"/>
-      <c r="I18" s="377"/>
-      <c r="J18" s="377"/>
+      <c r="G18" s="380"/>
+      <c r="H18" s="380"/>
+      <c r="I18" s="380"/>
+      <c r="J18" s="380"/>
     </row>
     <row r="19" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="245"/>
@@ -14147,31 +14147,31 @@
     <row r="20" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="245"/>
       <c r="E20" s="245"/>
-      <c r="F20" s="378" t="s">
+      <c r="F20" s="381" t="s">
         <v>4</v>
       </c>
-      <c r="G20" s="378"/>
-      <c r="H20" s="378"/>
-      <c r="I20" s="378"/>
-      <c r="J20" s="378"/>
+      <c r="G20" s="381"/>
+      <c r="H20" s="381"/>
+      <c r="I20" s="381"/>
+      <c r="J20" s="381"/>
     </row>
     <row r="21" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="245"/>
       <c r="E21" s="245"/>
-      <c r="F21" s="378"/>
-      <c r="G21" s="378"/>
-      <c r="H21" s="378"/>
-      <c r="I21" s="378"/>
-      <c r="J21" s="378"/>
+      <c r="F21" s="381"/>
+      <c r="G21" s="381"/>
+      <c r="H21" s="381"/>
+      <c r="I21" s="381"/>
+      <c r="J21" s="381"/>
     </row>
     <row r="22" spans="2:10" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="245"/>
       <c r="E22" s="245"/>
-      <c r="F22" s="378"/>
-      <c r="G22" s="378"/>
-      <c r="H22" s="378"/>
-      <c r="I22" s="378"/>
-      <c r="J22" s="378"/>
+      <c r="F22" s="381"/>
+      <c r="G22" s="381"/>
+      <c r="H22" s="381"/>
+      <c r="I22" s="381"/>
+      <c r="J22" s="381"/>
     </row>
     <row r="23" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="245"/>
@@ -14185,22 +14185,22 @@
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D24" s="245"/>
       <c r="E24" s="245"/>
-      <c r="F24" s="379" t="s">
+      <c r="F24" s="382" t="s">
         <v>5</v>
       </c>
-      <c r="G24" s="379"/>
-      <c r="H24" s="379"/>
-      <c r="I24" s="379"/>
-      <c r="J24" s="379"/>
+      <c r="G24" s="382"/>
+      <c r="H24" s="382"/>
+      <c r="I24" s="382"/>
+      <c r="J24" s="382"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D25" s="245"/>
       <c r="E25" s="245"/>
-      <c r="F25" s="379"/>
-      <c r="G25" s="379"/>
-      <c r="H25" s="379"/>
-      <c r="I25" s="379"/>
-      <c r="J25" s="379"/>
+      <c r="F25" s="382"/>
+      <c r="G25" s="382"/>
+      <c r="H25" s="382"/>
+      <c r="I25" s="382"/>
+      <c r="J25" s="382"/>
     </row>
     <row r="26" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="245"/>
@@ -14214,49 +14214,49 @@
     <row r="27" spans="2:10" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="245"/>
       <c r="E27" s="245"/>
-      <c r="F27" s="369"/>
-      <c r="G27" s="369"/>
-      <c r="H27" s="369"/>
-      <c r="I27" s="369"/>
-      <c r="J27" s="369"/>
+      <c r="F27" s="372"/>
+      <c r="G27" s="372"/>
+      <c r="H27" s="372"/>
+      <c r="I27" s="372"/>
+      <c r="J27" s="372"/>
     </row>
     <row r="28" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="245"/>
       <c r="E28" s="245"/>
-      <c r="F28" s="380" t="s">
-        <v>443</v>
-      </c>
-      <c r="G28" s="380"/>
-      <c r="H28" s="380"/>
-      <c r="I28" s="380"/>
-      <c r="J28" s="380"/>
+      <c r="F28" s="383" t="s">
+        <v>442</v>
+      </c>
+      <c r="G28" s="383"/>
+      <c r="H28" s="383"/>
+      <c r="I28" s="383"/>
+      <c r="J28" s="383"/>
     </row>
     <row r="29" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="245"/>
       <c r="E29" s="245"/>
-      <c r="F29" s="380"/>
-      <c r="G29" s="380"/>
-      <c r="H29" s="380"/>
-      <c r="I29" s="380"/>
-      <c r="J29" s="380"/>
+      <c r="F29" s="383"/>
+      <c r="G29" s="383"/>
+      <c r="H29" s="383"/>
+      <c r="I29" s="383"/>
+      <c r="J29" s="383"/>
     </row>
     <row r="30" spans="2:10" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="245"/>
       <c r="E30" s="245"/>
-      <c r="F30" s="380"/>
-      <c r="G30" s="380"/>
-      <c r="H30" s="380"/>
-      <c r="I30" s="380"/>
-      <c r="J30" s="380"/>
+      <c r="F30" s="383"/>
+      <c r="G30" s="383"/>
+      <c r="H30" s="383"/>
+      <c r="I30" s="383"/>
+      <c r="J30" s="383"/>
     </row>
     <row r="31" spans="2:10" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="245"/>
       <c r="E31" s="245"/>
-      <c r="F31" s="381"/>
-      <c r="G31" s="381"/>
-      <c r="H31" s="381"/>
-      <c r="I31" s="381"/>
-      <c r="J31" s="381"/>
+      <c r="F31" s="371"/>
+      <c r="G31" s="371"/>
+      <c r="H31" s="371"/>
+      <c r="I31" s="371"/>
+      <c r="J31" s="371"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="250" t="s">
@@ -14305,15 +14305,15 @@
     <row r="36" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="116"/>
       <c r="C36" s="113"/>
-      <c r="D36" s="381" t="s">
+      <c r="D36" s="371" t="s">
         <v>8</v>
       </c>
-      <c r="E36" s="381"/>
-      <c r="F36" s="381"/>
-      <c r="G36" s="381"/>
-      <c r="H36" s="381"/>
-      <c r="I36" s="381"/>
-      <c r="J36" s="381"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
+      <c r="G36" s="371"/>
+      <c r="H36" s="371"/>
+      <c r="I36" s="371"/>
+      <c r="J36" s="371"/>
     </row>
     <row r="37" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="117"/>
@@ -14329,24 +14329,24 @@
     <row r="38" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="241"/>
       <c r="C38" s="113"/>
-      <c r="D38" s="369" t="s">
+      <c r="D38" s="372" t="s">
         <v>9</v>
       </c>
-      <c r="E38" s="369"/>
-      <c r="F38" s="369"/>
-      <c r="G38" s="369"/>
-      <c r="H38" s="369"/>
-      <c r="I38" s="369"/>
-      <c r="J38" s="369"/>
+      <c r="E38" s="372"/>
+      <c r="F38" s="372"/>
+      <c r="G38" s="372"/>
+      <c r="H38" s="372"/>
+      <c r="I38" s="372"/>
+      <c r="J38" s="372"/>
     </row>
     <row r="39" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D39" s="369"/>
-      <c r="E39" s="369"/>
-      <c r="F39" s="369"/>
-      <c r="G39" s="369"/>
-      <c r="H39" s="369"/>
-      <c r="I39" s="369"/>
-      <c r="J39" s="369"/>
+      <c r="D39" s="372"/>
+      <c r="E39" s="372"/>
+      <c r="F39" s="372"/>
+      <c r="G39" s="372"/>
+      <c r="H39" s="372"/>
+      <c r="I39" s="372"/>
+      <c r="J39" s="372"/>
     </row>
     <row r="40" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="117"/>
@@ -14364,15 +14364,15 @@
         <v>10</v>
       </c>
       <c r="C41" s="113"/>
-      <c r="D41" s="382" t="s">
+      <c r="D41" s="369" t="s">
         <v>11</v>
       </c>
-      <c r="E41" s="382"/>
-      <c r="F41" s="382"/>
-      <c r="G41" s="382"/>
-      <c r="H41" s="382"/>
-      <c r="I41" s="382"/>
-      <c r="J41" s="382"/>
+      <c r="E41" s="369"/>
+      <c r="F41" s="369"/>
+      <c r="G41" s="369"/>
+      <c r="H41" s="369"/>
+      <c r="I41" s="369"/>
+      <c r="J41" s="369"/>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="113"/>
@@ -14386,30 +14386,30 @@
       <c r="J42" s="245"/>
     </row>
     <row r="43" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="383" t="s">
+      <c r="B43" s="370" t="s">
         <v>12</v>
       </c>
       <c r="C43" s="103"/>
-      <c r="D43" s="381" t="s">
+      <c r="D43" s="371" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="381"/>
-      <c r="F43" s="381"/>
-      <c r="G43" s="381"/>
-      <c r="H43" s="381"/>
-      <c r="I43" s="381"/>
-      <c r="J43" s="381"/>
+      <c r="E43" s="371"/>
+      <c r="F43" s="371"/>
+      <c r="G43" s="371"/>
+      <c r="H43" s="371"/>
+      <c r="I43" s="371"/>
+      <c r="J43" s="371"/>
     </row>
     <row r="44" spans="2:11" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="B44" s="383"/>
+      <c r="B44" s="370"/>
       <c r="C44" s="103"/>
-      <c r="D44" s="381"/>
-      <c r="E44" s="381"/>
-      <c r="F44" s="381"/>
-      <c r="G44" s="381"/>
-      <c r="H44" s="381"/>
-      <c r="I44" s="381"/>
-      <c r="J44" s="381"/>
+      <c r="D44" s="371"/>
+      <c r="E44" s="371"/>
+      <c r="F44" s="371"/>
+      <c r="G44" s="371"/>
+      <c r="H44" s="371"/>
+      <c r="I44" s="371"/>
+      <c r="J44" s="371"/>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D45" s="112"/>
@@ -14421,17 +14421,17 @@
       <c r="J45" s="114"/>
     </row>
     <row r="46" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="381" t="s">
-        <v>418</v>
-      </c>
-      <c r="C46" s="381"/>
-      <c r="D46" s="381"/>
-      <c r="E46" s="381"/>
-      <c r="F46" s="381"/>
-      <c r="G46" s="381"/>
-      <c r="H46" s="381"/>
-      <c r="I46" s="381"/>
-      <c r="J46" s="381"/>
+      <c r="B46" s="371" t="s">
+        <v>417</v>
+      </c>
+      <c r="C46" s="371"/>
+      <c r="D46" s="371"/>
+      <c r="E46" s="371"/>
+      <c r="F46" s="371"/>
+      <c r="G46" s="371"/>
+      <c r="H46" s="371"/>
+      <c r="I46" s="371"/>
+      <c r="J46" s="371"/>
       <c r="K46" s="107"/>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
@@ -14466,17 +14466,17 @@
       <c r="J49" s="112"/>
     </row>
     <row r="50" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="381" t="s">
+      <c r="B50" s="371" t="s">
         <v>15</v>
       </c>
-      <c r="C50" s="381"/>
-      <c r="D50" s="381"/>
-      <c r="E50" s="381"/>
-      <c r="F50" s="381"/>
-      <c r="G50" s="381"/>
-      <c r="H50" s="381"/>
-      <c r="I50" s="381"/>
-      <c r="J50" s="381"/>
+      <c r="C50" s="371"/>
+      <c r="D50" s="371"/>
+      <c r="E50" s="371"/>
+      <c r="F50" s="371"/>
+      <c r="G50" s="371"/>
+      <c r="H50" s="371"/>
+      <c r="I50" s="371"/>
+      <c r="J50" s="371"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D51" s="114"/>
@@ -14539,11 +14539,6 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="17">
-    <mergeCell ref="D41:J41"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="D43:J44"/>
-    <mergeCell ref="B46:J46"/>
-    <mergeCell ref="B50:J50"/>
     <mergeCell ref="D38:J39"/>
     <mergeCell ref="B5:J5"/>
     <mergeCell ref="F9:J9"/>
@@ -14556,6 +14551,11 @@
     <mergeCell ref="F28:J30"/>
     <mergeCell ref="F31:J31"/>
     <mergeCell ref="D36:J36"/>
+    <mergeCell ref="D41:J41"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="D43:J44"/>
+    <mergeCell ref="B46:J46"/>
+    <mergeCell ref="B50:J50"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F9:J9" location="Input_Beschaffung!A1" display="Geben Sie die übergeordneten Informationen zu Ihrem Beschaffungsfall ein. Hier können Informationen wie die erwartete jährliche Fahrleistung, die Art der Beschaffung (Kauf/Leasing) und weitere Informationen eingegeben werden." xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -14597,7 +14597,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>21</v>
@@ -14610,7 +14610,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -14626,7 +14626,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" s="54">
         <v>4</v>
@@ -14639,7 +14639,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C7" s="102" t="str">
         <f>IF(Anbieter4=0,"",Anbieter4)</f>
@@ -14661,7 +14661,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C9" s="102"/>
       <c r="E9" s="125"/>
@@ -14669,7 +14669,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C10" s="102" t="str">
         <f>IF(Hersteller4=0,"",Hersteller4)</f>
@@ -14681,7 +14681,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C11" s="102" t="str">
         <f>IF(Modell4=0,"",Modell4)</f>
@@ -14693,7 +14693,7 @@
     </row>
     <row r="12" spans="1:6" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="56" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C12" s="102" t="str">
         <f>IF(Zusatzinfo4=0,"",Zusatzinfo4)</f>
@@ -14705,7 +14705,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B13" s="57" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C13" s="102" t="str">
         <f>IF(Antriebsart4=0,"",Antriebsart4)</f>
@@ -14716,7 +14716,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C14" s="102" t="str">
         <f>IF(Energie4=0,"",Energie4)</f>
@@ -14732,7 +14732,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B16" s="154" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -14748,7 +14748,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B18" s="72" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C18" s="288">
         <f>0.0057*(ReichwPHEV4/23)^3-0.0838*(ReichwPHEV4/23)^2+0.4261*(ReichwPHEV4/23)+ 0.1633</f>
@@ -14760,35 +14760,35 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C19" s="289">
         <f>Verbrauch4/(1-0.9*C18)</f>
         <v>0</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E19" s="125"/>
       <c r="F19" s="125"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C20" s="290">
         <f>VerbEl_WLTP4/C18</f>
         <v>0</v>
       </c>
       <c r="D20" s="184" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E20" s="125"/>
       <c r="F20" s="125"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" s="186" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C21" s="291">
         <f>0.0021*(ReichwPHEV4/23)^3-0.0358*(ReichwPHEV4/23)^2+0.2607*(ReichwPHEV4/23)- 0.0267</f>
@@ -14803,14 +14803,14 @@
         <v>12</v>
       </c>
       <c r="B22" s="439" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C22" s="292">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
       <c r="D22" s="185" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E22" s="125"/>
       <c r="F22" s="125"/>
@@ -14823,7 +14823,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="183" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E23" s="125"/>
       <c r="F23" s="125"/>
@@ -14835,7 +14835,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B25" s="154" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -14848,7 +14848,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C27" s="61"/>
       <c r="D27" s="60"/>
@@ -14857,42 +14857,42 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C28" s="279">
         <f>IF(Antriebsart4="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie4,EnKostList,6,FALSE),0)*IF(Antriebsart4="Plug-In-Hybrid (PHEV)",VerbPHEV4,Verbrauch4)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E28" s="125"/>
       <c r="F28" s="125"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C29" s="279">
         <f>IF(Antriebsart4="Verbrenner",0,VLOOKUP("Strom",EnKostList,6,FALSE)*IF(Antriebsart4="Plug-In-Hybrid (PHEV)",VerbElPHEV4,VerbEl_WLTP4)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E29" s="125"/>
       <c r="F29" s="125"/>
     </row>
     <row r="30" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C30" s="280">
         <f>SUM(C28:C29)</f>
         <v>0</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E30" s="125"/>
       <c r="F30" s="125"/>
@@ -14905,7 +14905,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C32" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie4)</f>
@@ -14917,70 +14917,70 @@
     </row>
     <row r="33" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B33" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C33" s="279">
         <f>IF(Antriebsart4="Plug-In-Hybrid (PHEV)",VerbPHEV4*VLOOKUP(Energie4,CO2List,2,FALSE)/100,CO2_4)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E33" s="125"/>
       <c r="F33" s="125"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C34" s="279">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E34" s="125"/>
       <c r="F34" s="125"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C35" s="287">
         <f>IF(Energie4="Strom",0,NOX_4*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
       <c r="D35" s="65" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E35" s="125"/>
       <c r="F35" s="125"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B36" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C36" s="287">
         <f>IF(Energie4="Strom",0,Partikel4*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
       <c r="D36" s="65" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E36" s="125"/>
       <c r="F36" s="125"/>
     </row>
     <row r="37" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C37" s="280">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
       <c r="D37" s="64" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E37" s="125"/>
       <c r="F37" s="125"/>
@@ -14993,7 +14993,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B39" s="60" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C39" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie4,IF(Antriebsart4="Plug-In-Hybrid (PHEV)","+Strom",""))</f>
@@ -15005,28 +15005,28 @@
     </row>
     <row r="40" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C40" s="279">
         <f>IFERROR(IF(Antriebsart4="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP4/100*Fahrleistung/1000000,IF(Antriebsart4="Verbrenner",VLOOKUP(Energie4,CO2List,3,FALSE)*Verbrauch4/100*Fahrleistung/1000000,VLOOKUP(Energie4,CO2List,3,FALSE)*VerbPHEV4/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV4/100*Fahrleistung/1000000)),0)</f>
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E40" s="125"/>
       <c r="F40" s="125"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C41" s="279">
         <f>C40*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E41" s="125"/>
       <c r="F41" s="125"/>
@@ -15037,7 +15037,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B43" s="154" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -15054,55 +15054,55 @@
     <row r="45" spans="1:6" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="107"/>
       <c r="B45" s="90" t="s">
+        <v>155</v>
+      </c>
+      <c r="C45" s="134" t="s">
         <v>156</v>
-      </c>
-      <c r="C45" s="134" t="s">
-        <v>157</v>
       </c>
       <c r="D45" s="62"/>
       <c r="E45" s="125"/>
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="383" t="s">
+      <c r="A46" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="437" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C46" s="281">
         <f>IF(OR(Antriebsart4="Vollelektrisch (BEV)",Antriebsart4="Plug-In-Hybrid (PHEV)"),Batterie4*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
       <c r="D46" s="131" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E46" s="127"/>
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="383"/>
+      <c r="A47" s="370"/>
       <c r="B47" s="438"/>
       <c r="C47" s="281" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D47" s="130" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E47" s="127"/>
       <c r="F47" s="125"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C48" s="279" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E48" s="125"/>
       <c r="F48" s="125"/>
@@ -15126,20 +15126,20 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="70" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C54" s="282">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis4,0),Gesamtpreis4*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl4,0))</f>
         <v>0</v>
       </c>
       <c r="D54" s="68" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E54" s="69"/>
       <c r="F54" s="58"/>
@@ -15149,72 +15149,72 @@
         <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis4-Gesamtpreis4*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>0</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E55" s="125"/>
       <c r="F55" s="73"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C56" s="283">
         <f>C30*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F56" s="73"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C57" s="283">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F57" s="58"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C58" s="283">
         <f>C41*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B59" s="333" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C59" s="334" t="e">
         <f>C48*Haltedauer</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D59" s="80" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="383" t="s">
+      <c r="A60" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -15232,7 +15232,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="383"/>
+      <c r="A61" s="370"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -15248,7 +15248,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="383"/>
+      <c r="A62" s="370"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -15265,14 +15265,14 @@
     </row>
     <row r="63" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C63" s="284" t="e">
         <f>SUM(C54:C62)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D63" s="64" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E63" s="14"/>
       <c r="F63" s="58"/>
@@ -15287,26 +15287,26 @@
     </row>
     <row r="65" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B65" s="68" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C65" s="285" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D65" s="68" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="66" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B66" s="72" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C66" s="286">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D66" s="72" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E66" s="71"/>
     </row>
@@ -15357,7 +15357,7 @@
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>21</v>
@@ -15370,7 +15370,7 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -15386,7 +15386,7 @@
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" s="54">
         <v>5</v>
@@ -15399,7 +15399,7 @@
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C7" s="102" t="str">
         <f>IF(Anbieter5=0,"",Anbieter5)</f>
@@ -15421,7 +15421,7 @@
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C9" s="102"/>
       <c r="E9" s="125"/>
@@ -15429,7 +15429,7 @@
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C10" s="102" t="str">
         <f>IF(Hersteller5=0,"",Hersteller5)</f>
@@ -15441,7 +15441,7 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C11" s="102" t="str">
         <f>IF(Modell5=0,"",Modell5)</f>
@@ -15453,7 +15453,7 @@
     </row>
     <row r="12" spans="2:6" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="56" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C12" s="102" t="str">
         <f>IF(Zusatzinfo5=0,"",Zusatzinfo5)</f>
@@ -15465,7 +15465,7 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="57" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C13" s="102" t="str">
         <f>IF(Antriebsart5=0,"",Antriebsart5)</f>
@@ -15476,7 +15476,7 @@
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C14" s="102" t="str">
         <f>IF(Energie5=0,"",Energie5)</f>
@@ -15494,7 +15494,7 @@
     </row>
     <row r="16" spans="2:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="154" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -15511,7 +15511,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B18" s="72" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C18" s="288">
         <f>0.0057*(ReichwPHEV5/23)^3-0.0838*(ReichwPHEV5/23)^2+0.4261*(ReichwPHEV5/23)+ 0.1633</f>
@@ -15523,35 +15523,35 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C19" s="289">
         <f>Verbrauch5/(1-0.9*C18)</f>
         <v>0</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E19" s="125"/>
       <c r="F19" s="125"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C20" s="290">
         <f>VerbEl_WLTP5/C18</f>
         <v>0</v>
       </c>
       <c r="D20" s="184" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E20" s="125"/>
       <c r="F20" s="125"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" s="186" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C21" s="291">
         <f>0.0021*(ReichwPHEV5/23)^3-0.0358*(ReichwPHEV5/23)^2+0.2607*(ReichwPHEV5/23)- 0.0267</f>
@@ -15566,14 +15566,14 @@
         <v>12</v>
       </c>
       <c r="B22" s="439" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C22" s="292">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
       <c r="D22" s="185" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E22" s="125"/>
       <c r="F22" s="125"/>
@@ -15586,7 +15586,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="183" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E23" s="125"/>
       <c r="F23" s="125"/>
@@ -15598,7 +15598,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B25" s="154" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -15611,7 +15611,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C27" s="61"/>
       <c r="D27" s="60"/>
@@ -15620,42 +15620,42 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C28" s="279">
         <f>IF(Antriebsart5="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie5,EnKostList,6,FALSE),0)*IF(Antriebsart5="Plug-In-Hybrid (PHEV)",VerbPHEV5,Verbrauch5)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E28" s="125"/>
       <c r="F28" s="125"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C29" s="279">
         <f>IF(Antriebsart5="Verbrenner",0,VLOOKUP("Strom",EnKostList,6,FALSE)*IF(Antriebsart5="Plug-In-Hybrid (PHEV)",VerbElPHEV5,VerbEl_WLTP5)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E29" s="125"/>
       <c r="F29" s="125"/>
     </row>
     <row r="30" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C30" s="280">
         <f>SUM(C28:C29)</f>
         <v>0</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E30" s="125"/>
       <c r="F30" s="125"/>
@@ -15668,7 +15668,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C32" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie5)</f>
@@ -15681,70 +15681,70 @@
     <row r="33" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A33" s="126"/>
       <c r="B33" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C33" s="279">
         <f>IF(Antriebsart5="Plug-In-Hybrid (PHEV)",VerbPHEV5*VLOOKUP(Energie5,CO2List,2,FALSE)/100,CO2_5)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E33" s="125"/>
       <c r="F33" s="125"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C34" s="279">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E34" s="125"/>
       <c r="F34" s="125"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C35" s="287">
         <f>IF(Energie5="Strom",0,NOX_5*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
       <c r="D35" s="65" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E35" s="125"/>
       <c r="F35" s="125"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B36" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C36" s="287">
         <f>IF(Energie5="Strom",0,Partikel5*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
       <c r="D36" s="65" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E36" s="125"/>
       <c r="F36" s="125"/>
     </row>
     <row r="37" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C37" s="280">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
       <c r="D37" s="64" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E37" s="125"/>
       <c r="F37" s="125"/>
@@ -15757,7 +15757,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B39" s="60" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C39" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie5,IF(Antriebsart5="Plug-In-Hybrid (PHEV)","+Strom",""))</f>
@@ -15769,28 +15769,28 @@
     </row>
     <row r="40" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C40" s="279">
         <f>IFERROR(IF(Antriebsart5="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP5/100*Fahrleistung/1000000,IF(Antriebsart5="Verbrenner",VLOOKUP(Energie5,CO2List,3,FALSE)*Verbrauch5/100*Fahrleistung/1000000,VLOOKUP(Energie5,CO2List,3,FALSE)*VerbPHEV5/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV5/100*Fahrleistung/1000000)),0)</f>
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E40" s="125"/>
       <c r="F40" s="125"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C41" s="279">
         <f>C40*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E41" s="125"/>
       <c r="F41" s="125"/>
@@ -15801,7 +15801,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B43" s="154" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -15818,55 +15818,55 @@
     <row r="45" spans="1:6" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="107"/>
       <c r="B45" s="90" t="s">
+        <v>155</v>
+      </c>
+      <c r="C45" s="134" t="s">
         <v>156</v>
-      </c>
-      <c r="C45" s="134" t="s">
-        <v>157</v>
       </c>
       <c r="D45" s="62"/>
       <c r="E45" s="125"/>
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="383" t="s">
+      <c r="A46" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="437" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C46" s="281">
         <f>IF(OR(Antriebsart5="Vollelektrisch (BEV)",Antriebsart5="Plug-In-Hybrid (PHEV)"),Batterie5*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
       <c r="D46" s="131" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E46" s="127"/>
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="383"/>
+      <c r="A47" s="370"/>
       <c r="B47" s="438"/>
       <c r="C47" s="281" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D47" s="130" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E47" s="127"/>
       <c r="F47" s="125"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C48" s="279" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E48" s="125"/>
       <c r="F48" s="125"/>
@@ -15890,20 +15890,20 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="70" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C54" s="282">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis5,0),Gesamtpreis5*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl5,0))</f>
         <v>0</v>
       </c>
       <c r="D54" s="68" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E54" s="69"/>
       <c r="F54" s="58"/>
@@ -15913,72 +15913,72 @@
         <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis5-Gesamtpreis5*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>0</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E55" s="125"/>
       <c r="F55" s="73"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C56" s="283">
         <f>C30*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F56" s="73"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C57" s="283">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F57" s="58"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C58" s="283">
         <f>C41*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B59" s="329" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C59" s="330" t="e">
         <f>C48*Haltedauer</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D59" s="329" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="383" t="s">
+      <c r="A60" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -15996,7 +15996,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="383"/>
+      <c r="A61" s="370"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -16012,7 +16012,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="383"/>
+      <c r="A62" s="370"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -16029,14 +16029,14 @@
     </row>
     <row r="63" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C63" s="284" t="e">
         <f>SUM(C54:C62)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D63" s="64" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E63" s="14"/>
       <c r="F63" s="58"/>
@@ -16051,26 +16051,26 @@
     </row>
     <row r="65" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B65" s="68" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C65" s="285" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D65" s="68" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="66" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B66" s="72" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C66" s="286">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D66" s="72" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E66" s="71"/>
     </row>
@@ -16116,7 +16116,7 @@
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H2" s="106" t="s">
         <v>21</v>
@@ -16124,7 +16124,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -16133,18 +16133,18 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C6" s="63" t="s">
+        <v>166</v>
+      </c>
+      <c r="D6" s="63" t="s">
         <v>167</v>
       </c>
-      <c r="D6" s="63" t="s">
-        <v>168</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C7" s="302">
         <v>74.027000000000001</v>
@@ -16153,12 +16153,12 @@
         <v>23.4</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C8" s="302">
         <v>72.787000000000006</v>
@@ -16167,12 +16167,12 @@
         <v>23.2</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C9" s="302">
         <v>56.220999999999997</v>
@@ -16181,12 +16181,12 @@
         <v>20.3</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="92" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
@@ -16196,7 +16196,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B12" s="154" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C12" s="93"/>
       <c r="D12" s="5"/>
@@ -16214,14 +16214,14 @@
     </row>
     <row r="14" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="110" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C14" s="441" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D14" s="441"/>
       <c r="E14" s="442" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F14" s="442"/>
       <c r="G14" s="304"/>
@@ -16229,40 +16229,40 @@
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="66"/>
       <c r="B15" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C15" s="58">
         <v>1</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E15" s="136">
         <f>42.722*0.832</f>
         <v>35.544704000000003</v>
       </c>
       <c r="F15" s="111" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G15" s="111"/>
       <c r="H15" s="136"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C16" s="58">
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E16" s="136">
         <f>43.543*0.742</f>
         <v>32.308906</v>
       </c>
       <c r="F16" s="111" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G16" s="111"/>
       <c r="H16" s="136"/>
@@ -16270,54 +16270,54 @@
     <row r="17" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A17" s="66"/>
       <c r="B17" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C17" s="58">
         <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E17" s="303">
         <v>46.5</v>
       </c>
       <c r="F17" s="111" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G17" s="111"/>
     </row>
     <row r="18" spans="1:37" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="92" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D18" s="106"/>
       <c r="E18" s="10"/>
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B20" s="154" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="H20" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="21" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B21" s="66"/>
       <c r="I21" s="58" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J21" s="135" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="K21" s="135"/>
       <c r="L21" s="135"/>
       <c r="M21" s="135"/>
       <c r="O21" s="137" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P21" s="137"/>
       <c r="Q21" s="137"/>
@@ -16327,13 +16327,13 @@
     <row r="22" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B22" s="66"/>
       <c r="C22" s="63" t="s">
+        <v>166</v>
+      </c>
+      <c r="D22" s="63" t="s">
         <v>167</v>
       </c>
-      <c r="D22" s="63" t="s">
-        <v>168</v>
-      </c>
       <c r="E22" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:37" ht="16.2" x14ac:dyDescent="0.35">
@@ -16341,7 +16341,7 @@
         <v>12</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C23" s="58">
         <v>0</v>
@@ -16351,12 +16351,12 @@
         <v>#DIV/0!</v>
       </c>
       <c r="E23" s="74" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
       <c r="I23" s="58" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J23" s="2">
         <v>2023</v>
@@ -16445,7 +16445,7 @@
     </row>
     <row r="24" spans="1:37" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B24" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C24" s="96">
         <f>C7*E15</f>
@@ -16456,10 +16456,10 @@
         <v>831.74607360000005</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I24" s="58" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="J24" s="300">
         <v>445</v>
@@ -16548,7 +16548,7 @@
     </row>
     <row r="25" spans="1:37" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B25" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C25" s="96">
         <f>C8*E16</f>
@@ -16559,12 +16559,12 @@
         <v>749.56661919999999</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:37" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B26" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C26" s="96">
         <f>C9*E17</f>
@@ -16575,7 +16575,7 @@
         <v>943.95</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K26" s="136"/>
     </row>
@@ -16630,7 +16630,7 @@
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q2" s="106" t="s">
         <v>21</v>
@@ -16638,17 +16638,17 @@
     </row>
     <row r="39" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="234" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="234" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="41" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="234" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="42" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16659,12 +16659,12 @@
     </row>
     <row r="44" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="267" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="I45" s="106"/>
     </row>
@@ -16674,39 +16674,39 @@
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B51" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
@@ -16714,1111 +16714,1111 @@
         <v>31</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B55" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B60" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B62" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B63" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B64" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B65" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B66" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B67" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B68" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B69" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B70" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>225</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B71" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B72" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B73" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B74" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B75" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B76" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B77" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B78" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B79" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>243</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B80" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="81" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B81" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="82" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B82" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="83" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B83" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="84" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B84" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>253</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="85" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B85" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="86" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B86" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="87" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B87" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="88" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B88" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="89" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B89" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>263</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B90" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="91" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B91" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>267</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="92" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B92" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="93" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B93" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="94" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B94" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="95" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B95" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>275</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="96" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B96" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="97" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B97" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="98" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B98" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="99" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B99" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>283</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="100" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B100" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="101" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B101" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="102" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B102" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="103" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B103" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="104" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B104" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="105" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B105" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="106" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B106" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>297</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="107" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B107" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="108" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B108" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>301</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="109" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B109" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>303</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="110" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B110" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>305</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="111" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B111" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="112" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B112" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="113" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B113" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="114" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B114" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="115" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B115" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>315</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="116" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B116" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="117" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B117" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>319</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="118" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B118" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="119" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B119" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="120" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B120" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="121" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B121" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="122" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B122" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="123" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B123" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="124" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B124" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="125" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B125" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>335</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="126" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B126" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="D126" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="127" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B127" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="128" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B128" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>341</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="129" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B129" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="130" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B130" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="131" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B131" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>509</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="132" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B132" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>511</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="133" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B133" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>513</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="134" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B134" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>515</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="135" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B135" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>517</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="136" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B136" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>519</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="137" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B137" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>521</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="138" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B138" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>523</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B139" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>525</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B140" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>527</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="141" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B141" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>529</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="142" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B142" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="D142" s="1" t="s">
         <v>531</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="143" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B143" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>533</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="144" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B144" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="D144" s="1" t="s">
         <v>535</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="145" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B145" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>537</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="146" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B146" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>539</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="147" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B147" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>541</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B148" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>543</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="149" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B149" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D149" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="150" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B150" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D150" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="151" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B151" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>351</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="152" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B152" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>353</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="153" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B153" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="D153" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="154" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B154" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="155" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B155" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="156" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B156" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="157" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B157" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="158" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B158" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="159" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B159" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>548</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="160" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B160" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>550</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="161" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B161" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="D161" s="1" t="s">
         <v>552</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="162" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B162" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="D162" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="163" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B163" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="164" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B164" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="165" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B165" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="166" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B166" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D166" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="167" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B167" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D167" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="168" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B168" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D168" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="169" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B169" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="170" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B170" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="171" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B171" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="172" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B172" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="173" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B173" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="174" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B174" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="175" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B175" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="176" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B176" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="177" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B177" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="178" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B178" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="179" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B179" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="180" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B180" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="181" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B181" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="182" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B182" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="183" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B183" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="184" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B184" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="185" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B185" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="186" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B186" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="187" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B187" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="188" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B188" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="189" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B189" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="D189" s="1" t="s">
         <v>392</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="190" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B190" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="191" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B191" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="D191" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="D191" s="1" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="192" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B192" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="D192" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -17848,7 +17848,7 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -17860,37 +17860,37 @@
         <v>30</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -17899,7 +17899,7 @@
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
@@ -17909,7 +17909,7 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -17918,22 +17918,22 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -17942,38 +17942,38 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
@@ -17982,34 +17982,34 @@
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.25">
@@ -18028,12 +18028,12 @@
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
@@ -18042,12 +18042,12 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B34" s="12" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" s="12" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -18073,7 +18073,7 @@
   <sheetData>
     <row r="2" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C2" s="132"/>
       <c r="E2" s="106" t="s">
@@ -18082,159 +18082,159 @@
     </row>
     <row r="4" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B4" s="275" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C4" s="275" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="5" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C5" s="276" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B6" s="275" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C6" s="275" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="7" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C7" s="276" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="8" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="275" t="s">
+        <v>459</v>
+      </c>
+      <c r="C8" s="270" t="s">
         <v>460</v>
-      </c>
-      <c r="C8" s="270" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="9" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C9" s="276" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="10" spans="2:5" s="275" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="277" t="s">
+        <v>402</v>
+      </c>
+      <c r="C10" s="270" t="s">
         <v>403</v>
-      </c>
-      <c r="C10" s="270" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="11" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B11" s="270"/>
       <c r="C11" s="276" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="12" spans="2:5" s="275" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
       <c r="B12" s="278" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C12" s="275" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="13" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C13" s="276" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="14" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="275" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C14" s="275" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="15" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C15" s="276" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="16" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B16" s="278" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C16" s="275" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="17" spans="2:3" s="275" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
       <c r="C17" s="276" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="18" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="275" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C18" s="275" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="19" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C19" s="276" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="20" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B20" s="275" t="s">
+        <v>409</v>
+      </c>
+      <c r="C20" s="275" t="s">
         <v>410</v>
-      </c>
-      <c r="C20" s="275" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="21" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C21" s="276" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="22" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B22" s="275" t="s">
+        <v>439</v>
+      </c>
+      <c r="C22" s="275" t="s">
         <v>440</v>
-      </c>
-      <c r="C22" s="275" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="23" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C23" s="276" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="24" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B24" s="275" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C24" s="275" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="25" spans="2:3" s="275" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
       <c r="C25" s="276" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="26" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="275" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C26" s="275" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="27" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C27" s="269" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="28" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -18283,7 +18283,7 @@
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I2" s="106" t="s">
         <v>21</v>
@@ -18302,7 +18302,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C6" s="388"/>
       <c r="D6" s="389"/>
@@ -18392,7 +18392,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C15" s="152"/>
       <c r="D15" s="55" t="s">
@@ -18432,7 +18432,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B19" s="298" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C19" s="151"/>
       <c r="D19" s="55"/>
@@ -18491,7 +18491,7 @@
         <v>36</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F26" s="274">
         <f>Grunddaten!E38</f>
@@ -18503,7 +18503,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B28" s="154" t="s">
-        <v>37</v>
+        <v>561</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
@@ -18527,17 +18527,17 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B30" s="170" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C30" s="10"/>
       <c r="D30" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F30" s="10"/>
       <c r="G30" s="10"/>
       <c r="I30" s="7"/>
       <c r="J30" s="146" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K30" s="8"/>
       <c r="L30" s="8"/>
@@ -18549,14 +18549,14 @@
         <v>12</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C31" s="171">
         <v>50</v>
       </c>
       <c r="D31" s="242"/>
       <c r="E31" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F31" s="172"/>
       <c r="G31" s="173"/>
@@ -18572,7 +18572,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B32" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C32" s="10">
         <f>100-J31</f>
@@ -18696,7 +18696,7 @@
     </row>
     <row r="2" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C2" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D2" s="2"/>
       <c r="J2" s="7"/>
@@ -18717,7 +18717,7 @@
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C4" s="155" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D4" s="156"/>
       <c r="E4" s="156"/>
@@ -18747,7 +18747,7 @@
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C6" s="88" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6" s="88"/>
       <c r="E6" s="161">
@@ -18773,7 +18773,7 @@
     </row>
     <row r="7" spans="2:18" s="91" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="162" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D7" s="162"/>
       <c r="E7" s="139"/>
@@ -18793,7 +18793,7 @@
     </row>
     <row r="8" spans="2:18" s="91" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C8" s="162" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D8" s="162"/>
       <c r="E8" s="139"/>
@@ -18816,7 +18816,7 @@
     </row>
     <row r="9" spans="2:18" s="91" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C9" s="162" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D9" s="162"/>
       <c r="E9" s="140"/>
@@ -18836,7 +18836,7 @@
     </row>
     <row r="10" spans="2:18" s="91" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C10" s="162" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D10" s="162"/>
       <c r="E10" s="140"/>
@@ -18847,7 +18847,7 @@
       <c r="J10" s="238"/>
       <c r="K10" s="236"/>
       <c r="L10" s="411" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="M10" s="411"/>
       <c r="N10" s="236"/>
@@ -18858,7 +18858,7 @@
     </row>
     <row r="11" spans="2:18" s="91" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C11" s="162" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D11" s="162"/>
       <c r="E11" s="141"/>
@@ -18868,7 +18868,7 @@
       <c r="I11" s="141"/>
       <c r="J11" s="238"/>
       <c r="K11" s="413" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L11" s="413"/>
       <c r="M11" s="413"/>
@@ -18880,7 +18880,7 @@
     </row>
     <row r="12" spans="2:18" s="91" customFormat="1" ht="55.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="165" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D12" s="88"/>
       <c r="E12" s="141"/>
@@ -18890,7 +18890,7 @@
       <c r="I12" s="141"/>
       <c r="J12" s="164"/>
       <c r="K12" s="412" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L12" s="412"/>
       <c r="M12" s="412"/>
@@ -18926,10 +18926,10 @@
     </row>
     <row r="14" spans="2:18" s="91" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C14" s="162" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" s="263" t="s">
         <v>60</v>
-      </c>
-      <c r="D14" s="263" t="s">
-        <v>61</v>
       </c>
       <c r="E14" s="362"/>
       <c r="F14" s="365"/>
@@ -18937,7 +18937,7 @@
       <c r="H14" s="362"/>
       <c r="I14" s="362"/>
       <c r="J14" s="264" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K14" s="236"/>
       <c r="L14" s="236"/>
@@ -18950,13 +18950,13 @@
     </row>
     <row r="15" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="410" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="408" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="408" t="s">
+      <c r="D15" s="360" t="s">
         <v>64</v>
-      </c>
-      <c r="D15" s="360" t="s">
-        <v>65</v>
       </c>
       <c r="E15" s="366"/>
       <c r="F15" s="257"/>
@@ -18976,7 +18976,7 @@
       <c r="B16" s="410"/>
       <c r="C16" s="409"/>
       <c r="D16" s="166" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E16" s="358"/>
       <c r="F16" s="257"/>
@@ -18996,10 +18996,10 @@
     <row r="17" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="410"/>
       <c r="C17" s="162" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="166" t="s">
         <v>67</v>
-      </c>
-      <c r="D17" s="166" t="s">
-        <v>68</v>
       </c>
       <c r="E17" s="258"/>
       <c r="F17" s="140"/>
@@ -19019,10 +19019,10 @@
     <row r="18" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="410"/>
       <c r="C18" s="162" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" s="166" t="s">
         <v>69</v>
-      </c>
-      <c r="D18" s="166" t="s">
-        <v>70</v>
       </c>
       <c r="E18" s="258"/>
       <c r="F18" s="140"/>
@@ -19045,10 +19045,10 @@
     <row r="19" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="410"/>
       <c r="C19" s="162" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D19" s="166" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E19" s="258"/>
       <c r="F19" s="140"/>
@@ -19068,10 +19068,10 @@
     <row r="20" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="410"/>
       <c r="C20" s="162" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" s="166" t="s">
         <v>72</v>
-      </c>
-      <c r="D20" s="166" t="s">
-        <v>73</v>
       </c>
       <c r="E20" s="260"/>
       <c r="F20" s="261"/>
@@ -19090,10 +19090,10 @@
     </row>
     <row r="21" spans="2:18" s="91" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C21" s="162" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" s="168" t="s">
         <v>74</v>
-      </c>
-      <c r="D21" s="168" t="s">
-        <v>75</v>
       </c>
       <c r="E21" s="257"/>
       <c r="F21" s="257"/>
@@ -19112,7 +19112,7 @@
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D22" s="228" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E22" s="368">
         <f>IF(AND(OR(Energie1="nicht verfügbar",COUNTIF(EnList1,Energie1)&lt;&gt;1),Antriebsart1&lt;&gt;0),1,0)</f>
@@ -19145,7 +19145,7 @@
     </row>
     <row r="23" spans="2:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C23" s="77" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D23" s="228"/>
       <c r="E23" s="368"/>
@@ -19160,12 +19160,12 @@
       <c r="R23" s="7"/>
     </row>
     <row r="24" spans="2:18" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="383" t="s">
+      <c r="B24" s="370" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="331"/>
       <c r="D24" s="322" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E24" s="256"/>
       <c r="F24" s="256"/>
@@ -19179,10 +19179,10 @@
       <c r="R24" s="7"/>
     </row>
     <row r="25" spans="2:18" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="383"/>
+      <c r="B25" s="370"/>
       <c r="C25" s="331"/>
       <c r="D25" s="322" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E25" s="256"/>
       <c r="F25" s="256"/>
@@ -19196,10 +19196,10 @@
       <c r="R25" s="7"/>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B26" s="383"/>
+      <c r="B26" s="370"/>
       <c r="C26" s="335"/>
       <c r="D26" s="322" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E26" s="256"/>
       <c r="F26" s="256"/>
@@ -19214,7 +19214,7 @@
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D27" s="228" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E27" s="368">
         <f>IF(OR(AND(COUNT(E15:E21)&lt;7,Antriebsart1="Plug-In-Hybrid (PHEV)"),AND(COUNT(E16,E21)&lt;2,Antriebsart1="Vollelektrisch (BEV)"),AND(COUNT(E15,E17:E19)&lt;4,Antriebsart1="Verbrenner")),1,0)</f>
@@ -19247,7 +19247,7 @@
     </row>
     <row r="28" spans="2:18" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E28" s="405" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F28" s="406"/>
       <c r="G28" s="406"/>
@@ -19256,7 +19256,7 @@
     </row>
     <row r="29" spans="2:18" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E29" s="400" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F29" s="387"/>
       <c r="G29" s="387"/>
@@ -19272,7 +19272,7 @@
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C32" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
   </sheetData>
@@ -19656,7 +19656,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="118" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C1" s="118"/>
       <c r="D1" s="118"/>
@@ -19670,7 +19670,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C2" s="227"/>
       <c r="D2" s="230" t="str">
@@ -19698,7 +19698,7 @@
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="18"/>
       <c r="B4" s="154" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -19713,7 +19713,7 @@
     <row r="6" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18"/>
       <c r="B6" s="12" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C6" s="418" t="str">
         <f>IF(Projektname=0,"",Projektname)</f>
@@ -19795,7 +19795,7 @@
       <c r="B12" s="12"/>
       <c r="C12" s="76"/>
       <c r="E12" s="58" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F12" s="85">
         <f>Fahrleistung</f>
@@ -19835,7 +19835,7 @@
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="18"/>
       <c r="B15" s="293" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="21"/>
@@ -19847,7 +19847,7 @@
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="18"/>
       <c r="B16" s="37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" s="23"/>
       <c r="D16" s="24">
@@ -19894,10 +19894,10 @@
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="18"/>
       <c r="B18" s="177" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C18" s="178" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D18" s="179" t="str">
         <f>IF(FinArt="Kauf",Gesamtpreis1,"")</f>
@@ -19930,7 +19930,7 @@
         <v>Fahrzeugkosten (Leasingrate/Miete)</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D19" s="41">
         <f>Erg.Fzg._1!$C$54+Erg.Fzg._1!$C$55</f>
@@ -19956,10 +19956,10 @@
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="336"/>
       <c r="B20" s="45" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D20" s="41">
         <f>Erg.Fzg._1!$C$56</f>
@@ -19987,10 +19987,10 @@
         <v>12</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D21" s="43">
         <f>Erg.Fzg._1!$C$57</f>
@@ -20016,10 +20016,10 @@
     <row r="22" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="416"/>
       <c r="B22" s="27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D22" s="43">
         <f>Erg.Fzg._1!C41*Haltedauer</f>
@@ -20046,10 +20046,10 @@
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="417"/>
       <c r="B23" s="45" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C23" s="325" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D23" s="326" t="e">
         <f>Erg.Fzg._1!$C$59</f>
@@ -20171,10 +20171,10 @@
     <row r="27" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="18"/>
       <c r="B27" s="49" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C27" s="50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D27" s="51" t="e">
         <f>IF(SUM(D19:D26)=0,"",SUM(D19:D26))</f>
@@ -20200,7 +20200,7 @@
     <row r="28" spans="1:9" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="18"/>
       <c r="B28" s="75" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C28" s="50"/>
       <c r="D28" s="51" t="str">
@@ -20228,10 +20228,10 @@
     <row r="29" spans="1:9" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A29" s="18"/>
       <c r="B29" s="108" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C29" s="66" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D29" s="231">
         <f>IF(AND(COUNTIF(D19:D23,0)&gt;0,Antriebsart1="Plug-In-Hybrid (PHEV)"),1,IF(AND(COUNTIF(D19:D23,0)&gt;1,Antriebsart1&lt;&gt;0),1,0))</f>
@@ -20261,10 +20261,10 @@
     <row r="30" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="33"/>
       <c r="B30" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" s="316" t="s">
         <v>90</v>
-      </c>
-      <c r="C30" s="316" t="s">
-        <v>91</v>
       </c>
       <c r="D30" s="314" t="e">
         <f>Erg.Fzg._1!$C$65</f>
@@ -20290,10 +20290,10 @@
     <row r="31" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="309"/>
       <c r="B31" s="98" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C31" s="317" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D31" s="318">
         <f>Erg.Fzg._1!$C$66</f>
@@ -20320,10 +20320,10 @@
     <row r="32" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="309"/>
       <c r="B32" s="310" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C32" s="311" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D32" s="312" t="e">
         <f>SUM(D30:D31)</f>
@@ -20349,7 +20349,7 @@
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="293" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C34" s="21"/>
       <c r="D34" s="21"/>
@@ -20480,7 +20480,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="118" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C1" s="118"/>
       <c r="D1" s="118"/>
@@ -20494,7 +20494,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C2" s="227"/>
       <c r="D2" s="230" t="str">
@@ -20522,7 +20522,7 @@
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="18"/>
       <c r="B4" s="154" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -20537,7 +20537,7 @@
     <row r="6" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18"/>
       <c r="B6" s="12" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C6" s="418" t="str">
         <f>IF(Projektname=0,"",Projektname)</f>
@@ -20619,7 +20619,7 @@
       <c r="B12" s="12"/>
       <c r="C12" s="76"/>
       <c r="E12" s="58" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F12" s="85">
         <f>Fahrleistung</f>
@@ -20659,7 +20659,7 @@
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="18"/>
       <c r="B15" s="293" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="21"/>
@@ -20671,7 +20671,7 @@
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="18"/>
       <c r="B16" s="37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" s="23"/>
       <c r="D16" s="24">
@@ -20720,10 +20720,10 @@
         <v>12</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D18" s="43">
         <f>Erg.Fzg._1!$C$57-D19</f>
@@ -20749,10 +20749,10 @@
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="416"/>
       <c r="B19" s="27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D19" s="43">
         <f>(Erg.Fzg._1!$C$35+Erg.Fzg._1!$C$36)*Haltedauer</f>
@@ -20778,10 +20778,10 @@
     <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="416"/>
       <c r="B20" s="27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D20" s="43">
         <f>Erg.Fzg._1!C41*Haltedauer</f>
@@ -20808,10 +20808,10 @@
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="416"/>
       <c r="B21" s="29" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C21" s="46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D21" s="47" t="e">
         <f>Erg.Fzg._1!$C$59</f>
@@ -20837,10 +20837,10 @@
     <row r="22" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="18"/>
       <c r="B22" s="49" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C22" s="50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D22" s="51" t="e">
         <f>IF(SUM(D18:D21)=0,"",SUM(D18:D21))</f>
@@ -20866,7 +20866,7 @@
     <row r="23" spans="1:9" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18"/>
       <c r="B23" s="75" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C23" s="50"/>
       <c r="D23" s="51" t="str">
@@ -20894,10 +20894,10 @@
     <row r="24" spans="1:9" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A24" s="18"/>
       <c r="B24" s="108" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C24" s="66" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D24" s="231">
         <f>IF(AND(COUNTIF(D18:D21,0)&gt;0,Antriebsart1="Plug-In-Hybrid (PHEV)"),1,IF(AND(COUNTIF(D18:D21,0)&gt;1,Antriebsart1="Verbrenner"),1,IF(AND(COUNTIF(D18:D21,0)&gt;2,Antriebsart1&lt;&gt;""),1,0)))</f>
@@ -20927,10 +20927,10 @@
     <row r="25" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="33"/>
       <c r="B25" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" s="31" t="s">
         <v>90</v>
-      </c>
-      <c r="C25" s="31" t="s">
-        <v>91</v>
       </c>
       <c r="D25" s="32" t="e">
         <f>Erg.Fzg._1!$C$65</f>
@@ -20956,10 +20956,10 @@
     <row r="26" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="33"/>
       <c r="B26" s="98" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C26" s="99" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D26" s="35">
         <f>Erg.Fzg._1!$C$66</f>
@@ -20986,10 +20986,10 @@
     <row r="27" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="33"/>
       <c r="B27" s="310" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C27" s="311" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D27" s="312" t="e">
         <f>SUM(D25:D26)</f>
@@ -21015,7 +21015,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B29" s="293" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C29" s="21"/>
       <c r="D29" s="21"/>
@@ -21152,7 +21152,7 @@
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="119"/>
       <c r="B2" s="189" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C2" s="119"/>
       <c r="D2" s="119"/>
@@ -21177,7 +21177,7 @@
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="119"/>
       <c r="B4" s="293" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C4" s="354"/>
       <c r="D4" s="354"/>
@@ -21187,7 +21187,7 @@
       <c r="H4" s="119"/>
     </row>
     <row r="5" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="383" t="s">
+      <c r="A5" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="219"/>
@@ -21198,30 +21198,30 @@
       <c r="G5" s="190"/>
       <c r="H5" s="119"/>
       <c r="J5" s="427" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="K5" s="427"/>
       <c r="L5" s="427"/>
     </row>
     <row r="6" spans="1:12" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A6" s="383"/>
+      <c r="A6" s="370"/>
       <c r="B6" s="220" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" s="220" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="221" t="s">
         <v>97</v>
       </c>
-      <c r="C6" s="220" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="221" t="s">
+      <c r="E6" s="226" t="s">
         <v>98</v>
       </c>
-      <c r="E6" s="226" t="s">
+      <c r="F6" s="221" t="s">
         <v>99</v>
       </c>
-      <c r="F6" s="221" t="s">
+      <c r="G6" s="306" t="s">
         <v>100</v>
-      </c>
-      <c r="G6" s="306" t="s">
-        <v>101</v>
       </c>
       <c r="H6" s="119"/>
       <c r="J6" s="427"/>
@@ -21231,17 +21231,17 @@
     <row r="7" spans="1:12" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="352"/>
       <c r="B7" s="428" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C7" s="222" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D7" s="223">
         <v>120</v>
       </c>
       <c r="E7" s="272"/>
       <c r="F7" s="222" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G7" s="307">
         <f t="shared" ref="G7:G17" si="0">IF(ISBLANK(E7),D7,E7)</f>
@@ -21256,14 +21256,14 @@
       <c r="A8" s="352"/>
       <c r="B8" s="429"/>
       <c r="C8" s="222" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D8" s="223">
         <v>130</v>
       </c>
       <c r="E8" s="272"/>
       <c r="F8" s="222" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G8" s="307">
         <f t="shared" si="0"/>
@@ -21278,14 +21278,14 @@
       <c r="A9" s="352"/>
       <c r="B9" s="430"/>
       <c r="C9" s="222" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D9" s="223">
         <v>20</v>
       </c>
       <c r="E9" s="272"/>
       <c r="F9" s="222" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G9" s="307">
         <f t="shared" si="0"/>
@@ -21299,17 +21299,17 @@
     <row r="10" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A10" s="352"/>
       <c r="B10" s="356" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" s="222" t="s">
         <v>105</v>
-      </c>
-      <c r="C10" s="222" t="s">
-        <v>106</v>
       </c>
       <c r="D10" s="367">
         <v>64</v>
       </c>
       <c r="E10" s="272"/>
       <c r="F10" s="222" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G10" s="307">
         <f t="shared" si="0"/>
@@ -21323,17 +21323,17 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="352"/>
       <c r="B11" s="356" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C11" s="222" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D11" s="367">
         <v>3.6</v>
       </c>
       <c r="E11" s="272"/>
       <c r="F11" s="222" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G11" s="307">
         <f t="shared" si="0"/>
@@ -21347,17 +21347,17 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="352"/>
       <c r="B12" s="428" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" s="222" t="s">
         <v>108</v>
-      </c>
-      <c r="C12" s="222" t="s">
-        <v>109</v>
       </c>
       <c r="D12" s="223">
         <v>19</v>
       </c>
       <c r="E12" s="272"/>
       <c r="F12" s="222" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G12" s="307">
         <f t="shared" si="0"/>
@@ -21372,14 +21372,14 @@
       <c r="A13" s="352"/>
       <c r="B13" s="429"/>
       <c r="C13" s="222" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D13" s="223">
         <v>21</v>
       </c>
       <c r="E13" s="272"/>
       <c r="F13" s="222" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G13" s="307">
         <f>IF(ISBLANK(E13),D13,E13)</f>
@@ -21396,14 +21396,14 @@
       </c>
       <c r="B14" s="429"/>
       <c r="C14" s="222" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D14" s="223" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E14" s="272"/>
       <c r="F14" s="222" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G14" s="307" t="str">
         <f>IF(ISBLANK(E14),"keine",E14)</f>
@@ -21418,14 +21418,14 @@
       <c r="A15" s="416"/>
       <c r="B15" s="429"/>
       <c r="C15" s="222" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D15" s="223" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E15" s="272"/>
       <c r="F15" s="222" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G15" s="307" t="str">
         <f t="shared" ref="G15" si="1">IF(ISBLANK(E15),"keine",E15)</f>
@@ -21440,14 +21440,14 @@
       <c r="A16" s="416"/>
       <c r="B16" s="430"/>
       <c r="C16" s="222" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D16" s="223" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E16" s="272"/>
       <c r="F16" s="222" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G16" s="307" t="str">
         <f>IF(ISBLANK(E16),"keine",E16)</f>
@@ -21461,17 +21461,17 @@
     <row r="17" spans="1:12" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A17" s="353"/>
       <c r="B17" s="357" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C17" s="225" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D17" s="224">
         <v>60</v>
       </c>
       <c r="E17" s="273"/>
       <c r="F17" s="225" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G17" s="307">
         <f t="shared" si="0"/>
@@ -21505,11 +21505,11 @@
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="193"/>
       <c r="B21" s="192" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C21" s="192"/>
       <c r="D21" s="193" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E21" s="193"/>
       <c r="F21" s="193"/>
@@ -21531,7 +21531,7 @@
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="196"/>
       <c r="B23" s="293" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C23" s="339"/>
       <c r="D23" s="340"/>
@@ -21555,15 +21555,15 @@
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="196"/>
       <c r="B25" s="346" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C25" s="327"/>
       <c r="D25" s="296" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E25" s="347"/>
       <c r="F25" s="295" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G25" s="194"/>
       <c r="H25" s="195"/>
@@ -21575,23 +21575,23 @@
       <c r="C26" s="327"/>
       <c r="D26" s="209"/>
       <c r="E26" s="210" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F26" s="294"/>
       <c r="G26" s="308" t="s">
+        <v>115</v>
+      </c>
+      <c r="H26" s="198" t="s">
         <v>116</v>
       </c>
-      <c r="H26" s="198" t="s">
+      <c r="I26" s="255" t="s">
         <v>117</v>
-      </c>
-      <c r="I26" s="255" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="204"/>
       <c r="B27" s="212" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C27" s="213"/>
       <c r="D27" s="214">
@@ -21599,21 +21599,21 @@
       </c>
       <c r="E27" s="243"/>
       <c r="F27" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G27" s="308">
         <f>IF(ISNUMBER(E27),E27,D27)/100</f>
         <v>0.41399999999999998</v>
       </c>
       <c r="H27" s="199" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="I27" s="254"/>
     </row>
     <row r="28" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="204"/>
       <c r="B28" s="215" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C28" s="211"/>
       <c r="D28" s="214">
@@ -21621,21 +21621,21 @@
       </c>
       <c r="E28" s="243"/>
       <c r="F28" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G28" s="308">
         <f>IF(ISNUMBER(E28),E28,D28)/100</f>
         <v>0.59</v>
       </c>
       <c r="H28" s="199" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="I28" s="254"/>
     </row>
     <row r="29" spans="1:12" ht="14.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="205"/>
       <c r="B29" s="216" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C29" s="348"/>
       <c r="D29" s="349"/>
@@ -21651,7 +21651,7 @@
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="433"/>
       <c r="B30" s="212" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C30" s="213"/>
       <c r="D30" s="271">
@@ -21659,21 +21659,21 @@
       </c>
       <c r="E30" s="243"/>
       <c r="F30" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G30" s="308">
         <f t="shared" ref="G30:G32" si="2">IF(ISNUMBER(E30),E30,D30)</f>
         <v>1.6719999999999999</v>
       </c>
       <c r="H30" s="199" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I30" s="254"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="433"/>
       <c r="B31" s="212" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C31" s="213"/>
       <c r="D31" s="271">
@@ -21681,21 +21681,21 @@
       </c>
       <c r="E31" s="243"/>
       <c r="F31" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G31" s="308">
         <f t="shared" si="2"/>
         <v>1.788</v>
       </c>
       <c r="H31" s="199" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I31" s="254"/>
     </row>
     <row r="32" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A32" s="205"/>
       <c r="B32" s="212" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C32" s="213"/>
       <c r="D32" s="217">
@@ -21703,14 +21703,14 @@
       </c>
       <c r="E32" s="243"/>
       <c r="F32" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G32" s="308">
         <f t="shared" si="2"/>
         <v>1.3</v>
       </c>
       <c r="H32" s="199" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I32" s="254"/>
     </row>
@@ -21739,7 +21739,7 @@
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="193"/>
       <c r="B35" s="293" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C35" s="339"/>
       <c r="D35" s="340"/>
@@ -21752,14 +21752,14 @@
     <row r="36" spans="1:9" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="193"/>
       <c r="B36" s="434" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C36" s="435"/>
       <c r="D36" s="435"/>
       <c r="E36" s="435"/>
       <c r="F36" s="436"/>
       <c r="G36" s="308" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H36" s="202"/>
       <c r="I36" s="202"/>
@@ -21770,10 +21770,10 @@
       <c r="C37" s="327"/>
       <c r="D37" s="327"/>
       <c r="E37" s="342" t="s">
+        <v>98</v>
+      </c>
+      <c r="F37" s="343" t="s">
         <v>99</v>
-      </c>
-      <c r="F37" s="343" t="s">
-        <v>100</v>
       </c>
       <c r="G37" s="308"/>
       <c r="H37" s="195"/>
@@ -21782,7 +21782,7 @@
     <row r="38" spans="1:9" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A38" s="207"/>
       <c r="B38" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C38" s="327"/>
       <c r="D38" s="218">
@@ -21798,7 +21798,7 @@
         <v>860</v>
       </c>
       <c r="H38" s="199" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I38" s="254"/>
     </row>
@@ -21816,7 +21816,7 @@
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="193"/>
       <c r="B40" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C40" s="327"/>
       <c r="D40" s="218">
@@ -21824,21 +21824,21 @@
       </c>
       <c r="E40" s="243"/>
       <c r="F40" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G40" s="308">
         <f>IF(ISNUMBER(E40),E40,D40)</f>
         <v>0.02</v>
       </c>
       <c r="H40" s="199" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I40" s="254"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="193"/>
       <c r="B41" s="215" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C41" s="72"/>
       <c r="D41" s="218">
@@ -21846,14 +21846,14 @@
       </c>
       <c r="E41" s="243"/>
       <c r="F41" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G41" s="308">
         <f>IF(ISNUMBER(E41),E41,D41)</f>
         <v>0.15</v>
       </c>
       <c r="H41" s="199" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I41" s="254"/>
     </row>
@@ -21882,7 +21882,7 @@
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="193"/>
       <c r="B44" s="293" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C44" s="340"/>
       <c r="D44" s="340"/>
@@ -21895,7 +21895,7 @@
     <row r="45" spans="1:9" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A45" s="193"/>
       <c r="B45" s="431" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C45" s="432"/>
       <c r="D45" s="218">
@@ -21903,21 +21903,21 @@
       </c>
       <c r="E45" s="243"/>
       <c r="F45" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G45" s="308">
         <f>IF(ISNUMBER(E45),E45,D45)</f>
         <v>84</v>
       </c>
       <c r="H45" s="199" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I45" s="254"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="193"/>
       <c r="B46" s="246" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C46" s="247"/>
       <c r="D46" s="247"/>
@@ -22032,7 +22032,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>21</v>
@@ -22045,7 +22045,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C4" s="89"/>
       <c r="D4" s="89"/>
@@ -22059,7 +22059,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" s="54">
         <v>1</v>
@@ -22071,7 +22071,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C7" s="102" t="str">
         <f>IF(Anbieter1=0,"",Anbieter1)</f>
@@ -22091,14 +22091,14 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C9" s="102"/>
       <c r="F9" s="125"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C10" s="102" t="str">
         <f>IF(Hersteller1=0,"",Hersteller1)</f>
@@ -22109,7 +22109,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C11" s="102" t="str">
         <f>IF(Modell1=0,"",Modell1)</f>
@@ -22120,7 +22120,7 @@
     </row>
     <row r="12" spans="1:7" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="56" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C12" s="102" t="str">
         <f>IF(Zusatzinfo1=0,"",Zusatzinfo1)</f>
@@ -22131,7 +22131,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" s="57" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C13" s="102" t="str">
         <f>IF(Antriebsart1=0,"",Antriebsart1)</f>
@@ -22142,7 +22142,7 @@
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="107"/>
       <c r="B14" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C14" s="102" t="str">
         <f>IF(Energie1=0,"",Energie1)</f>
@@ -22159,7 +22159,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B16" s="154" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -22173,7 +22173,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B18" s="72" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C18" s="288">
         <f>0.0057*(ReichwPHEV1/23)^3-0.0838*(ReichwPHEV1/23)^2+0.4261*(ReichwPHEV1/23)+ 0.1633</f>
@@ -22184,33 +22184,33 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C19" s="289">
         <f>Verbrauch1/(1-0.9*C18)</f>
         <v>0</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F19" s="125"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C20" s="290">
         <f>VerbEl_WLTP1/C18</f>
         <v>0</v>
       </c>
       <c r="D20" s="184" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F20" s="125"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" s="186" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C21" s="291">
         <f>0.0021*(ReichwPHEV1/23)^3-0.0358*(ReichwPHEV1/23)^2+0.2607*(ReichwPHEV1/23)- 0.0267</f>
@@ -22224,14 +22224,14 @@
         <v>12</v>
       </c>
       <c r="B22" s="439" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C22" s="292">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
       <c r="D22" s="185" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F22" s="125"/>
     </row>
@@ -22243,7 +22243,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="183" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F23" s="125"/>
     </row>
@@ -22254,7 +22254,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B25" s="154" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C25" s="89"/>
       <c r="D25" s="89"/>
@@ -22265,7 +22265,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C27" s="61"/>
       <c r="D27" s="60"/>
@@ -22273,39 +22273,39 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C28" s="279">
         <f>IF(Antriebsart1="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie1,EnKostList,6,FALSE),0)*IF(Antriebsart1="Plug-In-Hybrid (PHEV)",VerbPHEV1,Verbrauch1)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F28" s="125"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C29" s="279">
         <f>IF(Antriebsart1="Verbrenner",0,VLOOKUP("Strom",EnKostList,6,FALSE)*IF(Antriebsart1="Plug-In-Hybrid (PHEV)",VerbElPHEV1,VerbEl_WLTP1)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C30" s="280">
         <f>SUM(C28:C29)</f>
         <v>0</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="14.4" thickTop="1" x14ac:dyDescent="0.25">
@@ -22314,7 +22314,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C32" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie1)</f>
@@ -22325,63 +22325,63 @@
     </row>
     <row r="33" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B33" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C33" s="279">
         <f>IF(Antriebsart1="Plug-In-Hybrid (PHEV)",VerbPHEV1*VLOOKUP(Energie1,CO2List,2,FALSE)/100,CO2_1)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F33" s="107"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C34" s="279">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C35" s="279">
         <f>IF(Energie1="Strom",0,NOX_1*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C36" s="279">
         <f>IF(Energie1="Strom",0,Partikel1*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C37" s="280">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
       <c r="D37" s="64" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="14.4" thickTop="1" x14ac:dyDescent="0.25">
@@ -22389,7 +22389,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B39" s="60" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C39" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie1,IF(Antriebsart1="Plug-In-Hybrid (PHEV)","+Strom",""))</f>
@@ -22399,32 +22399,32 @@
     </row>
     <row r="40" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C40" s="279">
         <f>IFERROR(IF(Antriebsart1="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP1/100*Fahrleistung/1000000,IF(Antriebsart1="Verbrenner",VLOOKUP(Energie1,CO2List,3,FALSE)*Verbrauch1/100*Fahrleistung/1000000,VLOOKUP(Energie1,CO2List,3,FALSE)*VerbPHEV1/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV1/100*Fahrleistung/1000000)),0)</f>
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F40" s="107"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C41" s="279">
         <f>C40*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B43" s="154" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C43" s="89"/>
       <c r="D43" s="89"/>
@@ -22438,53 +22438,53 @@
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="107"/>
       <c r="B45" s="90" t="s">
+        <v>155</v>
+      </c>
+      <c r="C45" s="134" t="s">
         <v>156</v>
       </c>
-      <c r="C45" s="134" t="s">
-        <v>157</v>
-      </c>
       <c r="D45" s="62"/>
     </row>
     <row r="46" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="383" t="s">
+      <c r="A46" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="437" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C46" s="281">
         <f>IF(OR(Antriebsart1="Vollelektrisch (BEV)",Antriebsart1="Plug-In-Hybrid (PHEV)"),Batterie1*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
       <c r="D46" s="131" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E46" s="127"/>
       <c r="F46" s="107"/>
     </row>
     <row r="47" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="383"/>
+      <c r="A47" s="370"/>
       <c r="B47" s="438"/>
       <c r="C47" s="281" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D47" s="130" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E47" s="127"/>
       <c r="F47" s="107"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C48" s="279" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -22503,19 +22503,19 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B54" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C54" s="282">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis1,0),Gesamtpreis1*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl1,0))</f>
         <v>0</v>
       </c>
       <c r="D54" s="68" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F54" s="58"/>
     </row>
@@ -22524,71 +22524,71 @@
         <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis1-Gesamtpreis1*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>0</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F55" s="58"/>
     </row>
     <row r="56" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C56" s="283">
         <f>C30*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F56" s="58"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C57" s="283">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F57" s="58"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C58" s="283">
         <f>C41*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B59" s="329" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C59" s="330" t="e">
         <f>C48*Haltedauer</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D59" s="329" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="383" t="s">
+      <c r="A60" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -22606,7 +22606,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="383"/>
+      <c r="A61" s="370"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -22622,7 +22622,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="383"/>
+      <c r="A62" s="370"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -22639,14 +22639,14 @@
     </row>
     <row r="63" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C63" s="284" t="e">
         <f>SUM(C54:C62)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D63" s="64" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F63" s="58"/>
     </row>
@@ -22655,26 +22655,26 @@
     </row>
     <row r="65" spans="2:4" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B65" s="68" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C65" s="285" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D65" s="68" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="66" spans="2:4" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B66" s="72" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C66" s="286">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D66" s="72" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -22724,7 +22724,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>21</v>
@@ -22737,7 +22737,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -22753,7 +22753,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" s="54">
         <v>2</v>
@@ -22766,7 +22766,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C7" s="102" t="str">
         <f>IF(Anbieter2=0,"",Anbieter2)</f>
@@ -22788,7 +22788,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C9" s="102"/>
       <c r="E9" s="125"/>
@@ -22796,7 +22796,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C10" s="102" t="str">
         <f>IF(Hersteller2=0,"",Hersteller2)</f>
@@ -22808,7 +22808,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C11" s="102" t="str">
         <f>IF(Modell2=0,"",Modell2)</f>
@@ -22820,7 +22820,7 @@
     </row>
     <row r="12" spans="1:6" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="56" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C12" s="102" t="str">
         <f>IF(Zusatzinfo2=0,"",Zusatzinfo2)</f>
@@ -22832,7 +22832,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B13" s="57" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C13" s="102" t="str">
         <f>IF(Antriebsart2=0,"",Antriebsart2)</f>
@@ -22843,7 +22843,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C14" s="102" t="str">
         <f>IF(Energie2=0,"",Energie2)</f>
@@ -22859,7 +22859,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B16" s="154" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -22875,7 +22875,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B18" s="72" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C18" s="288">
         <f>0.0057*(ReichwPHEV2/23)^3-0.0838*(ReichwPHEV2/23)^2+0.4261*(ReichwPHEV2/23)+ 0.1633</f>
@@ -22887,35 +22887,35 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C19" s="289">
         <f>Verbrauch2/(1-0.9*C18)</f>
         <v>0</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E19" s="125"/>
       <c r="F19" s="125"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C20" s="290">
         <f>VerbEl_WLTP2/C18</f>
         <v>0</v>
       </c>
       <c r="D20" s="184" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E20" s="125"/>
       <c r="F20" s="125"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" s="186" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C21" s="291">
         <f>0.0021*(ReichwPHEV2/23)^3-0.0358*(ReichwPHEV2/23)^2+0.2607*(ReichwPHEV2/23)- 0.0267</f>
@@ -22930,14 +22930,14 @@
         <v>12</v>
       </c>
       <c r="B22" s="439" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C22" s="292">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
       <c r="D22" s="185" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E22" s="125"/>
       <c r="F22" s="125"/>
@@ -22950,7 +22950,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="183" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E23" s="125"/>
       <c r="F23" s="125"/>
@@ -22962,7 +22962,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B25" s="154" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -22975,7 +22975,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C27" s="61"/>
       <c r="D27" s="60"/>
@@ -22984,42 +22984,42 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C28" s="279">
         <f>IF(Antriebsart2="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie2,EnKostList,6,FALSE),0)*IF(Antriebsart2="Plug-In-Hybrid (PHEV)",VerbPHEV2,Verbrauch2)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E28" s="125"/>
       <c r="F28" s="125"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C29" s="279">
         <f>IF(Antriebsart2="Verbrenner",0,VLOOKUP("Strom",EnKostList,6,FALSE)*IF(Antriebsart2="Plug-In-Hybrid (PHEV)",VerbElPHEV2,VerbEl_WLTP2)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E29" s="125"/>
       <c r="F29" s="125"/>
     </row>
     <row r="30" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C30" s="280">
         <f>SUM(C28:C29)</f>
         <v>0</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E30" s="125"/>
       <c r="F30" s="125"/>
@@ -23032,7 +23032,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C32" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie2)</f>
@@ -23044,70 +23044,70 @@
     </row>
     <row r="33" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B33" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C33" s="279">
         <f>IF(Antriebsart2="Plug-In-Hybrid (PHEV)",VerbPHEV2*VLOOKUP(Energie2,CO2List,2,FALSE)/100,CO2_2)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E33" s="125"/>
       <c r="F33" s="125"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C34" s="279">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E34" s="125"/>
       <c r="F34" s="125"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C35" s="287">
         <f>IF(Energie2="Strom",0,NOX_2*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
       <c r="D35" s="65" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E35" s="125"/>
       <c r="F35" s="125"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B36" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C36" s="287">
         <f>IF(Energie2="Strom",0,Partikel2*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
       <c r="D36" s="65" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E36" s="125"/>
       <c r="F36" s="125"/>
     </row>
     <row r="37" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C37" s="280">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
       <c r="D37" s="64" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E37" s="125"/>
       <c r="F37" s="125"/>
@@ -23120,7 +23120,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B39" s="60" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C39" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie2,IF(Antriebsart2="Plug-In-Hybrid (PHEV)","+Strom",""))</f>
@@ -23132,28 +23132,28 @@
     </row>
     <row r="40" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C40" s="279">
         <f>IFERROR(IF(Antriebsart2="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP2/100*Fahrleistung/1000000,IF(Antriebsart2="Verbrenner",VLOOKUP(Energie2,CO2List,3,FALSE)*Verbrauch2/100*Fahrleistung/1000000,VLOOKUP(Energie2,CO2List,3,FALSE)*VerbPHEV2/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV2/100*Fahrleistung/1000000)),0)</f>
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E40" s="125"/>
       <c r="F40" s="125"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C41" s="279">
         <f>C40*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E41" s="125"/>
       <c r="F41" s="125"/>
@@ -23164,7 +23164,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B43" s="154" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -23181,55 +23181,55 @@
     <row r="45" spans="1:6" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="107"/>
       <c r="B45" s="90" t="s">
+        <v>155</v>
+      </c>
+      <c r="C45" s="134" t="s">
         <v>156</v>
-      </c>
-      <c r="C45" s="134" t="s">
-        <v>157</v>
       </c>
       <c r="D45" s="62"/>
       <c r="E45" s="125"/>
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="383" t="s">
+      <c r="A46" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="437" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C46" s="281">
         <f>IF(OR(Antriebsart2="Vollelektrisch (BEV)",Antriebsart2="Plug-In-Hybrid (PHEV)"),Batterie2*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
       <c r="D46" s="131" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E46" s="127"/>
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="383"/>
+      <c r="A47" s="370"/>
       <c r="B47" s="438"/>
       <c r="C47" s="281" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D47" s="130" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E47" s="127"/>
       <c r="F47" s="125"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C48" s="279" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E48" s="125"/>
       <c r="F48" s="125"/>
@@ -23253,20 +23253,20 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="70" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C54" s="282">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis2,0),Gesamtpreis2*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl2,0))</f>
         <v>0</v>
       </c>
       <c r="D54" s="68" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E54" s="69"/>
       <c r="F54" s="58"/>
@@ -23276,72 +23276,72 @@
         <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis2-Gesamtpreis2*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>0</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E55" s="125"/>
       <c r="F55" s="73"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C56" s="283">
         <f>C30*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F56" s="73"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C57" s="283">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F57" s="58"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C58" s="283">
         <f>C41*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B59" s="329" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C59" s="330" t="e">
         <f>C48*Haltedauer</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D59" s="329" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="383" t="s">
+      <c r="A60" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -23359,7 +23359,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="383"/>
+      <c r="A61" s="370"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -23375,7 +23375,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="383"/>
+      <c r="A62" s="370"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -23392,14 +23392,14 @@
     </row>
     <row r="63" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C63" s="284" t="e">
         <f>SUM(C54:C62)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D63" s="64" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E63" s="14"/>
       <c r="F63" s="58"/>
@@ -23414,26 +23414,26 @@
     </row>
     <row r="65" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B65" s="68" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C65" s="285" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D65" s="68" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="66" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B66" s="72" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C66" s="286">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D66" s="72" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E66" s="71"/>
     </row>
@@ -23484,7 +23484,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>21</v>
@@ -23497,7 +23497,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -23513,7 +23513,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" s="54">
         <v>3</v>
@@ -23526,7 +23526,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C7" s="102" t="str">
         <f>IF(Anbieter3=0,"",Anbieter3)</f>
@@ -23548,7 +23548,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C9" s="102"/>
       <c r="E9" s="125"/>
@@ -23556,7 +23556,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C10" s="102" t="str">
         <f>IF(Hersteller3=0,"",Hersteller3)</f>
@@ -23568,7 +23568,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C11" s="102" t="str">
         <f>IF(Modell3=0,"",Modell3)</f>
@@ -23580,7 +23580,7 @@
     </row>
     <row r="12" spans="1:6" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="56" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C12" s="102" t="str">
         <f>IF(Zusatzinfo3=0,"",Zusatzinfo3)</f>
@@ -23592,7 +23592,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B13" s="57" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C13" s="102" t="str">
         <f>IF(Antriebsart3=0,"",Antriebsart3)</f>
@@ -23603,7 +23603,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C14" s="102" t="str">
         <f>IF(Energie3=0,"",Energie3)</f>
@@ -23619,7 +23619,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B16" s="154" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -23635,7 +23635,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B18" s="72" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C18" s="288">
         <f>0.0057*(ReichwPHEV3/23)^3-0.0838*(ReichwPHEV3/23)^2+0.4261*(ReichwPHEV3/23)+ 0.1633</f>
@@ -23647,35 +23647,35 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C19" s="289">
         <f>Verbrauch3/(1-0.9*C18)</f>
         <v>0</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E19" s="125"/>
       <c r="F19" s="125"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C20" s="290">
         <f>VerbEl_WLTP3/C18</f>
         <v>0</v>
       </c>
       <c r="D20" s="184" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E20" s="125"/>
       <c r="F20" s="125"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" s="186" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C21" s="291">
         <f>0.0021*(ReichwPHEV3/23)^3-0.0358*(ReichwPHEV3/23)^2+0.2607*(ReichwPHEV3/23)- 0.0267</f>
@@ -23690,14 +23690,14 @@
         <v>12</v>
       </c>
       <c r="B22" s="439" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C22" s="292">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
       <c r="D22" s="185" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E22" s="125"/>
       <c r="F22" s="125"/>
@@ -23710,7 +23710,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="183" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E23" s="125"/>
       <c r="F23" s="125"/>
@@ -23722,7 +23722,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B25" s="154" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -23735,7 +23735,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C27" s="61"/>
       <c r="D27" s="60"/>
@@ -23744,42 +23744,42 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C28" s="279">
         <f>IF(Antriebsart3="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie3,EnKostList,6,FALSE),0)*IF(Antriebsart3="Plug-In-Hybrid (PHEV)",VerbPHEV3,Verbrauch3)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E28" s="125"/>
       <c r="F28" s="125"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C29" s="279">
         <f>IF(Antriebsart3="Verbrenner",0,VLOOKUP("Strom",EnKostList,6,FALSE)*IF(Antriebsart3="Plug-In-Hybrid (PHEV)",VerbElPHEV3,VerbEl_WLTP3)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E29" s="125"/>
       <c r="F29" s="125"/>
     </row>
     <row r="30" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C30" s="280">
         <f>SUM(C28:C29)</f>
         <v>0</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E30" s="125"/>
       <c r="F30" s="125"/>
@@ -23792,7 +23792,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C32" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie3)</f>
@@ -23804,70 +23804,70 @@
     </row>
     <row r="33" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B33" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C33" s="279">
         <f>IF(Antriebsart3="Plug-In-Hybrid (PHEV)",VerbPHEV3*VLOOKUP(Energie3,CO2List,2,FALSE)/100,CO2_3)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E33" s="125"/>
       <c r="F33" s="125"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C34" s="279">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E34" s="125"/>
       <c r="F34" s="125"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C35" s="287">
         <f>IF(Energie3="Strom",0,NOX_3*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
       <c r="D35" s="65" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E35" s="125"/>
       <c r="F35" s="125"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B36" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C36" s="287">
         <f>IF(Energie3="Strom",0,Partikel3*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
       <c r="D36" s="65" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E36" s="125"/>
       <c r="F36" s="125"/>
     </row>
     <row r="37" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C37" s="280">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
       <c r="D37" s="64" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E37" s="125"/>
       <c r="F37" s="125"/>
@@ -23880,7 +23880,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B39" s="60" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C39" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie3,IF(Antriebsart3="Plug-In-Hybrid (PHEV)","+Strom",""))</f>
@@ -23892,28 +23892,28 @@
     </row>
     <row r="40" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C40" s="279">
         <f>IFERROR(IF(Antriebsart3="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP3/100*Fahrleistung/1000000,IF(Antriebsart3="Verbrenner",VLOOKUP(Energie3,CO2List,3,FALSE)*Verbrauch3/100*Fahrleistung/1000000,VLOOKUP(Energie3,CO2List,3,FALSE)*VerbPHEV3/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV3/100*Fahrleistung/1000000)),0)</f>
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E40" s="125"/>
       <c r="F40" s="125"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C41" s="279">
         <f>C40*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E41" s="125"/>
       <c r="F41" s="125"/>
@@ -23924,7 +23924,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B43" s="154" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -23941,55 +23941,55 @@
     <row r="45" spans="1:6" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="107"/>
       <c r="B45" s="90" t="s">
+        <v>155</v>
+      </c>
+      <c r="C45" s="134" t="s">
         <v>156</v>
-      </c>
-      <c r="C45" s="134" t="s">
-        <v>157</v>
       </c>
       <c r="D45" s="62"/>
       <c r="E45" s="125"/>
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="383" t="s">
+      <c r="A46" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="437" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C46" s="281">
         <f>IF(OR(Antriebsart3="Vollelektrisch (BEV)",Antriebsart3="Plug-In-Hybrid (PHEV)"),Batterie3*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
       <c r="D46" s="131" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E46" s="127"/>
       <c r="F46" s="133"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="383"/>
+      <c r="A47" s="370"/>
       <c r="B47" s="438"/>
       <c r="C47" s="281" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D47" s="130" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E47" s="127"/>
       <c r="F47" s="133"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C48" s="279" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E48" s="125"/>
       <c r="F48" s="125"/>
@@ -24013,20 +24013,20 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="70" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C54" s="282">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis3,0),Gesamtpreis3*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl3,0))</f>
         <v>0</v>
       </c>
       <c r="D54" s="68" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E54" s="69"/>
       <c r="F54" s="58"/>
@@ -24036,72 +24036,72 @@
         <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis3-Gesamtpreis3*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>0</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E55" s="125"/>
       <c r="F55" s="73"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C56" s="283">
         <f>C30*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F56" s="73"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C57" s="283">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F57" s="58"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C58" s="283">
         <f>C41*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B59" s="327" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C59" s="328" t="e">
         <f>C48*Haltedauer</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D59" s="327" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="383" t="s">
+      <c r="A60" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -24119,7 +24119,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="383"/>
+      <c r="A61" s="370"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -24135,7 +24135,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="383"/>
+      <c r="A62" s="370"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -24152,14 +24152,14 @@
     </row>
     <row r="63" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C63" s="284" t="e">
         <f>SUM(C54:C62)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D63" s="64" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E63" s="14"/>
       <c r="F63" s="58"/>
@@ -24174,26 +24174,26 @@
     </row>
     <row r="65" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B65" s="68" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C65" s="285" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D65" s="68" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="66" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B66" s="72" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C66" s="286">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D66" s="72" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E66" s="71"/>
     </row>
@@ -24451,6 +24451,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" xsi:nil="true"/>
@@ -24459,15 +24468,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -24490,26 +24490,26 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92A2CDCF-36F6-4C30-8F9B-D45880CB8E7E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{651615EB-DE44-4BF4-BD1E-846AB7A3DA36}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92A2CDCF-36F6-4C30-8F9B-D45880CB8E7E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/src/assets/downloads/LZK-Rechner_Pkw_V1.3.xlsx
+++ b/src/assets/downloads/LZK-Rechner_Pkw_V1.3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifeu2.sharepoint.com/sites/DBUBeschaffungBerlin/Freigegebene Dokumente/General/Folgeprojekt/03_Arbeitsdokumente/A4 - Aktualisierung der Instrumente aus Basisprojekt/LZK-Rechner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1224" documentId="13_ncr:1_{3372B5DA-C386-4B74-B09A-B44627B6D7C7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{15FA5D02-E4AC-479E-94D4-7CA04E4DDCD5}"/>
+  <xr:revisionPtr revIDLastSave="1228" documentId="13_ncr:1_{3372B5DA-C386-4B74-B09A-B44627B6D7C7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{C38B4280-322E-4CBE-9F67-5B06B03D8F7D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="887" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2657,49 +2657,6 @@
     <t>Gesellschaftliche Kosten von Umweltbelastungen - Klimakosten von Treibhausgas-Emissionen (02.07.2024)</t>
   </si>
   <si>
-    <r>
-      <t>Der Excel-Rechner ist</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> ohne Passwort</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> geschützt. Der Blattschutz kann unter "Überprüfen -&gt; Blattschutz aufheben" aufgehoben werden.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Das Tool kann grundsätzlich nach eigenen Bedürfnissen über die vorgesehenen Anpassungsmöglichkeiten hinaus angepasst werden. 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Es ist jedoch zu berücksichtigen, dass dadurch Berechnungsfehler entstehen können.</t>
-    </r>
-  </si>
-  <si>
     <t>Angaben zu den Energiekosten</t>
   </si>
   <si>
@@ -3295,6 +3252,49 @@
   </si>
   <si>
     <t>Ladeverhalten Elektrofahrzeug</t>
+  </si>
+  <si>
+    <r>
+      <t>Der Excel-Rechner ist</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ohne Passwort</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> geschützt. Der Blattschutz kann unter "Überprüfen -&gt; Blattschutz aufheben" aufgehoben werden.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Das Tool kann grundsätzlich nach eigenen Bedürfnissen über die vorgesehenen Anpassungsmöglichkeiten hinaus angepasst werden. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Es ist jedoch zu berücksichtigen, dass dadurch Berechnungsfehler entstehen können. Die Verantwortung liegt bei der Person, die den Rechner angepasst hat.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -5497,49 +5497,49 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="20" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="20" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -13970,7 +13970,7 @@
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
       <c r="J2" s="268" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
@@ -13992,17 +13992,17 @@
       <c r="J4" s="115"/>
     </row>
     <row r="5" spans="2:10" ht="149.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="373" t="s">
-        <v>468</v>
-      </c>
-      <c r="C5" s="373"/>
-      <c r="D5" s="373"/>
-      <c r="E5" s="373"/>
-      <c r="F5" s="373"/>
-      <c r="G5" s="373"/>
-      <c r="H5" s="373"/>
-      <c r="I5" s="373"/>
-      <c r="J5" s="373"/>
+      <c r="B5" s="370" t="s">
+        <v>467</v>
+      </c>
+      <c r="C5" s="370"/>
+      <c r="D5" s="370"/>
+      <c r="E5" s="370"/>
+      <c r="F5" s="370"/>
+      <c r="G5" s="370"/>
+      <c r="H5" s="370"/>
+      <c r="I5" s="370"/>
+      <c r="J5" s="370"/>
     </row>
     <row r="6" spans="2:10" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="245"/>
@@ -14040,13 +14040,13 @@
     <row r="9" spans="2:10" ht="52.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D9" s="245"/>
       <c r="E9" s="245"/>
-      <c r="F9" s="374" t="s">
-        <v>426</v>
-      </c>
-      <c r="G9" s="374"/>
-      <c r="H9" s="374"/>
-      <c r="I9" s="374"/>
-      <c r="J9" s="374"/>
+      <c r="F9" s="371" t="s">
+        <v>425</v>
+      </c>
+      <c r="G9" s="371"/>
+      <c r="H9" s="371"/>
+      <c r="I9" s="371"/>
+      <c r="J9" s="371"/>
     </row>
     <row r="10" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" s="245"/>
@@ -14060,31 +14060,31 @@
     <row r="11" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="245"/>
       <c r="E11" s="245"/>
-      <c r="F11" s="375" t="s">
-        <v>441</v>
-      </c>
-      <c r="G11" s="376"/>
-      <c r="H11" s="376"/>
-      <c r="I11" s="376"/>
-      <c r="J11" s="376"/>
+      <c r="F11" s="372" t="s">
+        <v>440</v>
+      </c>
+      <c r="G11" s="373"/>
+      <c r="H11" s="373"/>
+      <c r="I11" s="373"/>
+      <c r="J11" s="373"/>
     </row>
     <row r="12" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D12" s="245"/>
       <c r="E12" s="245"/>
-      <c r="F12" s="376"/>
-      <c r="G12" s="376"/>
-      <c r="H12" s="376"/>
-      <c r="I12" s="376"/>
-      <c r="J12" s="376"/>
+      <c r="F12" s="373"/>
+      <c r="G12" s="373"/>
+      <c r="H12" s="373"/>
+      <c r="I12" s="373"/>
+      <c r="J12" s="373"/>
     </row>
     <row r="13" spans="2:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D13" s="245"/>
       <c r="E13" s="245"/>
-      <c r="F13" s="376"/>
-      <c r="G13" s="376"/>
-      <c r="H13" s="376"/>
-      <c r="I13" s="376"/>
-      <c r="J13" s="376"/>
+      <c r="F13" s="373"/>
+      <c r="G13" s="373"/>
+      <c r="H13" s="373"/>
+      <c r="I13" s="373"/>
+      <c r="J13" s="373"/>
     </row>
     <row r="14" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D14" s="245"/>
@@ -14098,22 +14098,22 @@
     <row r="15" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="245"/>
       <c r="E15" s="245"/>
-      <c r="F15" s="377" t="s">
+      <c r="F15" s="374" t="s">
         <v>2</v>
       </c>
-      <c r="G15" s="378"/>
-      <c r="H15" s="378"/>
-      <c r="I15" s="378"/>
-      <c r="J15" s="378"/>
+      <c r="G15" s="375"/>
+      <c r="H15" s="375"/>
+      <c r="I15" s="375"/>
+      <c r="J15" s="375"/>
     </row>
     <row r="16" spans="2:10" ht="73.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D16" s="245"/>
       <c r="E16" s="245"/>
-      <c r="F16" s="378"/>
-      <c r="G16" s="378"/>
-      <c r="H16" s="378"/>
-      <c r="I16" s="378"/>
-      <c r="J16" s="378"/>
+      <c r="F16" s="375"/>
+      <c r="G16" s="375"/>
+      <c r="H16" s="375"/>
+      <c r="I16" s="375"/>
+      <c r="J16" s="375"/>
     </row>
     <row r="17" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D17" s="245"/>
@@ -14127,13 +14127,13 @@
     <row r="18" spans="2:10" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D18" s="245"/>
       <c r="E18" s="245"/>
-      <c r="F18" s="379" t="s">
+      <c r="F18" s="376" t="s">
         <v>3</v>
       </c>
-      <c r="G18" s="380"/>
-      <c r="H18" s="380"/>
-      <c r="I18" s="380"/>
-      <c r="J18" s="380"/>
+      <c r="G18" s="377"/>
+      <c r="H18" s="377"/>
+      <c r="I18" s="377"/>
+      <c r="J18" s="377"/>
     </row>
     <row r="19" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="245"/>
@@ -14147,31 +14147,31 @@
     <row r="20" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="245"/>
       <c r="E20" s="245"/>
-      <c r="F20" s="381" t="s">
+      <c r="F20" s="378" t="s">
         <v>4</v>
       </c>
-      <c r="G20" s="381"/>
-      <c r="H20" s="381"/>
-      <c r="I20" s="381"/>
-      <c r="J20" s="381"/>
+      <c r="G20" s="378"/>
+      <c r="H20" s="378"/>
+      <c r="I20" s="378"/>
+      <c r="J20" s="378"/>
     </row>
     <row r="21" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="245"/>
       <c r="E21" s="245"/>
-      <c r="F21" s="381"/>
-      <c r="G21" s="381"/>
-      <c r="H21" s="381"/>
-      <c r="I21" s="381"/>
-      <c r="J21" s="381"/>
+      <c r="F21" s="378"/>
+      <c r="G21" s="378"/>
+      <c r="H21" s="378"/>
+      <c r="I21" s="378"/>
+      <c r="J21" s="378"/>
     </row>
     <row r="22" spans="2:10" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="245"/>
       <c r="E22" s="245"/>
-      <c r="F22" s="381"/>
-      <c r="G22" s="381"/>
-      <c r="H22" s="381"/>
-      <c r="I22" s="381"/>
-      <c r="J22" s="381"/>
+      <c r="F22" s="378"/>
+      <c r="G22" s="378"/>
+      <c r="H22" s="378"/>
+      <c r="I22" s="378"/>
+      <c r="J22" s="378"/>
     </row>
     <row r="23" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="245"/>
@@ -14185,22 +14185,22 @@
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D24" s="245"/>
       <c r="E24" s="245"/>
-      <c r="F24" s="382" t="s">
+      <c r="F24" s="379" t="s">
         <v>5</v>
       </c>
-      <c r="G24" s="382"/>
-      <c r="H24" s="382"/>
-      <c r="I24" s="382"/>
-      <c r="J24" s="382"/>
+      <c r="G24" s="379"/>
+      <c r="H24" s="379"/>
+      <c r="I24" s="379"/>
+      <c r="J24" s="379"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D25" s="245"/>
       <c r="E25" s="245"/>
-      <c r="F25" s="382"/>
-      <c r="G25" s="382"/>
-      <c r="H25" s="382"/>
-      <c r="I25" s="382"/>
-      <c r="J25" s="382"/>
+      <c r="F25" s="379"/>
+      <c r="G25" s="379"/>
+      <c r="H25" s="379"/>
+      <c r="I25" s="379"/>
+      <c r="J25" s="379"/>
     </row>
     <row r="26" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="245"/>
@@ -14214,49 +14214,49 @@
     <row r="27" spans="2:10" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="245"/>
       <c r="E27" s="245"/>
-      <c r="F27" s="372"/>
-      <c r="G27" s="372"/>
-      <c r="H27" s="372"/>
-      <c r="I27" s="372"/>
-      <c r="J27" s="372"/>
+      <c r="F27" s="369"/>
+      <c r="G27" s="369"/>
+      <c r="H27" s="369"/>
+      <c r="I27" s="369"/>
+      <c r="J27" s="369"/>
     </row>
     <row r="28" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="245"/>
       <c r="E28" s="245"/>
-      <c r="F28" s="383" t="s">
-        <v>442</v>
-      </c>
-      <c r="G28" s="383"/>
-      <c r="H28" s="383"/>
-      <c r="I28" s="383"/>
-      <c r="J28" s="383"/>
+      <c r="F28" s="380" t="s">
+        <v>441</v>
+      </c>
+      <c r="G28" s="380"/>
+      <c r="H28" s="380"/>
+      <c r="I28" s="380"/>
+      <c r="J28" s="380"/>
     </row>
     <row r="29" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="245"/>
       <c r="E29" s="245"/>
-      <c r="F29" s="383"/>
-      <c r="G29" s="383"/>
-      <c r="H29" s="383"/>
-      <c r="I29" s="383"/>
-      <c r="J29" s="383"/>
+      <c r="F29" s="380"/>
+      <c r="G29" s="380"/>
+      <c r="H29" s="380"/>
+      <c r="I29" s="380"/>
+      <c r="J29" s="380"/>
     </row>
     <row r="30" spans="2:10" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="245"/>
       <c r="E30" s="245"/>
-      <c r="F30" s="383"/>
-      <c r="G30" s="383"/>
-      <c r="H30" s="383"/>
-      <c r="I30" s="383"/>
-      <c r="J30" s="383"/>
+      <c r="F30" s="380"/>
+      <c r="G30" s="380"/>
+      <c r="H30" s="380"/>
+      <c r="I30" s="380"/>
+      <c r="J30" s="380"/>
     </row>
     <row r="31" spans="2:10" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="245"/>
       <c r="E31" s="245"/>
-      <c r="F31" s="371"/>
-      <c r="G31" s="371"/>
-      <c r="H31" s="371"/>
-      <c r="I31" s="371"/>
-      <c r="J31" s="371"/>
+      <c r="F31" s="381"/>
+      <c r="G31" s="381"/>
+      <c r="H31" s="381"/>
+      <c r="I31" s="381"/>
+      <c r="J31" s="381"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="250" t="s">
@@ -14305,15 +14305,15 @@
     <row r="36" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="116"/>
       <c r="C36" s="113"/>
-      <c r="D36" s="371" t="s">
+      <c r="D36" s="381" t="s">
         <v>8</v>
       </c>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
-      <c r="G36" s="371"/>
-      <c r="H36" s="371"/>
-      <c r="I36" s="371"/>
-      <c r="J36" s="371"/>
+      <c r="E36" s="381"/>
+      <c r="F36" s="381"/>
+      <c r="G36" s="381"/>
+      <c r="H36" s="381"/>
+      <c r="I36" s="381"/>
+      <c r="J36" s="381"/>
     </row>
     <row r="37" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="117"/>
@@ -14329,24 +14329,24 @@
     <row r="38" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="241"/>
       <c r="C38" s="113"/>
-      <c r="D38" s="372" t="s">
+      <c r="D38" s="369" t="s">
         <v>9</v>
       </c>
-      <c r="E38" s="372"/>
-      <c r="F38" s="372"/>
-      <c r="G38" s="372"/>
-      <c r="H38" s="372"/>
-      <c r="I38" s="372"/>
-      <c r="J38" s="372"/>
+      <c r="E38" s="369"/>
+      <c r="F38" s="369"/>
+      <c r="G38" s="369"/>
+      <c r="H38" s="369"/>
+      <c r="I38" s="369"/>
+      <c r="J38" s="369"/>
     </row>
     <row r="39" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D39" s="372"/>
-      <c r="E39" s="372"/>
-      <c r="F39" s="372"/>
-      <c r="G39" s="372"/>
-      <c r="H39" s="372"/>
-      <c r="I39" s="372"/>
-      <c r="J39" s="372"/>
+      <c r="D39" s="369"/>
+      <c r="E39" s="369"/>
+      <c r="F39" s="369"/>
+      <c r="G39" s="369"/>
+      <c r="H39" s="369"/>
+      <c r="I39" s="369"/>
+      <c r="J39" s="369"/>
     </row>
     <row r="40" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="117"/>
@@ -14364,15 +14364,15 @@
         <v>10</v>
       </c>
       <c r="C41" s="113"/>
-      <c r="D41" s="369" t="s">
+      <c r="D41" s="382" t="s">
         <v>11</v>
       </c>
-      <c r="E41" s="369"/>
-      <c r="F41" s="369"/>
-      <c r="G41" s="369"/>
-      <c r="H41" s="369"/>
-      <c r="I41" s="369"/>
-      <c r="J41" s="369"/>
+      <c r="E41" s="382"/>
+      <c r="F41" s="382"/>
+      <c r="G41" s="382"/>
+      <c r="H41" s="382"/>
+      <c r="I41" s="382"/>
+      <c r="J41" s="382"/>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="113"/>
@@ -14386,30 +14386,30 @@
       <c r="J42" s="245"/>
     </row>
     <row r="43" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="370" t="s">
+      <c r="B43" s="383" t="s">
         <v>12</v>
       </c>
       <c r="C43" s="103"/>
-      <c r="D43" s="371" t="s">
+      <c r="D43" s="381" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="371"/>
-      <c r="F43" s="371"/>
-      <c r="G43" s="371"/>
-      <c r="H43" s="371"/>
-      <c r="I43" s="371"/>
-      <c r="J43" s="371"/>
+      <c r="E43" s="381"/>
+      <c r="F43" s="381"/>
+      <c r="G43" s="381"/>
+      <c r="H43" s="381"/>
+      <c r="I43" s="381"/>
+      <c r="J43" s="381"/>
     </row>
     <row r="44" spans="2:11" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="B44" s="370"/>
+      <c r="B44" s="383"/>
       <c r="C44" s="103"/>
-      <c r="D44" s="371"/>
-      <c r="E44" s="371"/>
-      <c r="F44" s="371"/>
-      <c r="G44" s="371"/>
-      <c r="H44" s="371"/>
-      <c r="I44" s="371"/>
-      <c r="J44" s="371"/>
+      <c r="D44" s="381"/>
+      <c r="E44" s="381"/>
+      <c r="F44" s="381"/>
+      <c r="G44" s="381"/>
+      <c r="H44" s="381"/>
+      <c r="I44" s="381"/>
+      <c r="J44" s="381"/>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D45" s="112"/>
@@ -14420,18 +14420,18 @@
       <c r="I45" s="114"/>
       <c r="J45" s="114"/>
     </row>
-    <row r="46" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="371" t="s">
-        <v>417</v>
-      </c>
-      <c r="C46" s="371"/>
-      <c r="D46" s="371"/>
-      <c r="E46" s="371"/>
-      <c r="F46" s="371"/>
-      <c r="G46" s="371"/>
-      <c r="H46" s="371"/>
-      <c r="I46" s="371"/>
-      <c r="J46" s="371"/>
+    <row r="46" spans="2:11" ht="58.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="381" t="s">
+        <v>561</v>
+      </c>
+      <c r="C46" s="381"/>
+      <c r="D46" s="381"/>
+      <c r="E46" s="381"/>
+      <c r="F46" s="381"/>
+      <c r="G46" s="381"/>
+      <c r="H46" s="381"/>
+      <c r="I46" s="381"/>
+      <c r="J46" s="381"/>
       <c r="K46" s="107"/>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
@@ -14466,17 +14466,17 @@
       <c r="J49" s="112"/>
     </row>
     <row r="50" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="371" t="s">
+      <c r="B50" s="381" t="s">
         <v>15</v>
       </c>
-      <c r="C50" s="371"/>
-      <c r="D50" s="371"/>
-      <c r="E50" s="371"/>
-      <c r="F50" s="371"/>
-      <c r="G50" s="371"/>
-      <c r="H50" s="371"/>
-      <c r="I50" s="371"/>
-      <c r="J50" s="371"/>
+      <c r="C50" s="381"/>
+      <c r="D50" s="381"/>
+      <c r="E50" s="381"/>
+      <c r="F50" s="381"/>
+      <c r="G50" s="381"/>
+      <c r="H50" s="381"/>
+      <c r="I50" s="381"/>
+      <c r="J50" s="381"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D51" s="114"/>
@@ -14539,6 +14539,11 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="17">
+    <mergeCell ref="D41:J41"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="D43:J44"/>
+    <mergeCell ref="B46:J46"/>
+    <mergeCell ref="B50:J50"/>
     <mergeCell ref="D38:J39"/>
     <mergeCell ref="B5:J5"/>
     <mergeCell ref="F9:J9"/>
@@ -14551,11 +14556,6 @@
     <mergeCell ref="F28:J30"/>
     <mergeCell ref="F31:J31"/>
     <mergeCell ref="D36:J36"/>
-    <mergeCell ref="D41:J41"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="D43:J44"/>
-    <mergeCell ref="B46:J46"/>
-    <mergeCell ref="B50:J50"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F9:J9" location="Input_Beschaffung!A1" display="Geben Sie die übergeordneten Informationen zu Ihrem Beschaffungsfall ein. Hier können Informationen wie die erwartete jährliche Fahrleistung, die Art der Beschaffung (Kauf/Leasing) und weitere Informationen eingegeben werden." xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -14597,7 +14597,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>21</v>
@@ -15064,7 +15064,7 @@
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="370" t="s">
+      <c r="A46" s="383" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="437" t="s">
@@ -15081,7 +15081,7 @@
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="370"/>
+      <c r="A47" s="383"/>
       <c r="B47" s="438"/>
       <c r="C47" s="281" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
@@ -15149,7 +15149,7 @@
         <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis4-Gesamtpreis4*(-0.2*LN(Haltedauer)+0.667),0)</f>
@@ -15214,7 +15214,7 @@
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="370" t="s">
+      <c r="A60" s="383" t="s">
         <v>12</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -15232,7 +15232,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="370"/>
+      <c r="A61" s="383"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -15248,7 +15248,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="370"/>
+      <c r="A62" s="383"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -15357,7 +15357,7 @@
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>21</v>
@@ -15828,7 +15828,7 @@
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="370" t="s">
+      <c r="A46" s="383" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="437" t="s">
@@ -15845,7 +15845,7 @@
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="370"/>
+      <c r="A47" s="383"/>
       <c r="B47" s="438"/>
       <c r="C47" s="281" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
@@ -15913,7 +15913,7 @@
         <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis5-Gesamtpreis5*(-0.2*LN(Haltedauer)+0.667),0)</f>
@@ -15978,7 +15978,7 @@
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="370" t="s">
+      <c r="A60" s="383" t="s">
         <v>12</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -15996,7 +15996,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="370"/>
+      <c r="A61" s="383"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -16012,7 +16012,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="370"/>
+      <c r="A62" s="383"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -16124,7 +16124,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -16186,7 +16186,7 @@
     </row>
     <row r="10" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="92" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
@@ -16288,14 +16288,14 @@
     </row>
     <row r="18" spans="1:37" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="92" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D18" s="106"/>
       <c r="E18" s="10"/>
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B20" s="154" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
@@ -16311,13 +16311,13 @@
         <v>116</v>
       </c>
       <c r="J21" s="135" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="K21" s="135"/>
       <c r="L21" s="135"/>
       <c r="M21" s="135"/>
       <c r="O21" s="137" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P21" s="137"/>
       <c r="Q21" s="137"/>
@@ -16459,7 +16459,7 @@
         <v>177</v>
       </c>
       <c r="I24" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="J24" s="300">
         <v>445</v>
@@ -16638,12 +16638,12 @@
     </row>
     <row r="39" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="234" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="234" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="41" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16659,12 +16659,12 @@
     </row>
     <row r="44" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="267" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="I45" s="106"/>
     </row>
@@ -16679,10 +16679,10 @@
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.25">
@@ -16690,7 +16690,7 @@
         <v>198</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.25">
@@ -16698,7 +16698,7 @@
         <v>199</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
@@ -16706,7 +16706,7 @@
         <v>200</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
@@ -16714,7 +16714,7 @@
         <v>31</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.25">
@@ -16722,7 +16722,7 @@
         <v>201</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
@@ -16730,15 +16730,15 @@
         <v>202</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
@@ -16746,7 +16746,7 @@
         <v>203</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
@@ -16754,7 +16754,7 @@
         <v>204</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
@@ -16762,7 +16762,7 @@
         <v>205</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
@@ -17327,146 +17327,146 @@
     </row>
     <row r="131" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B131" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>508</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="132" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B132" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>510</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="133" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B133" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>512</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="134" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B134" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>514</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="135" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B135" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>516</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="136" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B136" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>518</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="137" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B137" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>520</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="138" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B138" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>522</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B139" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>524</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B140" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>526</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="141" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B141" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>528</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="142" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B142" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="D142" s="1" t="s">
         <v>530</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="143" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B143" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>532</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="144" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B144" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="D144" s="1" t="s">
         <v>534</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="145" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B145" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>536</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="146" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B146" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>538</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="147" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B147" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>540</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B148" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>542</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="149" spans="2:4" x14ac:dyDescent="0.25">
@@ -17514,7 +17514,7 @@
         <v>386</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="155" spans="2:4" x14ac:dyDescent="0.25">
@@ -17522,7 +17522,7 @@
         <v>356</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="156" spans="2:4" x14ac:dyDescent="0.25">
@@ -17530,7 +17530,7 @@
         <v>357</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="157" spans="2:4" x14ac:dyDescent="0.25">
@@ -17546,31 +17546,31 @@
         <v>360</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="159" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B159" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>547</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="160" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B160" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>549</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="161" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B161" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="D161" s="1" t="s">
         <v>551</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="162" spans="2:4" x14ac:dyDescent="0.25">
@@ -17634,7 +17634,7 @@
         <v>375</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="170" spans="2:4" x14ac:dyDescent="0.25">
@@ -17642,7 +17642,7 @@
         <v>186</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="171" spans="2:4" x14ac:dyDescent="0.25">
@@ -17650,7 +17650,7 @@
         <v>187</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="172" spans="2:4" x14ac:dyDescent="0.25">
@@ -17658,7 +17658,7 @@
         <v>188</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="173" spans="2:4" x14ac:dyDescent="0.25">
@@ -17666,7 +17666,7 @@
         <v>190</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="174" spans="2:4" x14ac:dyDescent="0.25">
@@ -17674,7 +17674,7 @@
         <v>191</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="175" spans="2:4" x14ac:dyDescent="0.25">
@@ -17682,7 +17682,7 @@
         <v>376</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="176" spans="2:4" x14ac:dyDescent="0.25">
@@ -17690,7 +17690,7 @@
         <v>377</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="177" spans="2:4" x14ac:dyDescent="0.25">
@@ -17698,7 +17698,7 @@
         <v>378</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="178" spans="2:4" x14ac:dyDescent="0.25">
@@ -17706,7 +17706,7 @@
         <v>379</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="179" spans="2:4" x14ac:dyDescent="0.25">
@@ -17714,7 +17714,7 @@
         <v>380</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="180" spans="2:4" x14ac:dyDescent="0.25">
@@ -17722,7 +17722,7 @@
         <v>381</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="181" spans="2:4" x14ac:dyDescent="0.25">
@@ -17730,7 +17730,7 @@
         <v>382</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="182" spans="2:4" x14ac:dyDescent="0.25">
@@ -17738,7 +17738,7 @@
         <v>383</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="183" spans="2:4" x14ac:dyDescent="0.25">
@@ -17746,7 +17746,7 @@
         <v>384</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="184" spans="2:4" x14ac:dyDescent="0.25">
@@ -17754,7 +17754,7 @@
         <v>385</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="185" spans="2:4" x14ac:dyDescent="0.25">
@@ -17762,7 +17762,7 @@
         <v>387</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="186" spans="2:4" x14ac:dyDescent="0.25">
@@ -17770,7 +17770,7 @@
         <v>388</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="187" spans="2:4" x14ac:dyDescent="0.25">
@@ -17778,7 +17778,7 @@
         <v>389</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="188" spans="2:4" x14ac:dyDescent="0.25">
@@ -17786,7 +17786,7 @@
         <v>390</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="189" spans="2:4" x14ac:dyDescent="0.25">
@@ -17802,7 +17802,7 @@
         <v>393</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="191" spans="2:4" x14ac:dyDescent="0.25">
@@ -17950,7 +17950,7 @@
         <v>187</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
@@ -18082,7 +18082,7 @@
     </row>
     <row r="4" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B4" s="275" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C4" s="275" t="s">
         <v>399</v>
@@ -18095,23 +18095,23 @@
     </row>
     <row r="6" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B6" s="275" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C6" s="275" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="7" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C7" s="276" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="8" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="275" t="s">
+        <v>458</v>
+      </c>
+      <c r="C8" s="270" t="s">
         <v>459</v>
-      </c>
-      <c r="C8" s="270" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="9" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
@@ -18148,15 +18148,15 @@
     </row>
     <row r="14" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="275" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C14" s="275" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="15" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C15" s="276" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="16" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
@@ -18174,15 +18174,15 @@
     </row>
     <row r="18" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="275" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C18" s="275" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="19" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C19" s="276" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="20" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
@@ -18200,20 +18200,20 @@
     </row>
     <row r="22" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B22" s="275" t="s">
+        <v>438</v>
+      </c>
+      <c r="C22" s="275" t="s">
         <v>439</v>
-      </c>
-      <c r="C22" s="275" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="23" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C23" s="276" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="24" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B24" s="275" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C24" s="275" t="s">
         <v>416</v>
@@ -18226,15 +18226,15 @@
     </row>
     <row r="26" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="275" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C26" s="275" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="27" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C27" s="269" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="28" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -18283,7 +18283,7 @@
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="I2" s="106" t="s">
         <v>21</v>
@@ -18302,7 +18302,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C6" s="388"/>
       <c r="D6" s="389"/>
@@ -18392,7 +18392,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C15" s="152"/>
       <c r="D15" s="55" t="s">
@@ -18432,7 +18432,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B19" s="298" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C19" s="151"/>
       <c r="D19" s="55"/>
@@ -18491,7 +18491,7 @@
         <v>36</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F26" s="274">
         <f>Grunddaten!E38</f>
@@ -18503,7 +18503,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B28" s="154" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
@@ -18696,7 +18696,7 @@
     </row>
     <row r="2" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C2" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D2" s="2"/>
       <c r="J2" s="7"/>
@@ -18847,7 +18847,7 @@
       <c r="J10" s="238"/>
       <c r="K10" s="236"/>
       <c r="L10" s="411" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="M10" s="411"/>
       <c r="N10" s="236"/>
@@ -19145,7 +19145,7 @@
     </row>
     <row r="23" spans="2:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C23" s="77" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D23" s="228"/>
       <c r="E23" s="368"/>
@@ -19160,7 +19160,7 @@
       <c r="R23" s="7"/>
     </row>
     <row r="24" spans="2:18" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="370" t="s">
+      <c r="B24" s="383" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="331"/>
@@ -19179,7 +19179,7 @@
       <c r="R24" s="7"/>
     </row>
     <row r="25" spans="2:18" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="370"/>
+      <c r="B25" s="383"/>
       <c r="C25" s="331"/>
       <c r="D25" s="322" t="s">
         <v>147</v>
@@ -19196,7 +19196,7 @@
       <c r="R25" s="7"/>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B26" s="370"/>
+      <c r="B26" s="383"/>
       <c r="C26" s="335"/>
       <c r="D26" s="322" t="s">
         <v>147</v>
@@ -19272,7 +19272,7 @@
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C32" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
   </sheetData>
@@ -19656,7 +19656,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="118" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C1" s="118"/>
       <c r="D1" s="118"/>
@@ -19670,7 +19670,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C2" s="227"/>
       <c r="D2" s="230" t="str">
@@ -19713,7 +19713,7 @@
     <row r="6" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18"/>
       <c r="B6" s="12" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C6" s="418" t="str">
         <f>IF(Projektname=0,"",Projektname)</f>
@@ -19795,7 +19795,7 @@
       <c r="B12" s="12"/>
       <c r="C12" s="76"/>
       <c r="E12" s="58" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F12" s="85">
         <f>Fahrleistung</f>
@@ -20290,7 +20290,7 @@
     <row r="31" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="309"/>
       <c r="B31" s="98" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C31" s="317" t="s">
         <v>90</v>
@@ -20320,10 +20320,10 @@
     <row r="32" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="309"/>
       <c r="B32" s="310" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C32" s="311" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D32" s="312" t="e">
         <f>SUM(D30:D31)</f>
@@ -20480,7 +20480,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="118" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C1" s="118"/>
       <c r="D1" s="118"/>
@@ -20494,7 +20494,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C2" s="227"/>
       <c r="D2" s="230" t="str">
@@ -20537,7 +20537,7 @@
     <row r="6" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18"/>
       <c r="B6" s="12" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C6" s="418" t="str">
         <f>IF(Projektname=0,"",Projektname)</f>
@@ -20619,7 +20619,7 @@
       <c r="B12" s="12"/>
       <c r="C12" s="76"/>
       <c r="E12" s="58" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F12" s="85">
         <f>Fahrleistung</f>
@@ -20659,7 +20659,7 @@
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="18"/>
       <c r="B15" s="293" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="21"/>
@@ -20956,7 +20956,7 @@
     <row r="26" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="33"/>
       <c r="B26" s="98" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C26" s="99" t="s">
         <v>90</v>
@@ -20986,10 +20986,10 @@
     <row r="27" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="33"/>
       <c r="B27" s="310" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C27" s="311" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D27" s="312" t="e">
         <f>SUM(D25:D26)</f>
@@ -21015,7 +21015,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B29" s="293" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C29" s="21"/>
       <c r="D29" s="21"/>
@@ -21177,7 +21177,7 @@
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="119"/>
       <c r="B4" s="293" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C4" s="354"/>
       <c r="D4" s="354"/>
@@ -21187,7 +21187,7 @@
       <c r="H4" s="119"/>
     </row>
     <row r="5" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="370" t="s">
+      <c r="A5" s="383" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="219"/>
@@ -21198,13 +21198,13 @@
       <c r="G5" s="190"/>
       <c r="H5" s="119"/>
       <c r="J5" s="427" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="K5" s="427"/>
       <c r="L5" s="427"/>
     </row>
     <row r="6" spans="1:12" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A6" s="370"/>
+      <c r="A6" s="383"/>
       <c r="B6" s="220" t="s">
         <v>96</v>
       </c>
@@ -21399,7 +21399,7 @@
         <v>47</v>
       </c>
       <c r="D14" s="223" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E14" s="272"/>
       <c r="F14" s="222" t="s">
@@ -21418,10 +21418,10 @@
       <c r="A15" s="416"/>
       <c r="B15" s="429"/>
       <c r="C15" s="222" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D15" s="223" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E15" s="272"/>
       <c r="F15" s="222" t="s">
@@ -21440,10 +21440,10 @@
       <c r="A16" s="416"/>
       <c r="B16" s="430"/>
       <c r="C16" s="222" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D16" s="223" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E16" s="272"/>
       <c r="F16" s="222" t="s">
@@ -21531,7 +21531,7 @@
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="196"/>
       <c r="B23" s="293" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C23" s="339"/>
       <c r="D23" s="340"/>
@@ -21606,7 +21606,7 @@
         <v>0.41399999999999998</v>
       </c>
       <c r="H27" s="199" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I27" s="254"/>
     </row>
@@ -21628,7 +21628,7 @@
         <v>0.59</v>
       </c>
       <c r="H28" s="199" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="I28" s="254"/>
     </row>
@@ -21666,7 +21666,7 @@
         <v>1.6719999999999999</v>
       </c>
       <c r="H30" s="199" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="I30" s="254"/>
     </row>
@@ -21688,7 +21688,7 @@
         <v>1.788</v>
       </c>
       <c r="H31" s="199" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="I31" s="254"/>
     </row>
@@ -21710,7 +21710,7 @@
         <v>1.3</v>
       </c>
       <c r="H32" s="199" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="I32" s="254"/>
     </row>
@@ -21798,7 +21798,7 @@
         <v>860</v>
       </c>
       <c r="H38" s="199" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I38" s="254"/>
     </row>
@@ -21895,7 +21895,7 @@
     <row r="45" spans="1:9" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A45" s="193"/>
       <c r="B45" s="431" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C45" s="432"/>
       <c r="D45" s="218">
@@ -22032,7 +22032,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>21</v>
@@ -22446,7 +22446,7 @@
       <c r="D45" s="62"/>
     </row>
     <row r="46" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="370" t="s">
+      <c r="A46" s="383" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="437" t="s">
@@ -22463,7 +22463,7 @@
       <c r="F46" s="107"/>
     </row>
     <row r="47" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="370"/>
+      <c r="A47" s="383"/>
       <c r="B47" s="438"/>
       <c r="C47" s="281" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
@@ -22524,7 +22524,7 @@
         <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis1-Gesamtpreis1*(-0.2*LN(Haltedauer)+0.667),0)</f>
@@ -22588,7 +22588,7 @@
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="370" t="s">
+      <c r="A60" s="383" t="s">
         <v>12</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -22606,7 +22606,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="370"/>
+      <c r="A61" s="383"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -22622,7 +22622,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="370"/>
+      <c r="A62" s="383"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -22724,7 +22724,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>21</v>
@@ -23191,7 +23191,7 @@
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="370" t="s">
+      <c r="A46" s="383" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="437" t="s">
@@ -23208,7 +23208,7 @@
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="370"/>
+      <c r="A47" s="383"/>
       <c r="B47" s="438"/>
       <c r="C47" s="281" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
@@ -23276,7 +23276,7 @@
         <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis2-Gesamtpreis2*(-0.2*LN(Haltedauer)+0.667),0)</f>
@@ -23341,7 +23341,7 @@
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="370" t="s">
+      <c r="A60" s="383" t="s">
         <v>12</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -23359,7 +23359,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="370"/>
+      <c r="A61" s="383"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -23375,7 +23375,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="370"/>
+      <c r="A62" s="383"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -23484,7 +23484,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>21</v>
@@ -23951,7 +23951,7 @@
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="370" t="s">
+      <c r="A46" s="383" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="437" t="s">
@@ -23968,7 +23968,7 @@
       <c r="F46" s="133"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="370"/>
+      <c r="A47" s="383"/>
       <c r="B47" s="438"/>
       <c r="C47" s="281" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
@@ -24036,7 +24036,7 @@
         <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis3-Gesamtpreis3*(-0.2*LN(Haltedauer)+0.667),0)</f>
@@ -24101,7 +24101,7 @@
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="370" t="s">
+      <c r="A60" s="383" t="s">
         <v>12</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -24119,7 +24119,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="370"/>
+      <c r="A61" s="383"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -24135,7 +24135,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="370"/>
+      <c r="A62" s="383"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -24222,6 +24222,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e4dc333-02c0-4d6f-a03d-d04a548a7be7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101006A4EC2B1D245C948A7120CE5A36078F8" ma:contentTypeVersion="14" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="4b87026bc8dcc7f3f10cc45b8239b46f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5e4dc333-02c0-4d6f-a03d-d04a548a7be7" xmlns:ns3="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7f15f5ac45b0ba6c0c6284d6c06137b" ns2:_="" ns3:_="">
     <xsd:import namespace="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
@@ -24450,27 +24470,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{651615EB-DE44-4BF4-BD1E-846AB7A3DA36}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
+    <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e4dc333-02c0-4d6f-a03d-d04a548a7be7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92A2CDCF-36F6-4C30-8F9B-D45880CB8E7E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C82CFA85-B81D-4C7D-99B5-F82C00D97DE4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -24487,29 +24512,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92A2CDCF-36F6-4C30-8F9B-D45880CB8E7E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{651615EB-DE44-4BF4-BD1E-846AB7A3DA36}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/src/assets/downloads/LZK-Rechner_Pkw_V1.3.xlsx
+++ b/src/assets/downloads/LZK-Rechner_Pkw_V1.3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifeu2.sharepoint.com/sites/DBUBeschaffungBerlin/Freigegebene Dokumente/General/Folgeprojekt/03_Arbeitsdokumente/A4 - Aktualisierung der Instrumente aus Basisprojekt/LZK-Rechner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1228" documentId="13_ncr:1_{3372B5DA-C386-4B74-B09A-B44627B6D7C7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{C38B4280-322E-4CBE-9F67-5B06B03D8F7D}"/>
+  <xr:revisionPtr revIDLastSave="1236" documentId="13_ncr:1_{3372B5DA-C386-4B74-B09A-B44627B6D7C7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6EF0B98-CF65-48D1-87B3-81FDF162D5C7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="887" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12365,7 +12365,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9090449" y="2428875"/>
+          <a:off x="9418109" y="2428875"/>
           <a:ext cx="1631979" cy="976630"/>
           <a:chOff x="8390255" y="2565400"/>
           <a:chExt cx="1643409" cy="965200"/>
@@ -18677,7 +18677,7 @@
     <col min="1" max="1" width="2.109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="5.109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="28.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" style="1" customWidth="1"/>
     <col min="5" max="9" width="14.33203125" style="1" customWidth="1"/>
     <col min="10" max="10" width="3.33203125" style="1" customWidth="1"/>
     <col min="11" max="11" width="7.109375" style="7" customWidth="1"/>
@@ -18906,8 +18906,8 @@
         <v>Art der Beschaffung wählen in:</v>
       </c>
       <c r="D13" s="166" t="str">
-        <f>IF(ISBLANK(FinArt), "Input_Projekt", VLOOKUP(FinArt,FinArtList,2,FALSE))</f>
-        <v>Input_Projekt</v>
+        <f>IF(ISBLANK(FinArt), "Input_Beschaffung", VLOOKUP(FinArt,FinArtList,2,FALSE))</f>
+        <v>Input_Beschaffung</v>
       </c>
       <c r="E13" s="142"/>
       <c r="F13" s="142"/>
@@ -24474,13 +24474,13 @@
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{651615EB-DE44-4BF4-BD1E-846AB7A3DA36}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
-    <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>

--- a/src/assets/downloads/LZK-Rechner_Pkw_V1.3.xlsx
+++ b/src/assets/downloads/LZK-Rechner_Pkw_V1.3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifeu2.sharepoint.com/sites/DBUBeschaffungBerlin/Freigegebene Dokumente/General/Folgeprojekt/03_Arbeitsdokumente/A4 - Aktualisierung der Instrumente aus Basisprojekt/LZK-Rechner/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julia Pelzeter\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1236" documentId="13_ncr:1_{3372B5DA-C386-4B74-B09A-B44627B6D7C7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6EF0B98-CF65-48D1-87B3-81FDF162D5C7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90AAB12A-5F46-4016-98C8-57F8B44A9F83}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="887" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="11124" tabRatio="887" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Anleitung" sheetId="27" r:id="rId1"/>
@@ -180,7 +180,7 @@
     <definedName name="Zusatzinfo5">Eingabe_Angebotswerte!$I$12</definedName>
     <definedName name="Zustaendig">Input_Beschaffung!$C$10</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1" iterateCount="1000"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -858,9 +858,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="562">
   <si>
-    <t>Lebenszykluskosten-Rechner für Pkw - beispielhaft mit Daten befüllt</t>
-  </si>
-  <si>
     <t>Vorgehen</t>
   </si>
   <si>
@@ -2713,9 +2710,6 @@
   </si>
   <si>
     <t>UBA (2024b)</t>
-  </si>
-  <si>
-    <t>https://www.umweltbundesamt.de/sites/default/files/medien/11850/publikationen/23_2024_cc_strommix_07_2024.pdf</t>
   </si>
   <si>
     <t>Entwicklung der spezifischen Treibhausgas-Emissionen des deutschen Strommix in den Jahren 1990 - 2023</t>
@@ -3295,6 +3289,12 @@
       </rPr>
       <t>Es ist jedoch zu berücksichtigen, dass dadurch Berechnungsfehler entstehen können. Die Verantwortung liegt bei der Person, die den Rechner angepasst hat.</t>
     </r>
+  </si>
+  <si>
+    <t>Lebenszykluskosten-Rechner für Pkw</t>
+  </si>
+  <si>
+    <t>https://www.umweltbundesamt.de/publikationen/entwicklung-der-spezifischen-treibhausgas-10</t>
   </si>
 </sst>
 </file>
@@ -4605,7 +4605,7 @@
     <xf numFmtId="166" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="443">
+  <cellXfs count="442">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5229,9 +5229,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5497,6 +5494,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
@@ -5531,15 +5537,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -12365,8 +12362,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9418109" y="2428875"/>
-          <a:ext cx="1631979" cy="976630"/>
+          <a:off x="9400964" y="2388870"/>
+          <a:ext cx="1630074" cy="963295"/>
           <a:chOff x="8390255" y="2565400"/>
           <a:chExt cx="1643409" cy="965200"/>
         </a:xfrm>
@@ -13960,7 +13957,7 @@
   <sheetData>
     <row r="2" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="16" t="s">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="C2" s="16"/>
       <c r="D2" s="16"/>
@@ -13970,7 +13967,7 @@
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
       <c r="J2" s="268" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
@@ -13992,17 +13989,17 @@
       <c r="J4" s="115"/>
     </row>
     <row r="5" spans="2:10" ht="149.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="370" t="s">
-        <v>467</v>
-      </c>
-      <c r="C5" s="370"/>
-      <c r="D5" s="370"/>
-      <c r="E5" s="370"/>
-      <c r="F5" s="370"/>
-      <c r="G5" s="370"/>
-      <c r="H5" s="370"/>
-      <c r="I5" s="370"/>
-      <c r="J5" s="370"/>
+      <c r="B5" s="372" t="s">
+        <v>465</v>
+      </c>
+      <c r="C5" s="372"/>
+      <c r="D5" s="372"/>
+      <c r="E5" s="372"/>
+      <c r="F5" s="372"/>
+      <c r="G5" s="372"/>
+      <c r="H5" s="372"/>
+      <c r="I5" s="372"/>
+      <c r="J5" s="372"/>
     </row>
     <row r="6" spans="2:10" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="245"/>
@@ -14017,7 +14014,7 @@
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="16" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -14040,13 +14037,13 @@
     <row r="9" spans="2:10" ht="52.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D9" s="245"/>
       <c r="E9" s="245"/>
-      <c r="F9" s="371" t="s">
-        <v>425</v>
-      </c>
-      <c r="G9" s="371"/>
-      <c r="H9" s="371"/>
-      <c r="I9" s="371"/>
-      <c r="J9" s="371"/>
+      <c r="F9" s="373" t="s">
+        <v>424</v>
+      </c>
+      <c r="G9" s="373"/>
+      <c r="H9" s="373"/>
+      <c r="I9" s="373"/>
+      <c r="J9" s="373"/>
     </row>
     <row r="10" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" s="245"/>
@@ -14060,31 +14057,31 @@
     <row r="11" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="245"/>
       <c r="E11" s="245"/>
-      <c r="F11" s="372" t="s">
-        <v>440</v>
-      </c>
-      <c r="G11" s="373"/>
-      <c r="H11" s="373"/>
-      <c r="I11" s="373"/>
-      <c r="J11" s="373"/>
+      <c r="F11" s="374" t="s">
+        <v>438</v>
+      </c>
+      <c r="G11" s="375"/>
+      <c r="H11" s="375"/>
+      <c r="I11" s="375"/>
+      <c r="J11" s="375"/>
     </row>
     <row r="12" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D12" s="245"/>
       <c r="E12" s="245"/>
-      <c r="F12" s="373"/>
-      <c r="G12" s="373"/>
-      <c r="H12" s="373"/>
-      <c r="I12" s="373"/>
-      <c r="J12" s="373"/>
+      <c r="F12" s="375"/>
+      <c r="G12" s="375"/>
+      <c r="H12" s="375"/>
+      <c r="I12" s="375"/>
+      <c r="J12" s="375"/>
     </row>
     <row r="13" spans="2:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D13" s="245"/>
       <c r="E13" s="245"/>
-      <c r="F13" s="373"/>
-      <c r="G13" s="373"/>
-      <c r="H13" s="373"/>
-      <c r="I13" s="373"/>
-      <c r="J13" s="373"/>
+      <c r="F13" s="375"/>
+      <c r="G13" s="375"/>
+      <c r="H13" s="375"/>
+      <c r="I13" s="375"/>
+      <c r="J13" s="375"/>
     </row>
     <row r="14" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D14" s="245"/>
@@ -14098,22 +14095,22 @@
     <row r="15" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="245"/>
       <c r="E15" s="245"/>
-      <c r="F15" s="374" t="s">
-        <v>2</v>
-      </c>
-      <c r="G15" s="375"/>
-      <c r="H15" s="375"/>
-      <c r="I15" s="375"/>
-      <c r="J15" s="375"/>
+      <c r="F15" s="376" t="s">
+        <v>1</v>
+      </c>
+      <c r="G15" s="377"/>
+      <c r="H15" s="377"/>
+      <c r="I15" s="377"/>
+      <c r="J15" s="377"/>
     </row>
     <row r="16" spans="2:10" ht="73.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D16" s="245"/>
       <c r="E16" s="245"/>
-      <c r="F16" s="375"/>
-      <c r="G16" s="375"/>
-      <c r="H16" s="375"/>
-      <c r="I16" s="375"/>
-      <c r="J16" s="375"/>
+      <c r="F16" s="377"/>
+      <c r="G16" s="377"/>
+      <c r="H16" s="377"/>
+      <c r="I16" s="377"/>
+      <c r="J16" s="377"/>
     </row>
     <row r="17" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D17" s="245"/>
@@ -14127,13 +14124,13 @@
     <row r="18" spans="2:10" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D18" s="245"/>
       <c r="E18" s="245"/>
-      <c r="F18" s="376" t="s">
-        <v>3</v>
-      </c>
-      <c r="G18" s="377"/>
-      <c r="H18" s="377"/>
-      <c r="I18" s="377"/>
-      <c r="J18" s="377"/>
+      <c r="F18" s="378" t="s">
+        <v>2</v>
+      </c>
+      <c r="G18" s="379"/>
+      <c r="H18" s="379"/>
+      <c r="I18" s="379"/>
+      <c r="J18" s="379"/>
     </row>
     <row r="19" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="245"/>
@@ -14147,31 +14144,31 @@
     <row r="20" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="245"/>
       <c r="E20" s="245"/>
-      <c r="F20" s="378" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" s="378"/>
-      <c r="H20" s="378"/>
-      <c r="I20" s="378"/>
-      <c r="J20" s="378"/>
+      <c r="F20" s="380" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="380"/>
+      <c r="H20" s="380"/>
+      <c r="I20" s="380"/>
+      <c r="J20" s="380"/>
     </row>
     <row r="21" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="245"/>
       <c r="E21" s="245"/>
-      <c r="F21" s="378"/>
-      <c r="G21" s="378"/>
-      <c r="H21" s="378"/>
-      <c r="I21" s="378"/>
-      <c r="J21" s="378"/>
+      <c r="F21" s="380"/>
+      <c r="G21" s="380"/>
+      <c r="H21" s="380"/>
+      <c r="I21" s="380"/>
+      <c r="J21" s="380"/>
     </row>
     <row r="22" spans="2:10" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="245"/>
       <c r="E22" s="245"/>
-      <c r="F22" s="378"/>
-      <c r="G22" s="378"/>
-      <c r="H22" s="378"/>
-      <c r="I22" s="378"/>
-      <c r="J22" s="378"/>
+      <c r="F22" s="380"/>
+      <c r="G22" s="380"/>
+      <c r="H22" s="380"/>
+      <c r="I22" s="380"/>
+      <c r="J22" s="380"/>
     </row>
     <row r="23" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="245"/>
@@ -14185,22 +14182,22 @@
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D24" s="245"/>
       <c r="E24" s="245"/>
-      <c r="F24" s="379" t="s">
-        <v>5</v>
-      </c>
-      <c r="G24" s="379"/>
-      <c r="H24" s="379"/>
-      <c r="I24" s="379"/>
-      <c r="J24" s="379"/>
+      <c r="F24" s="381" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="381"/>
+      <c r="H24" s="381"/>
+      <c r="I24" s="381"/>
+      <c r="J24" s="381"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D25" s="245"/>
       <c r="E25" s="245"/>
-      <c r="F25" s="379"/>
-      <c r="G25" s="379"/>
-      <c r="H25" s="379"/>
-      <c r="I25" s="379"/>
-      <c r="J25" s="379"/>
+      <c r="F25" s="381"/>
+      <c r="G25" s="381"/>
+      <c r="H25" s="381"/>
+      <c r="I25" s="381"/>
+      <c r="J25" s="381"/>
     </row>
     <row r="26" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="245"/>
@@ -14214,53 +14211,53 @@
     <row r="27" spans="2:10" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="245"/>
       <c r="E27" s="245"/>
-      <c r="F27" s="369"/>
-      <c r="G27" s="369"/>
-      <c r="H27" s="369"/>
-      <c r="I27" s="369"/>
-      <c r="J27" s="369"/>
+      <c r="F27" s="371"/>
+      <c r="G27" s="371"/>
+      <c r="H27" s="371"/>
+      <c r="I27" s="371"/>
+      <c r="J27" s="371"/>
     </row>
     <row r="28" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="245"/>
       <c r="E28" s="245"/>
-      <c r="F28" s="380" t="s">
-        <v>441</v>
-      </c>
-      <c r="G28" s="380"/>
-      <c r="H28" s="380"/>
-      <c r="I28" s="380"/>
-      <c r="J28" s="380"/>
+      <c r="F28" s="382" t="s">
+        <v>439</v>
+      </c>
+      <c r="G28" s="382"/>
+      <c r="H28" s="382"/>
+      <c r="I28" s="382"/>
+      <c r="J28" s="382"/>
     </row>
     <row r="29" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="245"/>
       <c r="E29" s="245"/>
-      <c r="F29" s="380"/>
-      <c r="G29" s="380"/>
-      <c r="H29" s="380"/>
-      <c r="I29" s="380"/>
-      <c r="J29" s="380"/>
+      <c r="F29" s="382"/>
+      <c r="G29" s="382"/>
+      <c r="H29" s="382"/>
+      <c r="I29" s="382"/>
+      <c r="J29" s="382"/>
     </row>
     <row r="30" spans="2:10" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="245"/>
       <c r="E30" s="245"/>
-      <c r="F30" s="380"/>
-      <c r="G30" s="380"/>
-      <c r="H30" s="380"/>
-      <c r="I30" s="380"/>
-      <c r="J30" s="380"/>
+      <c r="F30" s="382"/>
+      <c r="G30" s="382"/>
+      <c r="H30" s="382"/>
+      <c r="I30" s="382"/>
+      <c r="J30" s="382"/>
     </row>
     <row r="31" spans="2:10" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="245"/>
       <c r="E31" s="245"/>
-      <c r="F31" s="381"/>
-      <c r="G31" s="381"/>
-      <c r="H31" s="381"/>
-      <c r="I31" s="381"/>
-      <c r="J31" s="381"/>
+      <c r="F31" s="370"/>
+      <c r="G31" s="370"/>
+      <c r="H31" s="370"/>
+      <c r="I31" s="370"/>
+      <c r="J31" s="370"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="250" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C32" s="251"/>
       <c r="D32" s="252"/>
@@ -14282,7 +14279,7 @@
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" s="16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C34" s="16"/>
       <c r="D34" s="16"/>
@@ -14305,15 +14302,15 @@
     <row r="36" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="116"/>
       <c r="C36" s="113"/>
-      <c r="D36" s="381" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" s="381"/>
-      <c r="F36" s="381"/>
-      <c r="G36" s="381"/>
-      <c r="H36" s="381"/>
-      <c r="I36" s="381"/>
-      <c r="J36" s="381"/>
+      <c r="D36" s="370" t="s">
+        <v>7</v>
+      </c>
+      <c r="E36" s="370"/>
+      <c r="F36" s="370"/>
+      <c r="G36" s="370"/>
+      <c r="H36" s="370"/>
+      <c r="I36" s="370"/>
+      <c r="J36" s="370"/>
     </row>
     <row r="37" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="117"/>
@@ -14329,24 +14326,24 @@
     <row r="38" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="241"/>
       <c r="C38" s="113"/>
-      <c r="D38" s="369" t="s">
-        <v>9</v>
-      </c>
-      <c r="E38" s="369"/>
-      <c r="F38" s="369"/>
-      <c r="G38" s="369"/>
-      <c r="H38" s="369"/>
-      <c r="I38" s="369"/>
-      <c r="J38" s="369"/>
+      <c r="D38" s="371" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="371"/>
+      <c r="F38" s="371"/>
+      <c r="G38" s="371"/>
+      <c r="H38" s="371"/>
+      <c r="I38" s="371"/>
+      <c r="J38" s="371"/>
     </row>
     <row r="39" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D39" s="369"/>
-      <c r="E39" s="369"/>
-      <c r="F39" s="369"/>
-      <c r="G39" s="369"/>
-      <c r="H39" s="369"/>
-      <c r="I39" s="369"/>
-      <c r="J39" s="369"/>
+      <c r="D39" s="371"/>
+      <c r="E39" s="371"/>
+      <c r="F39" s="371"/>
+      <c r="G39" s="371"/>
+      <c r="H39" s="371"/>
+      <c r="I39" s="371"/>
+      <c r="J39" s="371"/>
     </row>
     <row r="40" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="117"/>
@@ -14361,18 +14358,18 @@
     </row>
     <row r="41" spans="2:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="175" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="113"/>
+      <c r="D41" s="368" t="s">
         <v>10</v>
       </c>
-      <c r="C41" s="113"/>
-      <c r="D41" s="382" t="s">
-        <v>11</v>
-      </c>
-      <c r="E41" s="382"/>
-      <c r="F41" s="382"/>
-      <c r="G41" s="382"/>
-      <c r="H41" s="382"/>
-      <c r="I41" s="382"/>
-      <c r="J41" s="382"/>
+      <c r="E41" s="368"/>
+      <c r="F41" s="368"/>
+      <c r="G41" s="368"/>
+      <c r="H41" s="368"/>
+      <c r="I41" s="368"/>
+      <c r="J41" s="368"/>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="113"/>
@@ -14386,30 +14383,30 @@
       <c r="J42" s="245"/>
     </row>
     <row r="43" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="383" t="s">
+      <c r="B43" s="369" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" s="103"/>
+      <c r="D43" s="370" t="s">
         <v>12</v>
       </c>
-      <c r="C43" s="103"/>
-      <c r="D43" s="381" t="s">
-        <v>13</v>
-      </c>
-      <c r="E43" s="381"/>
-      <c r="F43" s="381"/>
-      <c r="G43" s="381"/>
-      <c r="H43" s="381"/>
-      <c r="I43" s="381"/>
-      <c r="J43" s="381"/>
+      <c r="E43" s="370"/>
+      <c r="F43" s="370"/>
+      <c r="G43" s="370"/>
+      <c r="H43" s="370"/>
+      <c r="I43" s="370"/>
+      <c r="J43" s="370"/>
     </row>
     <row r="44" spans="2:11" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="B44" s="383"/>
+      <c r="B44" s="369"/>
       <c r="C44" s="103"/>
-      <c r="D44" s="381"/>
-      <c r="E44" s="381"/>
-      <c r="F44" s="381"/>
-      <c r="G44" s="381"/>
-      <c r="H44" s="381"/>
-      <c r="I44" s="381"/>
-      <c r="J44" s="381"/>
+      <c r="D44" s="370"/>
+      <c r="E44" s="370"/>
+      <c r="F44" s="370"/>
+      <c r="G44" s="370"/>
+      <c r="H44" s="370"/>
+      <c r="I44" s="370"/>
+      <c r="J44" s="370"/>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D45" s="112"/>
@@ -14421,17 +14418,17 @@
       <c r="J45" s="114"/>
     </row>
     <row r="46" spans="2:11" ht="58.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="381" t="s">
-        <v>561</v>
-      </c>
-      <c r="C46" s="381"/>
-      <c r="D46" s="381"/>
-      <c r="E46" s="381"/>
-      <c r="F46" s="381"/>
-      <c r="G46" s="381"/>
-      <c r="H46" s="381"/>
-      <c r="I46" s="381"/>
-      <c r="J46" s="381"/>
+      <c r="B46" s="370" t="s">
+        <v>559</v>
+      </c>
+      <c r="C46" s="370"/>
+      <c r="D46" s="370"/>
+      <c r="E46" s="370"/>
+      <c r="F46" s="370"/>
+      <c r="G46" s="370"/>
+      <c r="H46" s="370"/>
+      <c r="I46" s="370"/>
+      <c r="J46" s="370"/>
       <c r="K46" s="107"/>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
@@ -14445,7 +14442,7 @@
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" s="16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C48" s="16"/>
       <c r="D48" s="16"/>
@@ -14466,17 +14463,17 @@
       <c r="J49" s="112"/>
     </row>
     <row r="50" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="381" t="s">
-        <v>15</v>
-      </c>
-      <c r="C50" s="381"/>
-      <c r="D50" s="381"/>
-      <c r="E50" s="381"/>
-      <c r="F50" s="381"/>
-      <c r="G50" s="381"/>
-      <c r="H50" s="381"/>
-      <c r="I50" s="381"/>
-      <c r="J50" s="381"/>
+      <c r="B50" s="370" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50" s="370"/>
+      <c r="D50" s="370"/>
+      <c r="E50" s="370"/>
+      <c r="F50" s="370"/>
+      <c r="G50" s="370"/>
+      <c r="H50" s="370"/>
+      <c r="I50" s="370"/>
+      <c r="J50" s="370"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D51" s="114"/>
@@ -14489,7 +14486,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B52" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="17"/>
@@ -14507,25 +14504,25 @@
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="18"/>
       <c r="B54" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="18"/>
       <c r="B55" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="18"/>
       <c r="B56" s="18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="18"/>
       <c r="B57" s="265" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -14539,11 +14536,6 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="17">
-    <mergeCell ref="D41:J41"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="D43:J44"/>
-    <mergeCell ref="B46:J46"/>
-    <mergeCell ref="B50:J50"/>
     <mergeCell ref="D38:J39"/>
     <mergeCell ref="B5:J5"/>
     <mergeCell ref="F9:J9"/>
@@ -14556,6 +14548,11 @@
     <mergeCell ref="F28:J30"/>
     <mergeCell ref="F31:J31"/>
     <mergeCell ref="D36:J36"/>
+    <mergeCell ref="D41:J41"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="D43:J44"/>
+    <mergeCell ref="B46:J46"/>
+    <mergeCell ref="B50:J50"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F9:J9" location="Input_Beschaffung!A1" display="Geben Sie die übergeordneten Informationen zu Ihrem Beschaffungsfall ein. Hier können Informationen wie die erwartete jährliche Fahrleistung, die Art der Beschaffung (Kauf/Leasing) und weitere Informationen eingegeben werden." xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -14597,10 +14594,10 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E2" s="106" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2" s="125"/>
     </row>
@@ -14610,7 +14607,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -14626,7 +14623,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" s="54">
         <v>4</v>
@@ -14639,7 +14636,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7" s="102" t="str">
         <f>IF(Anbieter4=0,"",Anbieter4)</f>
@@ -14661,7 +14658,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C9" s="102"/>
       <c r="E9" s="125"/>
@@ -14669,7 +14666,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C10" s="102" t="str">
         <f>IF(Hersteller4=0,"",Hersteller4)</f>
@@ -14681,7 +14678,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C11" s="102" t="str">
         <f>IF(Modell4=0,"",Modell4)</f>
@@ -14693,7 +14690,7 @@
     </row>
     <row r="12" spans="1:6" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="56" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C12" s="102" t="str">
         <f>IF(Zusatzinfo4=0,"",Zusatzinfo4)</f>
@@ -14705,7 +14702,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B13" s="57" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="102" t="str">
         <f>IF(Antriebsart4=0,"",Antriebsart4)</f>
@@ -14716,7 +14713,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="102" t="str">
         <f>IF(Energie4=0,"",Energie4)</f>
@@ -14732,7 +14729,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B16" s="154" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -14748,9 +14745,9 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B18" s="72" t="s">
-        <v>140</v>
-      </c>
-      <c r="C18" s="288">
+        <v>139</v>
+      </c>
+      <c r="C18" s="287">
         <f>0.0057*(ReichwPHEV4/23)^3-0.0838*(ReichwPHEV4/23)^2+0.4261*(ReichwPHEV4/23)+ 0.1633</f>
         <v>0.1633</v>
       </c>
@@ -14760,37 +14757,37 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C19" s="289">
+        <v>140</v>
+      </c>
+      <c r="C19" s="288">
         <f>Verbrauch4/(1-0.9*C18)</f>
         <v>0</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E19" s="125"/>
       <c r="F19" s="125"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>142</v>
-      </c>
-      <c r="C20" s="290">
+        <v>141</v>
+      </c>
+      <c r="C20" s="289">
         <f>VerbEl_WLTP4/C18</f>
         <v>0</v>
       </c>
       <c r="D20" s="184" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E20" s="125"/>
       <c r="F20" s="125"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" s="186" t="s">
-        <v>143</v>
-      </c>
-      <c r="C21" s="291">
+        <v>142</v>
+      </c>
+      <c r="C21" s="290">
         <f>0.0021*(ReichwPHEV4/23)^3-0.0358*(ReichwPHEV4/23)^2+0.2607*(ReichwPHEV4/23)- 0.0267</f>
         <v>-2.6700000000000002E-2</v>
       </c>
@@ -14799,31 +14796,31 @@
       <c r="F21" s="125"/>
     </row>
     <row r="22" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="440" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="439" t="s">
-        <v>144</v>
-      </c>
-      <c r="C22" s="292">
+      <c r="A22" s="439" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="438" t="s">
+        <v>143</v>
+      </c>
+      <c r="C22" s="291">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
       <c r="D22" s="185" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E22" s="125"/>
       <c r="F22" s="125"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="440"/>
-      <c r="B23" s="409"/>
-      <c r="C23" s="292">
+      <c r="A23" s="439"/>
+      <c r="B23" s="408"/>
+      <c r="C23" s="291">
         <f>C20*C21</f>
         <v>0</v>
       </c>
       <c r="D23" s="183" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E23" s="125"/>
       <c r="F23" s="125"/>
@@ -14835,7 +14832,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B25" s="154" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -14848,7 +14845,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C27" s="61"/>
       <c r="D27" s="60"/>
@@ -14857,42 +14854,42 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C28" s="279">
+        <v>145</v>
+      </c>
+      <c r="C28" s="278">
         <f>IF(Antriebsart4="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie4,EnKostList,6,FALSE),0)*IF(Antriebsart4="Plug-In-Hybrid (PHEV)",VerbPHEV4,Verbrauch4)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E28" s="125"/>
       <c r="F28" s="125"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C29" s="279">
+        <v>49</v>
+      </c>
+      <c r="C29" s="278">
         <f>IF(Antriebsart4="Verbrenner",0,VLOOKUP("Strom",EnKostList,6,FALSE)*IF(Antriebsart4="Plug-In-Hybrid (PHEV)",VerbElPHEV4,VerbEl_WLTP4)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E29" s="125"/>
       <c r="F29" s="125"/>
     </row>
     <row r="30" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="C30" s="280">
+        <v>85</v>
+      </c>
+      <c r="C30" s="279">
         <f>SUM(C28:C29)</f>
         <v>0</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E30" s="125"/>
       <c r="F30" s="125"/>
@@ -14905,7 +14902,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C32" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie4)</f>
@@ -14917,70 +14914,70 @@
     </row>
     <row r="33" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B33" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C33" s="279">
+        <v>148</v>
+      </c>
+      <c r="C33" s="278">
         <f>IF(Antriebsart4="Plug-In-Hybrid (PHEV)",VerbPHEV4*VLOOKUP(Energie4,CO2List,2,FALSE)/100,CO2_4)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E33" s="125"/>
       <c r="F33" s="125"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C34" s="279">
+        <v>125</v>
+      </c>
+      <c r="C34" s="278">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E34" s="125"/>
       <c r="F34" s="125"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C35" s="287">
+        <v>150</v>
+      </c>
+      <c r="C35" s="286">
         <f>IF(Energie4="Strom",0,NOX_4*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
       <c r="D35" s="65" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E35" s="125"/>
       <c r="F35" s="125"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B36" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36" s="287">
+        <v>69</v>
+      </c>
+      <c r="C36" s="286">
         <f>IF(Energie4="Strom",0,Partikel4*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
       <c r="D36" s="65" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E36" s="125"/>
       <c r="F36" s="125"/>
     </row>
     <row r="37" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="C37" s="280">
+        <v>85</v>
+      </c>
+      <c r="C37" s="279">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
       <c r="D37" s="64" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E37" s="125"/>
       <c r="F37" s="125"/>
@@ -14993,7 +14990,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B39" s="60" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C39" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie4,IF(Antriebsart4="Plug-In-Hybrid (PHEV)","+Strom",""))</f>
@@ -15005,28 +15002,28 @@
     </row>
     <row r="40" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C40" s="279">
+        <v>148</v>
+      </c>
+      <c r="C40" s="278">
         <f>IFERROR(IF(Antriebsart4="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP4/100*Fahrleistung/1000000,IF(Antriebsart4="Verbrenner",VLOOKUP(Energie4,CO2List,3,FALSE)*Verbrauch4/100*Fahrleistung/1000000,VLOOKUP(Energie4,CO2List,3,FALSE)*VerbPHEV4/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV4/100*Fahrleistung/1000000)),0)</f>
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E40" s="125"/>
       <c r="F40" s="125"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C41" s="279">
+        <v>152</v>
+      </c>
+      <c r="C41" s="278">
         <f>C40*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E41" s="125"/>
       <c r="F41" s="125"/>
@@ -15037,7 +15034,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B43" s="154" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -15054,55 +15051,55 @@
     <row r="45" spans="1:6" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="107"/>
       <c r="B45" s="90" t="s">
+        <v>154</v>
+      </c>
+      <c r="C45" s="134" t="s">
         <v>155</v>
-      </c>
-      <c r="C45" s="134" t="s">
-        <v>156</v>
       </c>
       <c r="D45" s="62"/>
       <c r="E45" s="125"/>
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="383" t="s">
-        <v>12</v>
-      </c>
-      <c r="B46" s="437" t="s">
-        <v>149</v>
-      </c>
-      <c r="C46" s="281">
+      <c r="A46" s="369" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" s="436" t="s">
+        <v>148</v>
+      </c>
+      <c r="C46" s="280">
         <f>IF(OR(Antriebsart4="Vollelektrisch (BEV)",Antriebsart4="Plug-In-Hybrid (PHEV)"),Batterie4*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
       <c r="D46" s="131" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E46" s="127"/>
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="383"/>
-      <c r="B47" s="438"/>
-      <c r="C47" s="281" t="e">
+      <c r="A47" s="369"/>
+      <c r="B47" s="437"/>
+      <c r="C47" s="280" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D47" s="130" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E47" s="127"/>
       <c r="F47" s="125"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C48" s="279" t="e">
+        <v>158</v>
+      </c>
+      <c r="C48" s="278" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E48" s="125"/>
       <c r="F48" s="125"/>
@@ -15126,138 +15123,138 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="70" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="68" t="s">
-        <v>161</v>
-      </c>
-      <c r="C54" s="282">
+        <v>160</v>
+      </c>
+      <c r="C54" s="281">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis4,0),Gesamtpreis4*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl4,0))</f>
         <v>0</v>
       </c>
       <c r="D54" s="68" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E54" s="69"/>
       <c r="F54" s="58"/>
     </row>
     <row r="55" spans="1:6" s="71" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A55" s="305" t="s">
-        <v>12</v>
+      <c r="A55" s="304" t="s">
+        <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="C55" s="283">
+        <v>452</v>
+      </c>
+      <c r="C55" s="282">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis4-Gesamtpreis4*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>0</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E55" s="125"/>
       <c r="F55" s="73"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C56" s="283">
+        <v>81</v>
+      </c>
+      <c r="C56" s="282">
         <f>C30*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F56" s="73"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C57" s="283">
+        <v>161</v>
+      </c>
+      <c r="C57" s="282">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F57" s="58"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C58" s="283">
+        <v>152</v>
+      </c>
+      <c r="C58" s="282">
         <f>C41*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B59" s="333" t="s">
-        <v>85</v>
-      </c>
-      <c r="C59" s="334" t="e">
+      <c r="B59" s="332" t="s">
+        <v>84</v>
+      </c>
+      <c r="C59" s="333" t="e">
         <f>C48*Haltedauer</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D59" s="80" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="383" t="s">
-        <v>12</v>
-      </c>
-      <c r="B60" s="327" t="str">
+      <c r="A60" s="369" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x)</f>
         <v/>
       </c>
-      <c r="C60" s="328" t="str">
+      <c r="C60" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x4*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D60" s="327" t="str">
+      <c r="D60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", "EUR")</f>
         <v/>
       </c>
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="383"/>
-      <c r="B61" s="327" t="str">
+      <c r="A61" s="369"/>
+      <c r="B61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
       </c>
-      <c r="C61" s="328" t="str">
+      <c r="C61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y4*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D61" s="327" t="str">
+      <c r="D61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", "EUR")</f>
         <v/>
       </c>
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="383"/>
-      <c r="B62" s="327" t="str">
+      <c r="A62" s="369"/>
+      <c r="B62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
       </c>
-      <c r="C62" s="328" t="str">
+      <c r="C62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z4*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D62" s="327" t="str">
+      <c r="D62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", "EUR")</f>
         <v/>
       </c>
@@ -15265,14 +15262,14 @@
     </row>
     <row r="63" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="C63" s="284" t="e">
+        <v>85</v>
+      </c>
+      <c r="C63" s="283" t="e">
         <f>SUM(C54:C62)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D63" s="64" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E63" s="14"/>
       <c r="F63" s="58"/>
@@ -15287,26 +15284,26 @@
     </row>
     <row r="65" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B65" s="68" t="s">
-        <v>163</v>
-      </c>
-      <c r="C65" s="285" t="e">
+        <v>162</v>
+      </c>
+      <c r="C65" s="284" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D65" s="68" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="66" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B66" s="72" t="s">
-        <v>91</v>
-      </c>
-      <c r="C66" s="286">
+        <v>90</v>
+      </c>
+      <c r="C66" s="285">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D66" s="72" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E66" s="71"/>
     </row>
@@ -15357,10 +15354,10 @@
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E2" s="106" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2" s="125"/>
     </row>
@@ -15370,7 +15367,7 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -15386,7 +15383,7 @@
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" s="54">
         <v>5</v>
@@ -15399,7 +15396,7 @@
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7" s="102" t="str">
         <f>IF(Anbieter5=0,"",Anbieter5)</f>
@@ -15421,7 +15418,7 @@
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C9" s="102"/>
       <c r="E9" s="125"/>
@@ -15429,7 +15426,7 @@
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C10" s="102" t="str">
         <f>IF(Hersteller5=0,"",Hersteller5)</f>
@@ -15441,7 +15438,7 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C11" s="102" t="str">
         <f>IF(Modell5=0,"",Modell5)</f>
@@ -15453,7 +15450,7 @@
     </row>
     <row r="12" spans="2:6" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="56" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C12" s="102" t="str">
         <f>IF(Zusatzinfo5=0,"",Zusatzinfo5)</f>
@@ -15465,7 +15462,7 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="57" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="102" t="str">
         <f>IF(Antriebsart5=0,"",Antriebsart5)</f>
@@ -15476,7 +15473,7 @@
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="102" t="str">
         <f>IF(Energie5=0,"",Energie5)</f>
@@ -15494,7 +15491,7 @@
     </row>
     <row r="16" spans="2:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="154" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -15511,9 +15508,9 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B18" s="72" t="s">
-        <v>140</v>
-      </c>
-      <c r="C18" s="288">
+        <v>139</v>
+      </c>
+      <c r="C18" s="287">
         <f>0.0057*(ReichwPHEV5/23)^3-0.0838*(ReichwPHEV5/23)^2+0.4261*(ReichwPHEV5/23)+ 0.1633</f>
         <v>0.1633</v>
       </c>
@@ -15523,37 +15520,37 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C19" s="289">
+        <v>140</v>
+      </c>
+      <c r="C19" s="288">
         <f>Verbrauch5/(1-0.9*C18)</f>
         <v>0</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E19" s="125"/>
       <c r="F19" s="125"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>142</v>
-      </c>
-      <c r="C20" s="290">
+        <v>141</v>
+      </c>
+      <c r="C20" s="289">
         <f>VerbEl_WLTP5/C18</f>
         <v>0</v>
       </c>
       <c r="D20" s="184" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E20" s="125"/>
       <c r="F20" s="125"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" s="186" t="s">
-        <v>143</v>
-      </c>
-      <c r="C21" s="291">
+        <v>142</v>
+      </c>
+      <c r="C21" s="290">
         <f>0.0021*(ReichwPHEV5/23)^3-0.0358*(ReichwPHEV5/23)^2+0.2607*(ReichwPHEV5/23)- 0.0267</f>
         <v>-2.6700000000000002E-2</v>
       </c>
@@ -15562,31 +15559,31 @@
       <c r="F21" s="125"/>
     </row>
     <row r="22" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="440" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="439" t="s">
-        <v>144</v>
-      </c>
-      <c r="C22" s="292">
+      <c r="A22" s="439" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="438" t="s">
+        <v>143</v>
+      </c>
+      <c r="C22" s="291">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
       <c r="D22" s="185" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E22" s="125"/>
       <c r="F22" s="125"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="440"/>
-      <c r="B23" s="409"/>
-      <c r="C23" s="292">
+      <c r="A23" s="439"/>
+      <c r="B23" s="408"/>
+      <c r="C23" s="291">
         <f>C20*C21</f>
         <v>0</v>
       </c>
       <c r="D23" s="183" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E23" s="125"/>
       <c r="F23" s="125"/>
@@ -15598,7 +15595,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B25" s="154" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -15611,7 +15608,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C27" s="61"/>
       <c r="D27" s="60"/>
@@ -15620,42 +15617,42 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C28" s="279">
+        <v>145</v>
+      </c>
+      <c r="C28" s="278">
         <f>IF(Antriebsart5="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie5,EnKostList,6,FALSE),0)*IF(Antriebsart5="Plug-In-Hybrid (PHEV)",VerbPHEV5,Verbrauch5)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E28" s="125"/>
       <c r="F28" s="125"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C29" s="279">
+        <v>49</v>
+      </c>
+      <c r="C29" s="278">
         <f>IF(Antriebsart5="Verbrenner",0,VLOOKUP("Strom",EnKostList,6,FALSE)*IF(Antriebsart5="Plug-In-Hybrid (PHEV)",VerbElPHEV5,VerbEl_WLTP5)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E29" s="125"/>
       <c r="F29" s="125"/>
     </row>
     <row r="30" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="C30" s="280">
+        <v>85</v>
+      </c>
+      <c r="C30" s="279">
         <f>SUM(C28:C29)</f>
         <v>0</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E30" s="125"/>
       <c r="F30" s="125"/>
@@ -15668,7 +15665,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C32" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie5)</f>
@@ -15681,70 +15678,70 @@
     <row r="33" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A33" s="126"/>
       <c r="B33" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C33" s="279">
+        <v>148</v>
+      </c>
+      <c r="C33" s="278">
         <f>IF(Antriebsart5="Plug-In-Hybrid (PHEV)",VerbPHEV5*VLOOKUP(Energie5,CO2List,2,FALSE)/100,CO2_5)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E33" s="125"/>
       <c r="F33" s="125"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C34" s="279">
+        <v>125</v>
+      </c>
+      <c r="C34" s="278">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E34" s="125"/>
       <c r="F34" s="125"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C35" s="287">
+        <v>150</v>
+      </c>
+      <c r="C35" s="286">
         <f>IF(Energie5="Strom",0,NOX_5*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
       <c r="D35" s="65" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E35" s="125"/>
       <c r="F35" s="125"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B36" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36" s="287">
+        <v>69</v>
+      </c>
+      <c r="C36" s="286">
         <f>IF(Energie5="Strom",0,Partikel5*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
       <c r="D36" s="65" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E36" s="125"/>
       <c r="F36" s="125"/>
     </row>
     <row r="37" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="C37" s="280">
+        <v>85</v>
+      </c>
+      <c r="C37" s="279">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
       <c r="D37" s="64" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E37" s="125"/>
       <c r="F37" s="125"/>
@@ -15757,7 +15754,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B39" s="60" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C39" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie5,IF(Antriebsart5="Plug-In-Hybrid (PHEV)","+Strom",""))</f>
@@ -15769,28 +15766,28 @@
     </row>
     <row r="40" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C40" s="279">
+        <v>148</v>
+      </c>
+      <c r="C40" s="278">
         <f>IFERROR(IF(Antriebsart5="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP5/100*Fahrleistung/1000000,IF(Antriebsart5="Verbrenner",VLOOKUP(Energie5,CO2List,3,FALSE)*Verbrauch5/100*Fahrleistung/1000000,VLOOKUP(Energie5,CO2List,3,FALSE)*VerbPHEV5/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV5/100*Fahrleistung/1000000)),0)</f>
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E40" s="125"/>
       <c r="F40" s="125"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C41" s="279">
+        <v>152</v>
+      </c>
+      <c r="C41" s="278">
         <f>C40*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E41" s="125"/>
       <c r="F41" s="125"/>
@@ -15801,7 +15798,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B43" s="154" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -15818,55 +15815,55 @@
     <row r="45" spans="1:6" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="107"/>
       <c r="B45" s="90" t="s">
+        <v>154</v>
+      </c>
+      <c r="C45" s="134" t="s">
         <v>155</v>
-      </c>
-      <c r="C45" s="134" t="s">
-        <v>156</v>
       </c>
       <c r="D45" s="62"/>
       <c r="E45" s="125"/>
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="383" t="s">
-        <v>12</v>
-      </c>
-      <c r="B46" s="437" t="s">
-        <v>149</v>
-      </c>
-      <c r="C46" s="281">
+      <c r="A46" s="369" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" s="436" t="s">
+        <v>148</v>
+      </c>
+      <c r="C46" s="280">
         <f>IF(OR(Antriebsart5="Vollelektrisch (BEV)",Antriebsart5="Plug-In-Hybrid (PHEV)"),Batterie5*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
       <c r="D46" s="131" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E46" s="127"/>
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="383"/>
-      <c r="B47" s="438"/>
-      <c r="C47" s="281" t="e">
+      <c r="A47" s="369"/>
+      <c r="B47" s="437"/>
+      <c r="C47" s="280" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D47" s="130" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E47" s="127"/>
       <c r="F47" s="125"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C48" s="279" t="e">
+        <v>158</v>
+      </c>
+      <c r="C48" s="278" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E48" s="125"/>
       <c r="F48" s="125"/>
@@ -15890,138 +15887,138 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="70" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="68" t="s">
-        <v>161</v>
-      </c>
-      <c r="C54" s="282">
+        <v>160</v>
+      </c>
+      <c r="C54" s="281">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis5,0),Gesamtpreis5*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl5,0))</f>
         <v>0</v>
       </c>
       <c r="D54" s="68" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E54" s="69"/>
       <c r="F54" s="58"/>
     </row>
     <row r="55" spans="1:6" s="71" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A55" s="305" t="s">
-        <v>12</v>
+      <c r="A55" s="304" t="s">
+        <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="C55" s="283">
+        <v>452</v>
+      </c>
+      <c r="C55" s="282">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis5-Gesamtpreis5*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>0</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E55" s="125"/>
       <c r="F55" s="73"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C56" s="283">
+        <v>81</v>
+      </c>
+      <c r="C56" s="282">
         <f>C30*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F56" s="73"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C57" s="283">
+        <v>161</v>
+      </c>
+      <c r="C57" s="282">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F57" s="58"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C58" s="283">
+        <v>152</v>
+      </c>
+      <c r="C58" s="282">
         <f>C41*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B59" s="329" t="s">
-        <v>85</v>
-      </c>
-      <c r="C59" s="330" t="e">
+      <c r="B59" s="328" t="s">
+        <v>84</v>
+      </c>
+      <c r="C59" s="329" t="e">
         <f>C48*Haltedauer</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D59" s="329" t="s">
-        <v>60</v>
+      <c r="D59" s="328" t="s">
+        <v>59</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="383" t="s">
-        <v>12</v>
-      </c>
-      <c r="B60" s="327" t="str">
+      <c r="A60" s="369" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x)</f>
         <v/>
       </c>
-      <c r="C60" s="328" t="str">
+      <c r="C60" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x5*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D60" s="327" t="str">
+      <c r="D60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", "EUR")</f>
         <v/>
       </c>
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="383"/>
-      <c r="B61" s="327" t="str">
+      <c r="A61" s="369"/>
+      <c r="B61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
       </c>
-      <c r="C61" s="328" t="str">
+      <c r="C61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y5*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D61" s="327" t="str">
+      <c r="D61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", "EUR")</f>
         <v/>
       </c>
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="383"/>
-      <c r="B62" s="327" t="str">
+      <c r="A62" s="369"/>
+      <c r="B62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
       </c>
-      <c r="C62" s="328" t="str">
+      <c r="C62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z5*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D62" s="327" t="str">
+      <c r="D62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", "EUR")</f>
         <v/>
       </c>
@@ -16029,14 +16026,14 @@
     </row>
     <row r="63" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="C63" s="284" t="e">
+        <v>85</v>
+      </c>
+      <c r="C63" s="283" t="e">
         <f>SUM(C54:C62)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D63" s="64" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E63" s="14"/>
       <c r="F63" s="58"/>
@@ -16051,26 +16048,26 @@
     </row>
     <row r="65" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B65" s="68" t="s">
-        <v>163</v>
-      </c>
-      <c r="C65" s="285" t="e">
+        <v>162</v>
+      </c>
+      <c r="C65" s="284" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D65" s="68" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="66" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B66" s="72" t="s">
-        <v>91</v>
-      </c>
-      <c r="C66" s="286">
+        <v>90</v>
+      </c>
+      <c r="C66" s="285">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D66" s="72" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E66" s="71"/>
     </row>
@@ -16116,15 +16113,15 @@
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H2" s="106" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -16133,60 +16130,60 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C6" s="63" t="s">
+        <v>165</v>
+      </c>
+      <c r="D6" s="63" t="s">
         <v>166</v>
       </c>
-      <c r="D6" s="63" t="s">
-        <v>167</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" s="302">
+        <v>50</v>
+      </c>
+      <c r="C7" s="301">
         <v>74.027000000000001</v>
       </c>
       <c r="D7" s="10">
         <v>23.4</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="302">
+        <v>51</v>
+      </c>
+      <c r="C8" s="301">
         <v>72.787000000000006</v>
       </c>
       <c r="D8" s="10">
         <v>23.2</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C9" s="302">
+        <v>121</v>
+      </c>
+      <c r="C9" s="301">
         <v>56.220999999999997</v>
       </c>
       <c r="D9" s="10">
         <v>20.3</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="92" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
@@ -16196,7 +16193,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B12" s="154" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C12" s="93"/>
       <c r="D12" s="5"/>
@@ -16214,55 +16211,55 @@
     </row>
     <row r="14" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="110" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" s="441" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="440" t="s">
+        <v>169</v>
+      </c>
+      <c r="D14" s="440"/>
+      <c r="E14" s="441" t="s">
         <v>170</v>
       </c>
-      <c r="D14" s="441"/>
-      <c r="E14" s="442" t="s">
-        <v>171</v>
-      </c>
-      <c r="F14" s="442"/>
-      <c r="G14" s="304"/>
+      <c r="F14" s="441"/>
+      <c r="G14" s="303"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="66"/>
       <c r="B15" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C15" s="58">
         <v>1</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E15" s="136">
         <f>42.722*0.832</f>
         <v>35.544704000000003</v>
       </c>
       <c r="F15" s="111" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G15" s="111"/>
       <c r="H15" s="136"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C16" s="58">
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E16" s="136">
         <f>43.543*0.742</f>
         <v>32.308906</v>
       </c>
       <c r="F16" s="111" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G16" s="111"/>
       <c r="H16" s="136"/>
@@ -16270,54 +16267,54 @@
     <row r="17" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A17" s="66"/>
       <c r="B17" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C17" s="58">
         <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="E17" s="303">
+        <v>173</v>
+      </c>
+      <c r="E17" s="302">
         <v>46.5</v>
       </c>
       <c r="F17" s="111" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G17" s="111"/>
     </row>
     <row r="18" spans="1:37" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="92" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D18" s="106"/>
       <c r="E18" s="10"/>
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B20" s="154" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="H20" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="21" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B21" s="66"/>
       <c r="I21" s="58" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J21" s="135" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="K21" s="135"/>
       <c r="L21" s="135"/>
       <c r="M21" s="135"/>
       <c r="O21" s="137" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="P21" s="137"/>
       <c r="Q21" s="137"/>
@@ -16327,36 +16324,36 @@
     <row r="22" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B22" s="66"/>
       <c r="C22" s="63" t="s">
+        <v>165</v>
+      </c>
+      <c r="D22" s="63" t="s">
         <v>166</v>
       </c>
-      <c r="D22" s="63" t="s">
-        <v>167</v>
-      </c>
       <c r="E22" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:37" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A23" s="138" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C23" s="58">
         <v>0</v>
       </c>
-      <c r="D23" s="299" t="e">
+      <c r="D23" s="298" t="e">
         <f>SUMIFS(J24:AE24, J23:AE23, "&gt;=" &amp; Anschaffungsjahr, J23:AE23,  "&lt;" &amp; Anschaffungsjahr + ROUND(Haltedauer, 0))/ROUND(Haltedauer, 0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E23" s="74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
       <c r="I23" s="58" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J23" s="2">
         <v>2023</v>
@@ -16445,7 +16442,7 @@
     </row>
     <row r="24" spans="1:37" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B24" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C24" s="96">
         <f>C7*E15</f>
@@ -16456,18 +16453,18 @@
         <v>831.74607360000005</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I24" s="58" t="s">
-        <v>470</v>
-      </c>
-      <c r="J24" s="300">
+        <v>468</v>
+      </c>
+      <c r="J24" s="299">
         <v>445</v>
       </c>
       <c r="K24" s="96">
         <v>408</v>
       </c>
-      <c r="L24" s="301">
+      <c r="L24" s="300">
         <v>371</v>
       </c>
       <c r="M24" s="96">
@@ -16482,7 +16479,7 @@
       <c r="P24" s="96">
         <v>211.8</v>
       </c>
-      <c r="Q24" s="301">
+      <c r="Q24" s="300">
         <v>172</v>
       </c>
       <c r="R24" s="96">
@@ -16497,7 +16494,7 @@
       <c r="U24" s="96">
         <v>119.2</v>
       </c>
-      <c r="V24" s="301">
+      <c r="V24" s="300">
         <v>106</v>
       </c>
       <c r="W24" s="96">
@@ -16512,7 +16509,7 @@
       <c r="Z24" s="96">
         <v>82</v>
       </c>
-      <c r="AA24" s="301">
+      <c r="AA24" s="300">
         <v>76</v>
       </c>
       <c r="AB24" s="136">
@@ -16542,13 +16539,13 @@
       <c r="AJ24" s="136">
         <v>79.599999999999994</v>
       </c>
-      <c r="AK24" s="301">
+      <c r="AK24" s="300">
         <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:37" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B25" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C25" s="96">
         <f>C8*E16</f>
@@ -16559,12 +16556,12 @@
         <v>749.56661919999999</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26" spans="1:37" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B26" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C26" s="96">
         <f>C9*E17</f>
@@ -16575,7 +16572,7 @@
         <v>943.95</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K26" s="136"/>
     </row>
@@ -16630,25 +16627,25 @@
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q2" s="106" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="234" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="234" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="41" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="234" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="42" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16659,12 +16656,12 @@
     </row>
     <row r="44" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="267" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="I45" s="106"/>
     </row>
@@ -16674,1151 +16671,1151 @@
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B51" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B54" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B55" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B60" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B62" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B63" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B64" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B65" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B66" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B67" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B68" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B69" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B70" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B71" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B72" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>228</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B73" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B74" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B75" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>234</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B76" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B77" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B78" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B79" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B80" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="81" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B81" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="82" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B82" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="83" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B83" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="84" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B84" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="85" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B85" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="86" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B86" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="87" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B87" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>258</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="88" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B88" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="89" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B89" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B90" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>264</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="91" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B91" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="92" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B92" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="93" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B93" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="94" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B94" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="95" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B95" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="96" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B96" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="97" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B97" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="98" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B98" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="99" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B99" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="100" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B100" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="101" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B101" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="102" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B102" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="103" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B103" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="104" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B104" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>292</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="105" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B105" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="106" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B106" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="107" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B107" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="108" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B108" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="109" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B109" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>302</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="110" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B110" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="111" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B111" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>306</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="112" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B112" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>308</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="113" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B113" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>310</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="114" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B114" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="115" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B115" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="116" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B116" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="117" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B117" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="118" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B118" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="119" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B119" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="120" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B120" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="121" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B121" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="122" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B122" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="123" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B123" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="124" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B124" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="125" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B125" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="126" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B126" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D126" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="127" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B127" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="128" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B128" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="129" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B129" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="130" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B130" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="131" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B131" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="132" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B132" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="133" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B133" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="134" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B134" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="135" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B135" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="136" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B136" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="137" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B137" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="138" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B138" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B139" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B140" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="141" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B141" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="142" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B142" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="143" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B143" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="144" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B144" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="145" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B145" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="146" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B146" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="147" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B147" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B148" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="149" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B149" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D149" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="150" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B150" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D150" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="151" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B151" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="152" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B152" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="153" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B153" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D153" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="154" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B154" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="155" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B155" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="156" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B156" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="157" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B157" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="158" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B158" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="159" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B159" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="160" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B160" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="161" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B161" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="162" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B162" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="D162" s="1" t="s">
         <v>361</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="163" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B163" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="164" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B164" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>365</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="165" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B165" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>367</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="166" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B166" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="D166" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="167" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B167" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="D167" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="168" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B168" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="D168" s="1" t="s">
         <v>373</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="169" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B169" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="170" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B170" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="171" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B171" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="172" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B172" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="173" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B173" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="174" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B174" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="175" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B175" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="176" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B176" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="177" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B177" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="178" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B178" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="179" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B179" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="180" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B180" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="181" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B181" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="182" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B182" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="183" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B183" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="184" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B184" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="185" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B185" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="186" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B186" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="187" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B187" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="188" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B188" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="189" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B189" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D189" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="190" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B190" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="191" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B191" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="D191" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="D191" s="1" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="192" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B192" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="D192" s="1" t="s">
         <v>396</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -17848,7 +17845,7 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -17857,40 +17854,40 @@
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -17899,17 +17896,17 @@
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -17918,22 +17915,22 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -17942,38 +17939,38 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
@@ -17982,39 +17979,39 @@
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="5"/>
@@ -18023,17 +18020,17 @@
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
@@ -18042,12 +18039,12 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B34" s="12" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" s="12" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>
@@ -18073,171 +18070,171 @@
   <sheetData>
     <row r="2" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C2" s="132"/>
       <c r="E2" s="106" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="275" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="274" t="s">
+        <v>461</v>
+      </c>
+      <c r="C4" s="274" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C5" s="275" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="274" t="s">
+        <v>431</v>
+      </c>
+      <c r="C6" s="274" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C7" s="275" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="274" t="s">
+        <v>456</v>
+      </c>
+      <c r="C8" s="269" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C9" s="275" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" s="274" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="276" t="s">
+        <v>401</v>
+      </c>
+      <c r="C10" s="269" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="269"/>
+      <c r="C11" s="275" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" s="274" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
+      <c r="B12" s="277" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12" s="274" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C13" s="275" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="274" t="s">
+        <v>458</v>
+      </c>
+      <c r="C14" s="274" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C15" s="275" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="277" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" s="274" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" s="274" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
+      <c r="C17" s="275" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="274" t="s">
+        <v>464</v>
+      </c>
+      <c r="C18" s="274" t="s">
         <v>463</v>
       </c>
-      <c r="C4" s="275" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C5" s="276" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="275" t="s">
-        <v>433</v>
-      </c>
-      <c r="C6" s="275" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C7" s="276" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="275" t="s">
-        <v>458</v>
-      </c>
-      <c r="C8" s="270" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C9" s="276" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" s="275" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="277" t="s">
-        <v>402</v>
-      </c>
-      <c r="C10" s="270" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="270"/>
-      <c r="C11" s="276" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" s="275" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
-      <c r="B12" s="278" t="s">
-        <v>133</v>
-      </c>
-      <c r="C12" s="275" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C13" s="276" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="275" t="s">
-        <v>460</v>
-      </c>
-      <c r="C14" s="275" t="s">
+    </row>
+    <row r="19" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C19" s="275" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="15" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C15" s="276" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="278" t="s">
-        <v>127</v>
-      </c>
-      <c r="C16" s="275" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" s="275" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
-      <c r="C17" s="276" t="s">
+    <row r="20" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="274" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="18" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="275" t="s">
-        <v>466</v>
-      </c>
-      <c r="C18" s="275" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C19" s="276" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="275" t="s">
+      <c r="C20" s="274" t="s">
         <v>409</v>
       </c>
-      <c r="C20" s="275" t="s">
+    </row>
+    <row r="21" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C21" s="275" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="21" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C21" s="276" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="275" t="s">
-        <v>438</v>
-      </c>
-      <c r="C22" s="275" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C23" s="276" t="s">
+    <row r="22" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="274" t="s">
+        <v>436</v>
+      </c>
+      <c r="C22" s="274" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="24" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="275" t="s">
+    <row r="23" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C23" s="275" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="274" t="s">
+        <v>426</v>
+      </c>
+      <c r="C24" s="274" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" s="274" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
+      <c r="C25" s="275" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="274" t="s">
         <v>427</v>
       </c>
-      <c r="C24" s="275" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" s="275" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
-      <c r="C25" s="276" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="275" t="s">
+      <c r="C26" s="274" t="s">
         <v>428</v>
       </c>
-      <c r="C26" s="275" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C27" s="269" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2"/>
+    </row>
+    <row r="27" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C27" s="275" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <hyperlinks>
@@ -18283,15 +18280,15 @@
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="I2" s="106" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -18302,56 +18299,56 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="C6" s="388"/>
-      <c r="D6" s="389"/>
-      <c r="E6" s="389"/>
-      <c r="F6" s="389"/>
-      <c r="G6" s="389"/>
-      <c r="H6" s="390"/>
+        <v>455</v>
+      </c>
+      <c r="C6" s="387"/>
+      <c r="D6" s="388"/>
+      <c r="E6" s="388"/>
+      <c r="F6" s="388"/>
+      <c r="G6" s="388"/>
+      <c r="H6" s="389"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C7" s="391"/>
-      <c r="D7" s="392"/>
-      <c r="E7" s="392"/>
-      <c r="F7" s="392"/>
-      <c r="G7" s="392"/>
-      <c r="H7" s="393"/>
+      <c r="C7" s="390"/>
+      <c r="D7" s="391"/>
+      <c r="E7" s="391"/>
+      <c r="F7" s="391"/>
+      <c r="G7" s="391"/>
+      <c r="H7" s="392"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C8" s="394"/>
-      <c r="D8" s="395"/>
-      <c r="E8" s="395"/>
-      <c r="F8" s="395"/>
-      <c r="G8" s="395"/>
-      <c r="H8" s="396"/>
+      <c r="C8" s="393"/>
+      <c r="D8" s="394"/>
+      <c r="E8" s="394"/>
+      <c r="F8" s="394"/>
+      <c r="G8" s="394"/>
+      <c r="H8" s="395"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="397"/>
-      <c r="D9" s="398"/>
-      <c r="E9" s="398"/>
-      <c r="F9" s="398"/>
-      <c r="G9" s="398"/>
-      <c r="H9" s="399"/>
+        <v>22</v>
+      </c>
+      <c r="C9" s="396"/>
+      <c r="D9" s="397"/>
+      <c r="E9" s="397"/>
+      <c r="F9" s="397"/>
+      <c r="G9" s="397"/>
+      <c r="H9" s="398"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="397"/>
-      <c r="D10" s="398"/>
-      <c r="E10" s="398"/>
-      <c r="F10" s="398"/>
-      <c r="G10" s="398"/>
-      <c r="H10" s="399"/>
+        <v>23</v>
+      </c>
+      <c r="C10" s="396"/>
+      <c r="D10" s="397"/>
+      <c r="E10" s="397"/>
+      <c r="F10" s="397"/>
+      <c r="G10" s="397"/>
+      <c r="H10" s="398"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" s="150"/>
       <c r="D11" s="55"/>
@@ -18370,13 +18367,13 @@
     </row>
     <row r="13" spans="1:9" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A13" s="97" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="385"/>
-      <c r="D13" s="386"/>
+        <v>25</v>
+      </c>
+      <c r="C13" s="384"/>
+      <c r="D13" s="385"/>
       <c r="E13" s="55"/>
       <c r="F13" s="55"/>
       <c r="G13" s="55"/>
@@ -18392,11 +18389,11 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C15" s="152"/>
       <c r="D15" s="55" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E15" s="55"/>
       <c r="F15" s="55"/>
@@ -18413,7 +18410,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C17" s="153"/>
       <c r="D17" s="55"/>
@@ -18431,8 +18428,8 @@
       <c r="H18" s="55"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B19" s="298" t="s">
-        <v>424</v>
+      <c r="B19" s="297" t="s">
+        <v>423</v>
       </c>
       <c r="C19" s="151"/>
       <c r="D19" s="55"/>
@@ -18442,7 +18439,7 @@
       <c r="H19" s="55"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B20" s="297"/>
+      <c r="B20" s="296"/>
       <c r="C20" s="55"/>
       <c r="D20" s="55"/>
       <c r="E20" s="55"/>
@@ -18452,11 +18449,11 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B21" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C21" s="151"/>
       <c r="D21" s="55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E21" s="55"/>
       <c r="F21" s="55"/>
@@ -18465,45 +18462,45 @@
     </row>
     <row r="23" spans="1:14" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A23" s="97" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="387" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="384"/>
-      <c r="D23" s="384"/>
+        <v>11</v>
+      </c>
+      <c r="B23" s="386" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="383"/>
+      <c r="D23" s="383"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B24" s="387"/>
+      <c r="B24" s="386"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B25" s="176"/>
     </row>
     <row r="26" spans="1:14" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A26" s="97" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" s="176" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26" s="153"/>
       <c r="D26" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="F26" s="274">
+        <v>422</v>
+      </c>
+      <c r="F26" s="273">
         <f>Grunddaten!E38</f>
         <v>0</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B28" s="154" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
@@ -18527,17 +18524,17 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B30" s="170" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C30" s="10"/>
       <c r="D30" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F30" s="10"/>
       <c r="G30" s="10"/>
       <c r="I30" s="7"/>
       <c r="J30" s="146" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K30" s="8"/>
       <c r="L30" s="8"/>
@@ -18546,17 +18543,17 @@
     </row>
     <row r="31" spans="1:14" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A31" s="97" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31" s="171">
         <v>50</v>
       </c>
       <c r="D31" s="242"/>
       <c r="E31" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F31" s="172"/>
       <c r="G31" s="173"/>
@@ -18572,7 +18569,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B32" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C32" s="10">
         <f>100-J31</f>
@@ -18696,12 +18693,12 @@
     </row>
     <row r="2" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C2" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D2" s="2"/>
       <c r="J2" s="7"/>
       <c r="K2" s="106" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O2" s="7"/>
       <c r="P2" s="7"/>
@@ -18717,7 +18714,7 @@
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C4" s="155" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D4" s="156"/>
       <c r="E4" s="156"/>
@@ -18747,7 +18744,7 @@
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C6" s="88" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D6" s="88"/>
       <c r="E6" s="161">
@@ -18773,7 +18770,7 @@
     </row>
     <row r="7" spans="2:18" s="91" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="162" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D7" s="162"/>
       <c r="E7" s="139"/>
@@ -18793,7 +18790,7 @@
     </row>
     <row r="8" spans="2:18" s="91" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C8" s="162" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D8" s="162"/>
       <c r="E8" s="139"/>
@@ -18816,7 +18813,7 @@
     </row>
     <row r="9" spans="2:18" s="91" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C9" s="162" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D9" s="162"/>
       <c r="E9" s="140"/>
@@ -18836,7 +18833,7 @@
     </row>
     <row r="10" spans="2:18" s="91" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C10" s="162" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D10" s="162"/>
       <c r="E10" s="140"/>
@@ -18846,10 +18843,10 @@
       <c r="I10" s="140"/>
       <c r="J10" s="238"/>
       <c r="K10" s="236"/>
-      <c r="L10" s="411" t="s">
-        <v>420</v>
-      </c>
-      <c r="M10" s="411"/>
+      <c r="L10" s="410" t="s">
+        <v>419</v>
+      </c>
+      <c r="M10" s="410"/>
       <c r="N10" s="236"/>
       <c r="O10" s="164"/>
       <c r="P10" s="164"/>
@@ -18858,7 +18855,7 @@
     </row>
     <row r="11" spans="2:18" s="91" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C11" s="162" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D11" s="162"/>
       <c r="E11" s="141"/>
@@ -18867,12 +18864,12 @@
       <c r="H11" s="141"/>
       <c r="I11" s="141"/>
       <c r="J11" s="238"/>
-      <c r="K11" s="413" t="s">
-        <v>56</v>
-      </c>
-      <c r="L11" s="413"/>
-      <c r="M11" s="413"/>
-      <c r="N11" s="413"/>
+      <c r="K11" s="412" t="s">
+        <v>55</v>
+      </c>
+      <c r="L11" s="412"/>
+      <c r="M11" s="412"/>
+      <c r="N11" s="412"/>
       <c r="O11" s="164"/>
       <c r="P11" s="164"/>
       <c r="Q11" s="164"/>
@@ -18880,7 +18877,7 @@
     </row>
     <row r="12" spans="2:18" s="91" customFormat="1" ht="55.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="165" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D12" s="88"/>
       <c r="E12" s="141"/>
@@ -18889,12 +18886,12 @@
       <c r="H12" s="141"/>
       <c r="I12" s="141"/>
       <c r="J12" s="164"/>
-      <c r="K12" s="412" t="s">
-        <v>58</v>
-      </c>
-      <c r="L12" s="412"/>
-      <c r="M12" s="412"/>
-      <c r="N12" s="412"/>
+      <c r="K12" s="411" t="s">
+        <v>57</v>
+      </c>
+      <c r="L12" s="411"/>
+      <c r="M12" s="411"/>
+      <c r="N12" s="411"/>
       <c r="O12" s="164"/>
       <c r="P12" s="164"/>
       <c r="Q12" s="164"/>
@@ -18926,18 +18923,18 @@
     </row>
     <row r="14" spans="2:18" s="91" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C14" s="162" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="263" t="s">
         <v>59</v>
       </c>
-      <c r="D14" s="263" t="s">
+      <c r="E14" s="361"/>
+      <c r="F14" s="364"/>
+      <c r="G14" s="361"/>
+      <c r="H14" s="361"/>
+      <c r="I14" s="361"/>
+      <c r="J14" s="264" t="s">
         <v>60</v>
-      </c>
-      <c r="E14" s="362"/>
-      <c r="F14" s="365"/>
-      <c r="G14" s="362"/>
-      <c r="H14" s="362"/>
-      <c r="I14" s="362"/>
-      <c r="J14" s="264" t="s">
-        <v>61</v>
       </c>
       <c r="K14" s="236"/>
       <c r="L14" s="236"/>
@@ -18949,21 +18946,21 @@
       <c r="R14" s="164"/>
     </row>
     <row r="15" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="410" t="s">
+      <c r="B15" s="409" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="407" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="408" t="s">
+      <c r="D15" s="359" t="s">
         <v>63</v>
       </c>
-      <c r="D15" s="360" t="s">
-        <v>64</v>
-      </c>
-      <c r="E15" s="366"/>
+      <c r="E15" s="365"/>
       <c r="F15" s="257"/>
-      <c r="G15" s="364"/>
-      <c r="H15" s="364"/>
-      <c r="I15" s="363"/>
-      <c r="J15" s="361"/>
+      <c r="G15" s="363"/>
+      <c r="H15" s="363"/>
+      <c r="I15" s="362"/>
+      <c r="J15" s="360"/>
       <c r="K15" s="236"/>
       <c r="L15" s="236"/>
       <c r="M15" s="237"/>
@@ -18973,16 +18970,16 @@
       <c r="R15" s="164"/>
     </row>
     <row r="16" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="410"/>
-      <c r="C16" s="409"/>
+      <c r="B16" s="409"/>
+      <c r="C16" s="408"/>
       <c r="D16" s="166" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" s="358"/>
+        <v>64</v>
+      </c>
+      <c r="E16" s="357"/>
       <c r="F16" s="257"/>
       <c r="G16" s="257"/>
       <c r="H16" s="257"/>
-      <c r="I16" s="359"/>
+      <c r="I16" s="358"/>
       <c r="J16" s="164"/>
       <c r="K16" s="236"/>
       <c r="L16" s="236"/>
@@ -18994,12 +18991,12 @@
       <c r="R16" s="164"/>
     </row>
     <row r="17" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="410"/>
+      <c r="B17" s="409"/>
       <c r="C17" s="162" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="166" t="s">
         <v>66</v>
-      </c>
-      <c r="D17" s="166" t="s">
-        <v>67</v>
       </c>
       <c r="E17" s="258"/>
       <c r="F17" s="140"/>
@@ -19017,12 +19014,12 @@
       <c r="R17" s="164"/>
     </row>
     <row r="18" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="410"/>
+      <c r="B18" s="409"/>
       <c r="C18" s="162" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="166" t="s">
         <v>68</v>
-      </c>
-      <c r="D18" s="166" t="s">
-        <v>69</v>
       </c>
       <c r="E18" s="258"/>
       <c r="F18" s="140"/>
@@ -19043,12 +19040,12 @@
       <c r="R18" s="164"/>
     </row>
     <row r="19" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="410"/>
+      <c r="B19" s="409"/>
       <c r="C19" s="162" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D19" s="166" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E19" s="258"/>
       <c r="F19" s="140"/>
@@ -19066,12 +19063,12 @@
       <c r="R19" s="164"/>
     </row>
     <row r="20" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="410"/>
+      <c r="B20" s="409"/>
       <c r="C20" s="162" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="166" t="s">
         <v>71</v>
-      </c>
-      <c r="D20" s="166" t="s">
-        <v>72</v>
       </c>
       <c r="E20" s="260"/>
       <c r="F20" s="261"/>
@@ -19090,10 +19087,10 @@
     </row>
     <row r="21" spans="2:18" s="91" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C21" s="162" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" s="168" t="s">
         <v>73</v>
-      </c>
-      <c r="D21" s="168" t="s">
-        <v>74</v>
       </c>
       <c r="E21" s="257"/>
       <c r="F21" s="257"/>
@@ -19112,25 +19109,25 @@
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D22" s="228" t="s">
-        <v>75</v>
-      </c>
-      <c r="E22" s="368">
+        <v>74</v>
+      </c>
+      <c r="E22" s="367">
         <f>IF(AND(OR(Energie1="nicht verfügbar",COUNTIF(EnList1,Energie1)&lt;&gt;1),Antriebsart1&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="F22" s="368">
+      <c r="F22" s="367">
         <f>IF(AND(OR(Energie2="nicht verfügbar",COUNTIF(EnList2,Energie2)&lt;&gt;1),Antriebsart2&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="368">
+      <c r="G22" s="367">
         <f>IF(AND(OR(Energie3="nicht verfügbar",COUNTIF(EnList3,Energie3)&lt;&gt;1),Antriebsart3&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="H22" s="368">
+      <c r="H22" s="367">
         <f>IF(AND(OR(Energie4="nicht verfügbar",COUNTIF(EnList4,Energie4)&lt;&gt;1),Antriebsart4&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="I22" s="368">
+      <c r="I22" s="367">
         <f>IF(AND(OR(Energie5="nicht verfügbar",COUNTIF(EnList5,Energie5)&lt;&gt;1),Antriebsart5&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
@@ -19145,14 +19142,14 @@
     </row>
     <row r="23" spans="2:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C23" s="77" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D23" s="228"/>
-      <c r="E23" s="368"/>
-      <c r="F23" s="368"/>
-      <c r="G23" s="368"/>
-      <c r="H23" s="368"/>
-      <c r="I23" s="368"/>
+      <c r="E23" s="367"/>
+      <c r="F23" s="367"/>
+      <c r="G23" s="367"/>
+      <c r="H23" s="367"/>
+      <c r="I23" s="367"/>
       <c r="J23" s="146"/>
       <c r="O23" s="7"/>
       <c r="P23" s="7"/>
@@ -19160,12 +19157,12 @@
       <c r="R23" s="7"/>
     </row>
     <row r="24" spans="2:18" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="383" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="331"/>
-      <c r="D24" s="322" t="s">
-        <v>147</v>
+      <c r="B24" s="369" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="330"/>
+      <c r="D24" s="321" t="s">
+        <v>146</v>
       </c>
       <c r="E24" s="256"/>
       <c r="F24" s="256"/>
@@ -19179,10 +19176,10 @@
       <c r="R24" s="7"/>
     </row>
     <row r="25" spans="2:18" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="383"/>
-      <c r="C25" s="331"/>
-      <c r="D25" s="322" t="s">
-        <v>147</v>
+      <c r="B25" s="369"/>
+      <c r="C25" s="330"/>
+      <c r="D25" s="321" t="s">
+        <v>146</v>
       </c>
       <c r="E25" s="256"/>
       <c r="F25" s="256"/>
@@ -19196,10 +19193,10 @@
       <c r="R25" s="7"/>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B26" s="383"/>
-      <c r="C26" s="335"/>
-      <c r="D26" s="322" t="s">
-        <v>147</v>
+      <c r="B26" s="369"/>
+      <c r="C26" s="334"/>
+      <c r="D26" s="321" t="s">
+        <v>146</v>
       </c>
       <c r="E26" s="256"/>
       <c r="F26" s="256"/>
@@ -19214,25 +19211,25 @@
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D27" s="228" t="s">
-        <v>76</v>
-      </c>
-      <c r="E27" s="368">
+        <v>75</v>
+      </c>
+      <c r="E27" s="367">
         <f>IF(OR(AND(COUNT(E15:E21)&lt;7,Antriebsart1="Plug-In-Hybrid (PHEV)"),AND(COUNT(E16,E21)&lt;2,Antriebsart1="Vollelektrisch (BEV)"),AND(COUNT(E15,E17:E19)&lt;4,Antriebsart1="Verbrenner")),1,0)</f>
         <v>0</v>
       </c>
-      <c r="F27" s="368">
+      <c r="F27" s="367">
         <f>IF(OR(AND(COUNT(F15:F21)&lt;7,Antriebsart2="Plug-In-Hybrid (PHEV)"),AND(COUNT(F16,F21)&lt;2,Antriebsart2="Vollelektrisch (BEV)"),AND(COUNT(F15,F17:F19)&lt;4,Antriebsart2="Verbrenner")),1,0)</f>
         <v>0</v>
       </c>
-      <c r="G27" s="368">
+      <c r="G27" s="367">
         <f>IF(OR(AND(COUNT(G15:G21)&lt;7,Antriebsart3="Plug-In-Hybrid (PHEV)"),AND(COUNT(G16,G21)&lt;2,Antriebsart3="Vollelektrisch (BEV)"),AND(COUNT(G15,G17:G19)&lt;4,Antriebsart3="Verbrenner")),1,0)</f>
         <v>0</v>
       </c>
-      <c r="H27" s="368">
+      <c r="H27" s="367">
         <f>IF(OR(AND(COUNT(H15:H21)&lt;7,Antriebsart4="Plug-In-Hybrid (PHEV)"),AND(COUNT(H16,H21)&lt;2,Antriebsart4="Vollelektrisch (BEV)"),AND(COUNT(H15,H17:H19)&lt;4,Antriebsart4="Verbrenner")),1,0)</f>
         <v>0</v>
       </c>
-      <c r="I27" s="368">
+      <c r="I27" s="367">
         <f>IF(OR(AND(COUNT(I15:I21)&lt;7,Antriebsart5="Plug-In-Hybrid (PHEV)"),AND(COUNT(I16,I21)&lt;2,Antriebsart5="Vollelektrisch (BEV)"),AND(COUNT(I15,I17:I19)&lt;4,Antriebsart5="Verbrenner")),1,0)</f>
         <v>0</v>
       </c>
@@ -19246,33 +19243,33 @@
       <c r="R27" s="7"/>
     </row>
     <row r="28" spans="2:18" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E28" s="405" t="s">
+      <c r="E28" s="404" t="s">
+        <v>76</v>
+      </c>
+      <c r="F28" s="405"/>
+      <c r="G28" s="405"/>
+      <c r="H28" s="405"/>
+      <c r="I28" s="406"/>
+    </row>
+    <row r="29" spans="2:18" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E29" s="399" t="s">
         <v>77</v>
       </c>
-      <c r="F28" s="406"/>
-      <c r="G28" s="406"/>
-      <c r="H28" s="406"/>
-      <c r="I28" s="407"/>
-    </row>
-    <row r="29" spans="2:18" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E29" s="400" t="s">
-        <v>78</v>
-      </c>
-      <c r="F29" s="387"/>
-      <c r="G29" s="387"/>
-      <c r="H29" s="387"/>
-      <c r="I29" s="401"/>
+      <c r="F29" s="386"/>
+      <c r="G29" s="386"/>
+      <c r="H29" s="386"/>
+      <c r="I29" s="400"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="E30" s="402"/>
-      <c r="F30" s="403"/>
-      <c r="G30" s="403"/>
-      <c r="H30" s="403"/>
-      <c r="I30" s="404"/>
+      <c r="E30" s="401"/>
+      <c r="F30" s="402"/>
+      <c r="G30" s="402"/>
+      <c r="H30" s="402"/>
+      <c r="I30" s="403"/>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C32" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
   </sheetData>
@@ -19656,7 +19653,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="118" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C1" s="118"/>
       <c r="D1" s="118"/>
@@ -19667,10 +19664,10 @@
     </row>
     <row r="2" spans="1:10" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A2" s="97" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C2" s="227"/>
       <c r="D2" s="230" t="str">
@@ -19682,7 +19679,7 @@
       <c r="G2" s="229"/>
       <c r="H2" s="20"/>
       <c r="J2" s="106" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -19698,7 +19695,7 @@
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="18"/>
       <c r="B4" s="154" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -19713,42 +19710,42 @@
     <row r="6" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18"/>
       <c r="B6" s="12" t="s">
-        <v>457</v>
-      </c>
-      <c r="C6" s="418" t="str">
+        <v>455</v>
+      </c>
+      <c r="C6" s="417" t="str">
         <f>IF(Projektname=0,"",Projektname)</f>
         <v/>
       </c>
-      <c r="D6" s="419"/>
-      <c r="E6" s="419"/>
-      <c r="F6" s="419"/>
-      <c r="G6" s="419"/>
-      <c r="H6" s="420"/>
+      <c r="D6" s="418"/>
+      <c r="E6" s="418"/>
+      <c r="F6" s="418"/>
+      <c r="G6" s="418"/>
+      <c r="H6" s="419"/>
     </row>
     <row r="7" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18"/>
       <c r="B7" s="12"/>
-      <c r="C7" s="421"/>
-      <c r="D7" s="422"/>
-      <c r="E7" s="422"/>
-      <c r="F7" s="422"/>
-      <c r="G7" s="422"/>
-      <c r="H7" s="423"/>
+      <c r="C7" s="420"/>
+      <c r="D7" s="421"/>
+      <c r="E7" s="421"/>
+      <c r="F7" s="421"/>
+      <c r="G7" s="421"/>
+      <c r="H7" s="422"/>
     </row>
     <row r="8" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="18"/>
       <c r="B8" s="12"/>
-      <c r="C8" s="424"/>
-      <c r="D8" s="425"/>
-      <c r="E8" s="425"/>
-      <c r="F8" s="425"/>
-      <c r="G8" s="425"/>
-      <c r="H8" s="426"/>
+      <c r="C8" s="423"/>
+      <c r="D8" s="424"/>
+      <c r="E8" s="424"/>
+      <c r="F8" s="424"/>
+      <c r="G8" s="424"/>
+      <c r="H8" s="425"/>
     </row>
     <row r="9" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="18"/>
       <c r="B9" s="74" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="82" t="str">
         <f>IF(Unternehmen=0,"",Unternehmen)</f>
@@ -19763,7 +19760,7 @@
     <row r="10" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="18"/>
       <c r="B10" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="82" t="str">
         <f>IF(Zustaendig=0,"",Zustaendig)</f>
@@ -19778,13 +19775,13 @@
     <row r="11" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="18"/>
       <c r="B11" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="414" t="str">
+        <v>24</v>
+      </c>
+      <c r="C11" s="413" t="str">
         <f>IF(Datum=0,"",Datum)</f>
         <v/>
       </c>
-      <c r="D11" s="415"/>
+      <c r="D11" s="414"/>
       <c r="E11" s="79"/>
       <c r="F11" s="81"/>
       <c r="G11" s="81"/>
@@ -19795,14 +19792,14 @@
       <c r="B12" s="12"/>
       <c r="C12" s="76"/>
       <c r="E12" s="58" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F12" s="85">
         <f>Fahrleistung</f>
         <v>0</v>
       </c>
       <c r="G12" s="86" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H12" s="80"/>
     </row>
@@ -19811,14 +19808,14 @@
       <c r="B13" s="58"/>
       <c r="C13" s="77"/>
       <c r="E13" s="73" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F13" s="87">
         <f>Haltedauer</f>
         <v>0</v>
       </c>
       <c r="G13" s="86" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H13" s="80"/>
     </row>
@@ -19834,8 +19831,8 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="18"/>
-      <c r="B15" s="293" t="s">
-        <v>80</v>
+      <c r="B15" s="292" t="s">
+        <v>79</v>
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="21"/>
@@ -19847,7 +19844,7 @@
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="18"/>
       <c r="B16" s="37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C16" s="23"/>
       <c r="D16" s="24">
@@ -19894,10 +19891,10 @@
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="18"/>
       <c r="B18" s="177" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C18" s="178" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D18" s="179" t="str">
         <f>IF(FinArt="Kauf",Gesamtpreis1,"")</f>
@@ -19922,15 +19919,15 @@
       <c r="I18" s="107"/>
     </row>
     <row r="19" spans="1:9" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A19" s="321" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="338" t="str">
+      <c r="A19" s="320" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="337" t="str">
         <f>IF(FinArt="Kauf",KaufpreisRech,"Fahrzeugkosten (Leasingrate/Miete)")</f>
         <v>Fahrzeugkosten (Leasingrate/Miete)</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D19" s="41">
         <f>Erg.Fzg._1!$C$54+Erg.Fzg._1!$C$55</f>
@@ -19948,18 +19945,18 @@
         <f>Erg.Fzg._4!$C$54+Erg.Fzg._4!$C$55</f>
         <v>0</v>
       </c>
-      <c r="H19" s="337">
+      <c r="H19" s="336">
         <f>Erg.Fzg._5!$C$54+Erg.Fzg._5!$C$55</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="336"/>
+      <c r="A20" s="335"/>
       <c r="B20" s="45" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D20" s="41">
         <f>Erg.Fzg._1!$C$56</f>
@@ -19983,14 +19980,14 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="416" t="s">
-        <v>12</v>
+      <c r="A21" s="415" t="s">
+        <v>11</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D21" s="43">
         <f>Erg.Fzg._1!$C$57</f>
@@ -20014,12 +20011,12 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="416"/>
+      <c r="A22" s="415"/>
       <c r="B22" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D22" s="43">
         <f>Erg.Fzg._1!C41*Haltedauer</f>
@@ -20044,26 +20041,26 @@
       <c r="I22" s="107"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="417"/>
+      <c r="A23" s="416"/>
       <c r="B23" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" s="325" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" s="326" t="e">
+        <v>84</v>
+      </c>
+      <c r="C23" s="324" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" s="325" t="e">
         <f>Erg.Fzg._1!$C$59</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E23" s="326" t="e">
+      <c r="E23" s="325" t="e">
         <f>Erg.Fzg._2!$C$59</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F23" s="326" t="e">
+      <c r="F23" s="325" t="e">
         <f>Erg.Fzg._3!$C$59</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G23" s="326" t="e">
+      <c r="G23" s="325" t="e">
         <f>Erg.Fzg._4!$C$59</f>
         <v>#DIV/0!</v>
       </c>
@@ -20073,30 +20070,30 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="416" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" s="332" t="str">
+      <c r="A24" s="415" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="331" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x)</f>
         <v/>
       </c>
-      <c r="C24" s="323" t="str">
+      <c r="C24" s="322" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", "EUR")</f>
         <v/>
       </c>
-      <c r="D24" s="324" t="str">
+      <c r="D24" s="323" t="str">
         <f>Erg.Fzg._1!$C$60</f>
         <v/>
       </c>
-      <c r="E24" s="324" t="str">
+      <c r="E24" s="323" t="str">
         <f>Erg.Fzg._2!$C$60</f>
         <v/>
       </c>
-      <c r="F24" s="324" t="str">
+      <c r="F24" s="323" t="str">
         <f>Erg.Fzg._3!$C$60</f>
         <v/>
       </c>
-      <c r="G24" s="324" t="str">
+      <c r="G24" s="323" t="str">
         <f>Erg.Fzg._4!$C$60</f>
         <v/>
       </c>
@@ -20106,28 +20103,28 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="416"/>
-      <c r="B25" s="332" t="str">
+      <c r="A25" s="415"/>
+      <c r="B25" s="331" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
       </c>
-      <c r="C25" s="323" t="str">
+      <c r="C25" s="322" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", "EUR")</f>
         <v/>
       </c>
-      <c r="D25" s="324" t="str">
+      <c r="D25" s="323" t="str">
         <f>Erg.Fzg._1!$C$61</f>
         <v/>
       </c>
-      <c r="E25" s="324" t="str">
+      <c r="E25" s="323" t="str">
         <f>Erg.Fzg._2!$C$61</f>
         <v/>
       </c>
-      <c r="F25" s="324" t="str">
+      <c r="F25" s="323" t="str">
         <f>Erg.Fzg._3!$C$61</f>
         <v/>
       </c>
-      <c r="G25" s="324" t="str">
+      <c r="G25" s="323" t="str">
         <f>Erg.Fzg._4!$C$61</f>
         <v/>
       </c>
@@ -20138,28 +20135,28 @@
       <c r="I25" s="6"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="416"/>
-      <c r="B26" s="332" t="str">
+      <c r="A26" s="415"/>
+      <c r="B26" s="331" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
       </c>
-      <c r="C26" s="323" t="str">
+      <c r="C26" s="322" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", "EUR")</f>
         <v/>
       </c>
-      <c r="D26" s="324" t="str">
+      <c r="D26" s="323" t="str">
         <f>Erg.Fzg._1!$C$62</f>
         <v/>
       </c>
-      <c r="E26" s="324" t="str">
+      <c r="E26" s="323" t="str">
         <f>Erg.Fzg._2!$C$62</f>
         <v/>
       </c>
-      <c r="F26" s="324" t="str">
+      <c r="F26" s="323" t="str">
         <f>Erg.Fzg._3!$C$62</f>
         <v/>
       </c>
-      <c r="G26" s="324" t="str">
+      <c r="G26" s="323" t="str">
         <f>Erg.Fzg._4!$C$62</f>
         <v/>
       </c>
@@ -20171,10 +20168,10 @@
     <row r="27" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="18"/>
       <c r="B27" s="49" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C27" s="50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D27" s="51" t="e">
         <f>IF(SUM(D19:D26)=0,"",SUM(D19:D26))</f>
@@ -20200,7 +20197,7 @@
     <row r="28" spans="1:9" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="18"/>
       <c r="B28" s="75" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C28" s="50"/>
       <c r="D28" s="51" t="str">
@@ -20228,10 +20225,10 @@
     <row r="29" spans="1:9" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A29" s="18"/>
       <c r="B29" s="108" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C29" s="66" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D29" s="231">
         <f>IF(AND(COUNTIF(D19:D23,0)&gt;0,Antriebsart1="Plug-In-Hybrid (PHEV)"),1,IF(AND(COUNTIF(D19:D23,0)&gt;1,Antriebsart1&lt;&gt;0),1,0))</f>
@@ -20261,95 +20258,95 @@
     <row r="30" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="33"/>
       <c r="B30" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" s="315" t="s">
         <v>89</v>
       </c>
-      <c r="C30" s="316" t="s">
-        <v>90</v>
-      </c>
-      <c r="D30" s="314" t="e">
+      <c r="D30" s="313" t="e">
         <f>Erg.Fzg._1!$C$65</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E30" s="314" t="e">
+      <c r="E30" s="313" t="e">
         <f>Erg.Fzg._2!$C$65</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F30" s="314" t="e">
+      <c r="F30" s="313" t="e">
         <f>Erg.Fzg._3!$C$65</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G30" s="314" t="e">
+      <c r="G30" s="313" t="e">
         <f>Erg.Fzg._4!$C$65</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H30" s="315" t="e">
+      <c r="H30" s="314" t="e">
         <f>Erg.Fzg._5!$C$65</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="309"/>
+      <c r="A31" s="308"/>
       <c r="B31" s="98" t="s">
-        <v>468</v>
-      </c>
-      <c r="C31" s="317" t="s">
-        <v>90</v>
-      </c>
-      <c r="D31" s="318">
+        <v>466</v>
+      </c>
+      <c r="C31" s="316" t="s">
+        <v>89</v>
+      </c>
+      <c r="D31" s="317">
         <f>Erg.Fzg._1!$C$66</f>
         <v>0</v>
       </c>
-      <c r="E31" s="318">
+      <c r="E31" s="317">
         <f>Erg.Fzg._2!$C$66</f>
         <v>0</v>
       </c>
-      <c r="F31" s="318">
+      <c r="F31" s="317">
         <f>Erg.Fzg._3!$C$66</f>
         <v>0</v>
       </c>
-      <c r="G31" s="318">
+      <c r="G31" s="317">
         <f>Erg.Fzg._4!$C$66</f>
         <v>0</v>
       </c>
-      <c r="H31" s="319">
+      <c r="H31" s="318">
         <f>Erg.Fzg._5!$C$66</f>
         <v>0</v>
       </c>
       <c r="I31" s="91"/>
     </row>
     <row r="32" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="309"/>
-      <c r="B32" s="310" t="s">
-        <v>456</v>
-      </c>
-      <c r="C32" s="311" t="s">
-        <v>455</v>
-      </c>
-      <c r="D32" s="312" t="e">
+      <c r="A32" s="308"/>
+      <c r="B32" s="309" t="s">
+        <v>454</v>
+      </c>
+      <c r="C32" s="310" t="s">
+        <v>453</v>
+      </c>
+      <c r="D32" s="311" t="e">
         <f>SUM(D30:D31)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E32" s="312" t="e">
+      <c r="E32" s="311" t="e">
         <f t="shared" ref="E32:H32" si="2">SUM(E30:E31)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F32" s="312" t="e">
+      <c r="F32" s="311" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G32" s="312" t="e">
+      <c r="G32" s="311" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H32" s="313" t="e">
+      <c r="H32" s="312" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I32" s="91"/>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B34" s="293" t="s">
-        <v>94</v>
+      <c r="B34" s="292" t="s">
+        <v>93</v>
       </c>
       <c r="C34" s="21"/>
       <c r="D34" s="21"/>
@@ -20480,7 +20477,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="118" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C1" s="118"/>
       <c r="D1" s="118"/>
@@ -20490,11 +20487,11 @@
       <c r="H1" s="119"/>
     </row>
     <row r="2" spans="1:10" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A2" s="320" t="s">
-        <v>12</v>
+      <c r="A2" s="319" t="s">
+        <v>11</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C2" s="227"/>
       <c r="D2" s="230" t="str">
@@ -20506,7 +20503,7 @@
       <c r="G2" s="229"/>
       <c r="H2" s="20"/>
       <c r="J2" s="106" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -20522,7 +20519,7 @@
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="18"/>
       <c r="B4" s="154" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -20537,42 +20534,42 @@
     <row r="6" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18"/>
       <c r="B6" s="12" t="s">
-        <v>457</v>
-      </c>
-      <c r="C6" s="418" t="str">
+        <v>455</v>
+      </c>
+      <c r="C6" s="417" t="str">
         <f>IF(Projektname=0,"",Projektname)</f>
         <v/>
       </c>
-      <c r="D6" s="419"/>
-      <c r="E6" s="419"/>
-      <c r="F6" s="419"/>
-      <c r="G6" s="419"/>
-      <c r="H6" s="420"/>
+      <c r="D6" s="418"/>
+      <c r="E6" s="418"/>
+      <c r="F6" s="418"/>
+      <c r="G6" s="418"/>
+      <c r="H6" s="419"/>
     </row>
     <row r="7" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18"/>
       <c r="B7" s="12"/>
-      <c r="C7" s="421"/>
-      <c r="D7" s="422"/>
-      <c r="E7" s="422"/>
-      <c r="F7" s="422"/>
-      <c r="G7" s="422"/>
-      <c r="H7" s="423"/>
+      <c r="C7" s="420"/>
+      <c r="D7" s="421"/>
+      <c r="E7" s="421"/>
+      <c r="F7" s="421"/>
+      <c r="G7" s="421"/>
+      <c r="H7" s="422"/>
     </row>
     <row r="8" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="18"/>
       <c r="B8" s="12"/>
-      <c r="C8" s="424"/>
-      <c r="D8" s="425"/>
-      <c r="E8" s="425"/>
-      <c r="F8" s="425"/>
-      <c r="G8" s="425"/>
-      <c r="H8" s="426"/>
+      <c r="C8" s="423"/>
+      <c r="D8" s="424"/>
+      <c r="E8" s="424"/>
+      <c r="F8" s="424"/>
+      <c r="G8" s="424"/>
+      <c r="H8" s="425"/>
     </row>
     <row r="9" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="18"/>
       <c r="B9" s="74" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="82" t="str">
         <f>IF(Unternehmen=0,"",Unternehmen)</f>
@@ -20587,7 +20584,7 @@
     <row r="10" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="18"/>
       <c r="B10" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="82" t="str">
         <f>IF(Zustaendig=0,"",Zustaendig)</f>
@@ -20602,13 +20599,13 @@
     <row r="11" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="18"/>
       <c r="B11" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="414" t="str">
+        <v>24</v>
+      </c>
+      <c r="C11" s="413" t="str">
         <f>IF(Datum=0,"",Datum)</f>
         <v/>
       </c>
-      <c r="D11" s="415"/>
+      <c r="D11" s="414"/>
       <c r="E11" s="79"/>
       <c r="F11" s="81"/>
       <c r="G11" s="81"/>
@@ -20619,14 +20616,14 @@
       <c r="B12" s="12"/>
       <c r="C12" s="76"/>
       <c r="E12" s="58" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F12" s="85">
         <f>Fahrleistung</f>
         <v>0</v>
       </c>
       <c r="G12" s="86" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H12" s="80"/>
     </row>
@@ -20635,14 +20632,14 @@
       <c r="B13" s="58"/>
       <c r="C13" s="77"/>
       <c r="E13" s="73" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F13" s="87">
         <f>Haltedauer</f>
         <v>0</v>
       </c>
       <c r="G13" s="86" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H13" s="80"/>
     </row>
@@ -20658,8 +20655,8 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="18"/>
-      <c r="B15" s="293" t="s">
-        <v>447</v>
+      <c r="B15" s="292" t="s">
+        <v>445</v>
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="21"/>
@@ -20671,7 +20668,7 @@
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="18"/>
       <c r="B16" s="37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C16" s="23"/>
       <c r="D16" s="24">
@@ -20716,14 +20713,14 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="416" t="s">
-        <v>12</v>
+      <c r="A18" s="415" t="s">
+        <v>11</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D18" s="43">
         <f>Erg.Fzg._1!$C$57-D19</f>
@@ -20747,12 +20744,12 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="416"/>
+      <c r="A19" s="415"/>
       <c r="B19" s="27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D19" s="43">
         <f>(Erg.Fzg._1!$C$35+Erg.Fzg._1!$C$36)*Haltedauer</f>
@@ -20776,12 +20773,12 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="416"/>
+      <c r="A20" s="415"/>
       <c r="B20" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D20" s="43">
         <f>Erg.Fzg._1!C41*Haltedauer</f>
@@ -20806,12 +20803,12 @@
       <c r="I20" s="107"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="416"/>
+      <c r="A21" s="415"/>
       <c r="B21" s="29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C21" s="46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D21" s="47" t="e">
         <f>Erg.Fzg._1!$C$59</f>
@@ -20837,10 +20834,10 @@
     <row r="22" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="18"/>
       <c r="B22" s="49" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C22" s="50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D22" s="51" t="e">
         <f>IF(SUM(D18:D21)=0,"",SUM(D18:D21))</f>
@@ -20866,7 +20863,7 @@
     <row r="23" spans="1:9" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18"/>
       <c r="B23" s="75" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C23" s="50"/>
       <c r="D23" s="51" t="str">
@@ -20894,10 +20891,10 @@
     <row r="24" spans="1:9" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A24" s="18"/>
       <c r="B24" s="108" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C24" s="66" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D24" s="231">
         <f>IF(AND(COUNTIF(D18:D21,0)&gt;0,Antriebsart1="Plug-In-Hybrid (PHEV)"),1,IF(AND(COUNTIF(D18:D21,0)&gt;1,Antriebsart1="Verbrenner"),1,IF(AND(COUNTIF(D18:D21,0)&gt;2,Antriebsart1&lt;&gt;""),1,0)))</f>
@@ -20927,10 +20924,10 @@
     <row r="25" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="33"/>
       <c r="B25" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" s="31" t="s">
         <v>89</v>
-      </c>
-      <c r="C25" s="31" t="s">
-        <v>90</v>
       </c>
       <c r="D25" s="32" t="e">
         <f>Erg.Fzg._1!$C$65</f>
@@ -20956,10 +20953,10 @@
     <row r="26" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="33"/>
       <c r="B26" s="98" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C26" s="99" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D26" s="35">
         <f>Erg.Fzg._1!$C$66</f>
@@ -20985,37 +20982,37 @@
     </row>
     <row r="27" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="33"/>
-      <c r="B27" s="310" t="s">
-        <v>456</v>
-      </c>
-      <c r="C27" s="311" t="s">
-        <v>455</v>
-      </c>
-      <c r="D27" s="312" t="e">
+      <c r="B27" s="309" t="s">
+        <v>454</v>
+      </c>
+      <c r="C27" s="310" t="s">
+        <v>453</v>
+      </c>
+      <c r="D27" s="311" t="e">
         <f>SUM(D25:D26)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E27" s="312" t="e">
+      <c r="E27" s="311" t="e">
         <f t="shared" ref="E27:G27" si="2">SUM(E25:E26)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F27" s="312" t="e">
+      <c r="F27" s="311" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G27" s="312" t="e">
+      <c r="G27" s="311" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H27" s="313" t="e">
+      <c r="H27" s="312" t="e">
         <f>SUM(H25:H26)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I27" s="91"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="293" t="s">
-        <v>448</v>
+      <c r="B29" s="292" t="s">
+        <v>446</v>
       </c>
       <c r="C29" s="21"/>
       <c r="D29" s="21"/>
@@ -21146,13 +21143,13 @@
   <sheetData>
     <row r="1" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="G1" s="97" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="119"/>
       <c r="B2" s="189" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C2" s="119"/>
       <c r="D2" s="119"/>
@@ -21161,7 +21158,7 @@
       <c r="G2" s="190"/>
       <c r="H2" s="119"/>
       <c r="I2" s="106" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -21176,19 +21173,19 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="119"/>
-      <c r="B4" s="293" t="s">
-        <v>418</v>
-      </c>
-      <c r="C4" s="354"/>
-      <c r="D4" s="354"/>
-      <c r="E4" s="354"/>
-      <c r="F4" s="355"/>
+      <c r="B4" s="292" t="s">
+        <v>417</v>
+      </c>
+      <c r="C4" s="353"/>
+      <c r="D4" s="353"/>
+      <c r="E4" s="353"/>
+      <c r="F4" s="354"/>
       <c r="G4" s="190"/>
       <c r="H4" s="119"/>
     </row>
     <row r="5" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="383" t="s">
-        <v>12</v>
+      <c r="A5" s="369" t="s">
+        <v>11</v>
       </c>
       <c r="B5" s="219"/>
       <c r="C5" s="219"/>
@@ -21197,290 +21194,290 @@
       <c r="F5" s="219"/>
       <c r="G5" s="190"/>
       <c r="H5" s="119"/>
-      <c r="J5" s="427" t="s">
-        <v>421</v>
-      </c>
-      <c r="K5" s="427"/>
-      <c r="L5" s="427"/>
+      <c r="J5" s="426" t="s">
+        <v>420</v>
+      </c>
+      <c r="K5" s="426"/>
+      <c r="L5" s="426"/>
     </row>
     <row r="6" spans="1:12" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A6" s="383"/>
+      <c r="A6" s="369"/>
       <c r="B6" s="220" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="220" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="221" t="s">
         <v>96</v>
       </c>
-      <c r="C6" s="220" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="221" t="s">
+      <c r="E6" s="226" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="226" t="s">
+      <c r="F6" s="221" t="s">
         <v>98</v>
       </c>
-      <c r="F6" s="221" t="s">
+      <c r="G6" s="305" t="s">
         <v>99</v>
       </c>
-      <c r="G6" s="306" t="s">
+      <c r="H6" s="119"/>
+      <c r="J6" s="426"/>
+      <c r="K6" s="426"/>
+      <c r="L6" s="426"/>
+    </row>
+    <row r="7" spans="1:12" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="351"/>
+      <c r="B7" s="427" t="s">
         <v>100</v>
       </c>
-      <c r="H6" s="119"/>
-      <c r="J6" s="427"/>
-      <c r="K6" s="427"/>
-      <c r="L6" s="427"/>
-    </row>
-    <row r="7" spans="1:12" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="352"/>
-      <c r="B7" s="428" t="s">
-        <v>101</v>
-      </c>
       <c r="C7" s="222" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D7" s="223">
         <v>120</v>
       </c>
-      <c r="E7" s="272"/>
+      <c r="E7" s="271"/>
       <c r="F7" s="222" t="s">
-        <v>67</v>
-      </c>
-      <c r="G7" s="307">
+        <v>66</v>
+      </c>
+      <c r="G7" s="306">
         <f t="shared" ref="G7:G17" si="0">IF(ISBLANK(E7),D7,E7)</f>
         <v>120</v>
       </c>
       <c r="H7" s="119"/>
-      <c r="J7" s="427"/>
-      <c r="K7" s="427"/>
-      <c r="L7" s="427"/>
+      <c r="J7" s="426"/>
+      <c r="K7" s="426"/>
+      <c r="L7" s="426"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="352"/>
-      <c r="B8" s="429"/>
+      <c r="A8" s="351"/>
+      <c r="B8" s="428"/>
       <c r="C8" s="222" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D8" s="223">
         <v>130</v>
       </c>
-      <c r="E8" s="272"/>
+      <c r="E8" s="271"/>
       <c r="F8" s="222" t="s">
-        <v>67</v>
-      </c>
-      <c r="G8" s="307">
+        <v>66</v>
+      </c>
+      <c r="G8" s="306">
         <f t="shared" si="0"/>
         <v>130</v>
       </c>
       <c r="H8" s="119"/>
-      <c r="J8" s="427"/>
-      <c r="K8" s="427"/>
-      <c r="L8" s="427"/>
+      <c r="J8" s="426"/>
+      <c r="K8" s="426"/>
+      <c r="L8" s="426"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="352"/>
-      <c r="B9" s="430"/>
+      <c r="A9" s="351"/>
+      <c r="B9" s="429"/>
       <c r="C9" s="222" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D9" s="223">
         <v>20</v>
       </c>
-      <c r="E9" s="272"/>
+      <c r="E9" s="271"/>
       <c r="F9" s="222" t="s">
-        <v>67</v>
-      </c>
-      <c r="G9" s="307">
+        <v>66</v>
+      </c>
+      <c r="G9" s="306">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="H9" s="119"/>
-      <c r="J9" s="427"/>
-      <c r="K9" s="427"/>
-      <c r="L9" s="427"/>
+      <c r="J9" s="426"/>
+      <c r="K9" s="426"/>
+      <c r="L9" s="426"/>
     </row>
     <row r="10" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A10" s="352"/>
-      <c r="B10" s="356" t="s">
+      <c r="A10" s="351"/>
+      <c r="B10" s="355" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="222" t="s">
         <v>104</v>
       </c>
-      <c r="C10" s="222" t="s">
-        <v>105</v>
-      </c>
-      <c r="D10" s="367">
+      <c r="D10" s="366">
         <v>64</v>
       </c>
-      <c r="E10" s="272"/>
+      <c r="E10" s="271"/>
       <c r="F10" s="222" t="s">
-        <v>69</v>
-      </c>
-      <c r="G10" s="307">
+        <v>68</v>
+      </c>
+      <c r="G10" s="306">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="H10" s="119"/>
-      <c r="J10" s="427"/>
-      <c r="K10" s="427"/>
-      <c r="L10" s="427"/>
+      <c r="J10" s="426"/>
+      <c r="K10" s="426"/>
+      <c r="L10" s="426"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="352"/>
-      <c r="B11" s="356" t="s">
-        <v>106</v>
+      <c r="A11" s="351"/>
+      <c r="B11" s="355" t="s">
+        <v>105</v>
       </c>
       <c r="C11" s="222" t="s">
-        <v>105</v>
-      </c>
-      <c r="D11" s="367">
+        <v>104</v>
+      </c>
+      <c r="D11" s="366">
         <v>3.6</v>
       </c>
-      <c r="E11" s="272"/>
+      <c r="E11" s="271"/>
       <c r="F11" s="222" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11" s="307">
+        <v>68</v>
+      </c>
+      <c r="G11" s="306">
         <f t="shared" si="0"/>
         <v>3.6</v>
       </c>
       <c r="H11" s="119"/>
-      <c r="J11" s="427"/>
-      <c r="K11" s="427"/>
-      <c r="L11" s="427"/>
+      <c r="J11" s="426"/>
+      <c r="K11" s="426"/>
+      <c r="L11" s="426"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="352"/>
-      <c r="B12" s="428" t="s">
+      <c r="A12" s="351"/>
+      <c r="B12" s="427" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" s="222" t="s">
         <v>107</v>
-      </c>
-      <c r="C12" s="222" t="s">
-        <v>108</v>
       </c>
       <c r="D12" s="223">
         <v>19</v>
       </c>
-      <c r="E12" s="272"/>
+      <c r="E12" s="271"/>
       <c r="F12" s="222" t="s">
-        <v>109</v>
-      </c>
-      <c r="G12" s="307">
+        <v>108</v>
+      </c>
+      <c r="G12" s="306">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="H12" s="119"/>
-      <c r="J12" s="427"/>
-      <c r="K12" s="427"/>
-      <c r="L12" s="427"/>
+      <c r="J12" s="426"/>
+      <c r="K12" s="426"/>
+      <c r="L12" s="426"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="352"/>
-      <c r="B13" s="429"/>
+      <c r="A13" s="351"/>
+      <c r="B13" s="428"/>
       <c r="C13" s="222" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D13" s="223">
         <v>21</v>
       </c>
-      <c r="E13" s="272"/>
+      <c r="E13" s="271"/>
       <c r="F13" s="222" t="s">
-        <v>109</v>
-      </c>
-      <c r="G13" s="307">
+        <v>108</v>
+      </c>
+      <c r="G13" s="306">
         <f>IF(ISBLANK(E13),D13,E13)</f>
         <v>21</v>
       </c>
       <c r="H13" s="119"/>
-      <c r="J13" s="427"/>
-      <c r="K13" s="427"/>
-      <c r="L13" s="427"/>
+      <c r="J13" s="426"/>
+      <c r="K13" s="426"/>
+      <c r="L13" s="426"/>
     </row>
     <row r="14" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="416" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="429"/>
+      <c r="A14" s="415" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="428"/>
       <c r="C14" s="222" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D14" s="223" t="s">
-        <v>544</v>
-      </c>
-      <c r="E14" s="272"/>
+        <v>542</v>
+      </c>
+      <c r="E14" s="271"/>
       <c r="F14" s="222" t="s">
-        <v>64</v>
-      </c>
-      <c r="G14" s="307" t="str">
+        <v>63</v>
+      </c>
+      <c r="G14" s="306" t="str">
         <f>IF(ISBLANK(E14),"keine",E14)</f>
         <v>keine</v>
       </c>
       <c r="H14" s="119"/>
-      <c r="J14" s="427"/>
-      <c r="K14" s="427"/>
-      <c r="L14" s="427"/>
+      <c r="J14" s="426"/>
+      <c r="K14" s="426"/>
+      <c r="L14" s="426"/>
     </row>
     <row r="15" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="416"/>
-      <c r="B15" s="429"/>
+      <c r="A15" s="415"/>
+      <c r="B15" s="428"/>
       <c r="C15" s="222" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D15" s="223" t="s">
-        <v>544</v>
-      </c>
-      <c r="E15" s="272"/>
+        <v>542</v>
+      </c>
+      <c r="E15" s="271"/>
       <c r="F15" s="222" t="s">
-        <v>64</v>
-      </c>
-      <c r="G15" s="307" t="str">
+        <v>63</v>
+      </c>
+      <c r="G15" s="306" t="str">
         <f t="shared" ref="G15" si="1">IF(ISBLANK(E15),"keine",E15)</f>
         <v>keine</v>
       </c>
       <c r="H15" s="119"/>
-      <c r="J15" s="427"/>
-      <c r="K15" s="427"/>
-      <c r="L15" s="427"/>
+      <c r="J15" s="426"/>
+      <c r="K15" s="426"/>
+      <c r="L15" s="426"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="416"/>
-      <c r="B16" s="430"/>
+      <c r="A16" s="415"/>
+      <c r="B16" s="429"/>
       <c r="C16" s="222" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D16" s="223" t="s">
-        <v>544</v>
-      </c>
-      <c r="E16" s="272"/>
+        <v>542</v>
+      </c>
+      <c r="E16" s="271"/>
       <c r="F16" s="222" t="s">
-        <v>109</v>
-      </c>
-      <c r="G16" s="307" t="str">
+        <v>108</v>
+      </c>
+      <c r="G16" s="306" t="str">
         <f>IF(ISBLANK(E16),"keine",E16)</f>
         <v>keine</v>
       </c>
       <c r="H16" s="119"/>
-      <c r="J16" s="427"/>
-      <c r="K16" s="427"/>
-      <c r="L16" s="427"/>
+      <c r="J16" s="426"/>
+      <c r="K16" s="426"/>
+      <c r="L16" s="426"/>
     </row>
     <row r="17" spans="1:12" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A17" s="353"/>
-      <c r="B17" s="357" t="s">
-        <v>111</v>
+      <c r="A17" s="352"/>
+      <c r="B17" s="356" t="s">
+        <v>110</v>
       </c>
       <c r="C17" s="225" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D17" s="224">
         <v>60</v>
       </c>
-      <c r="E17" s="273"/>
+      <c r="E17" s="272"/>
       <c r="F17" s="225" t="s">
-        <v>72</v>
-      </c>
-      <c r="G17" s="307">
+        <v>71</v>
+      </c>
+      <c r="G17" s="306">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="H17" s="191"/>
-      <c r="J17" s="427"/>
-      <c r="K17" s="427"/>
-      <c r="L17" s="427"/>
+      <c r="J17" s="426"/>
+      <c r="K17" s="426"/>
+      <c r="L17" s="426"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="119"/>
@@ -21505,11 +21502,11 @@
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="193"/>
       <c r="B21" s="192" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C21" s="192"/>
       <c r="D21" s="193" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E21" s="193"/>
       <c r="F21" s="193"/>
@@ -21530,13 +21527,13 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="196"/>
-      <c r="B23" s="293" t="s">
-        <v>417</v>
-      </c>
-      <c r="C23" s="339"/>
-      <c r="D23" s="340"/>
-      <c r="E23" s="340"/>
-      <c r="F23" s="341"/>
+      <c r="B23" s="292" t="s">
+        <v>416</v>
+      </c>
+      <c r="C23" s="338"/>
+      <c r="D23" s="339"/>
+      <c r="E23" s="339"/>
+      <c r="F23" s="340"/>
       <c r="G23" s="194"/>
       <c r="H23" s="195"/>
       <c r="I23" s="195"/>
@@ -21544,9 +21541,9 @@
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="196"/>
       <c r="B24" s="6"/>
-      <c r="C24" s="327"/>
+      <c r="C24" s="326"/>
       <c r="D24" s="6"/>
-      <c r="E24" s="327"/>
+      <c r="E24" s="326"/>
       <c r="F24" s="208"/>
       <c r="G24" s="194"/>
       <c r="H24" s="195"/>
@@ -21554,16 +21551,16 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="196"/>
-      <c r="B25" s="346" t="s">
-        <v>49</v>
-      </c>
-      <c r="C25" s="327"/>
-      <c r="D25" s="296" t="s">
-        <v>114</v>
-      </c>
-      <c r="E25" s="347"/>
-      <c r="F25" s="295" t="s">
-        <v>99</v>
+      <c r="B25" s="345" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="326"/>
+      <c r="D25" s="295" t="s">
+        <v>113</v>
+      </c>
+      <c r="E25" s="346"/>
+      <c r="F25" s="294" t="s">
+        <v>98</v>
       </c>
       <c r="G25" s="194"/>
       <c r="H25" s="195"/>
@@ -21572,26 +21569,26 @@
     <row r="26" spans="1:12" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A26" s="196"/>
       <c r="B26" s="6"/>
-      <c r="C26" s="327"/>
+      <c r="C26" s="326"/>
       <c r="D26" s="209"/>
       <c r="E26" s="210" t="s">
-        <v>98</v>
-      </c>
-      <c r="F26" s="294"/>
-      <c r="G26" s="308" t="s">
+        <v>97</v>
+      </c>
+      <c r="F26" s="293"/>
+      <c r="G26" s="307" t="s">
+        <v>114</v>
+      </c>
+      <c r="H26" s="198" t="s">
         <v>115</v>
       </c>
-      <c r="H26" s="198" t="s">
+      <c r="I26" s="255" t="s">
         <v>116</v>
-      </c>
-      <c r="I26" s="255" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="204"/>
       <c r="B27" s="212" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C27" s="213"/>
       <c r="D27" s="214">
@@ -21599,21 +21596,21 @@
       </c>
       <c r="E27" s="243"/>
       <c r="F27" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="G27" s="308">
+        <v>118</v>
+      </c>
+      <c r="G27" s="307">
         <f>IF(ISNUMBER(E27),E27,D27)/100</f>
         <v>0.41399999999999998</v>
       </c>
       <c r="H27" s="199" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="I27" s="254"/>
     </row>
     <row r="28" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="204"/>
       <c r="B28" s="215" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C28" s="211"/>
       <c r="D28" s="214">
@@ -21621,27 +21618,27 @@
       </c>
       <c r="E28" s="243"/>
       <c r="F28" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="G28" s="308">
+        <v>118</v>
+      </c>
+      <c r="G28" s="307">
         <f>IF(ISNUMBER(E28),E28,D28)/100</f>
         <v>0.59</v>
       </c>
       <c r="H28" s="199" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="I28" s="254"/>
     </row>
     <row r="29" spans="1:12" ht="14.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="205"/>
       <c r="B29" s="216" t="s">
-        <v>50</v>
-      </c>
-      <c r="C29" s="348"/>
-      <c r="D29" s="349"/>
-      <c r="E29" s="350"/>
+        <v>49</v>
+      </c>
+      <c r="C29" s="347"/>
+      <c r="D29" s="348"/>
+      <c r="E29" s="349"/>
       <c r="F29" s="208"/>
-      <c r="G29" s="308">
+      <c r="G29" s="307">
         <f>G27*Input_Beschaffung!J31/100+G28*(1-Input_Beschaffung!J31/100)</f>
         <v>0.502</v>
       </c>
@@ -21649,53 +21646,53 @@
       <c r="I29" s="254"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="433"/>
+      <c r="A30" s="432"/>
       <c r="B30" s="212" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C30" s="213"/>
-      <c r="D30" s="271">
+      <c r="D30" s="270">
         <v>1.6719999999999999</v>
       </c>
       <c r="E30" s="243"/>
       <c r="F30" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="G30" s="308">
+        <v>120</v>
+      </c>
+      <c r="G30" s="307">
         <f t="shared" ref="G30:G32" si="2">IF(ISNUMBER(E30),E30,D30)</f>
         <v>1.6719999999999999</v>
       </c>
       <c r="H30" s="199" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="I30" s="254"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="433"/>
+      <c r="A31" s="432"/>
       <c r="B31" s="212" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C31" s="213"/>
-      <c r="D31" s="271">
+      <c r="D31" s="270">
         <v>1.788</v>
       </c>
       <c r="E31" s="243"/>
       <c r="F31" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="G31" s="308">
+        <v>120</v>
+      </c>
+      <c r="G31" s="307">
         <f t="shared" si="2"/>
         <v>1.788</v>
       </c>
       <c r="H31" s="199" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="I31" s="254"/>
     </row>
     <row r="32" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A32" s="205"/>
       <c r="B32" s="212" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C32" s="213"/>
       <c r="D32" s="217">
@@ -21703,14 +21700,14 @@
       </c>
       <c r="E32" s="243"/>
       <c r="F32" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="G32" s="308">
+        <v>122</v>
+      </c>
+      <c r="G32" s="307">
         <f t="shared" si="2"/>
         <v>1.3</v>
       </c>
       <c r="H32" s="199" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="I32" s="254"/>
     </row>
@@ -21738,28 +21735,28 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="193"/>
-      <c r="B35" s="293" t="s">
-        <v>124</v>
-      </c>
-      <c r="C35" s="339"/>
-      <c r="D35" s="340"/>
-      <c r="E35" s="340"/>
-      <c r="F35" s="341"/>
+      <c r="B35" s="292" t="s">
+        <v>123</v>
+      </c>
+      <c r="C35" s="338"/>
+      <c r="D35" s="339"/>
+      <c r="E35" s="339"/>
+      <c r="F35" s="340"/>
       <c r="G35" s="201"/>
       <c r="H35" s="201"/>
       <c r="I35" s="201"/>
     </row>
     <row r="36" spans="1:9" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="193"/>
-      <c r="B36" s="434" t="s">
-        <v>125</v>
-      </c>
-      <c r="C36" s="435"/>
-      <c r="D36" s="435"/>
-      <c r="E36" s="435"/>
-      <c r="F36" s="436"/>
-      <c r="G36" s="308" t="s">
-        <v>115</v>
+      <c r="B36" s="433" t="s">
+        <v>124</v>
+      </c>
+      <c r="C36" s="434"/>
+      <c r="D36" s="434"/>
+      <c r="E36" s="434"/>
+      <c r="F36" s="435"/>
+      <c r="G36" s="307" t="s">
+        <v>114</v>
       </c>
       <c r="H36" s="202"/>
       <c r="I36" s="202"/>
@@ -21767,78 +21764,78 @@
     <row r="37" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A37" s="193"/>
       <c r="B37" s="6"/>
-      <c r="C37" s="327"/>
-      <c r="D37" s="327"/>
-      <c r="E37" s="342" t="s">
+      <c r="C37" s="326"/>
+      <c r="D37" s="326"/>
+      <c r="E37" s="341" t="s">
+        <v>97</v>
+      </c>
+      <c r="F37" s="342" t="s">
         <v>98</v>
       </c>
-      <c r="F37" s="343" t="s">
-        <v>99</v>
-      </c>
-      <c r="G37" s="308"/>
+      <c r="G37" s="307"/>
       <c r="H37" s="195"/>
       <c r="I37" s="195"/>
     </row>
     <row r="38" spans="1:9" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A38" s="207"/>
       <c r="B38" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="C38" s="327"/>
+        <v>125</v>
+      </c>
+      <c r="C38" s="326"/>
       <c r="D38" s="218">
         <f>IF(KostTHGVorgabe="(Niedrig) 250", 250, 860)</f>
         <v>860</v>
       </c>
       <c r="E38" s="243"/>
       <c r="F38" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="G38" s="308">
+        <v>35</v>
+      </c>
+      <c r="G38" s="307">
         <f>IF(ISNUMBER(E38),E38,D38)</f>
         <v>860</v>
       </c>
       <c r="H38" s="199" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I38" s="254"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="193"/>
       <c r="B39" s="6"/>
-      <c r="C39" s="327"/>
-      <c r="D39" s="344"/>
-      <c r="E39" s="344"/>
-      <c r="F39" s="345"/>
-      <c r="G39" s="308"/>
+      <c r="C39" s="326"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="344"/>
+      <c r="G39" s="307"/>
       <c r="H39" s="195"/>
       <c r="I39" s="195"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="193"/>
       <c r="B40" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C40" s="327"/>
+        <v>127</v>
+      </c>
+      <c r="C40" s="326"/>
       <c r="D40" s="218">
         <v>0.02</v>
       </c>
       <c r="E40" s="243"/>
       <c r="F40" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="G40" s="308">
+        <v>128</v>
+      </c>
+      <c r="G40" s="307">
         <f>IF(ISNUMBER(E40),E40,D40)</f>
         <v>0.02</v>
       </c>
       <c r="H40" s="199" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I40" s="254"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="193"/>
       <c r="B41" s="215" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C41" s="72"/>
       <c r="D41" s="218">
@@ -21846,14 +21843,14 @@
       </c>
       <c r="E41" s="243"/>
       <c r="F41" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="G41" s="308">
+        <v>128</v>
+      </c>
+      <c r="G41" s="307">
         <f>IF(ISNUMBER(E41),E41,D41)</f>
         <v>0.15</v>
       </c>
       <c r="H41" s="199" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I41" s="254"/>
     </row>
@@ -21864,7 +21861,7 @@
       <c r="D42" s="194"/>
       <c r="E42" s="194"/>
       <c r="F42" s="193"/>
-      <c r="G42" s="308"/>
+      <c r="G42" s="307"/>
       <c r="H42" s="195"/>
       <c r="I42" s="195"/>
     </row>
@@ -21875,49 +21872,49 @@
       <c r="D43" s="193"/>
       <c r="E43" s="193"/>
       <c r="F43" s="193"/>
-      <c r="G43" s="308"/>
+      <c r="G43" s="307"/>
       <c r="H43" s="194"/>
       <c r="I43" s="194"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="193"/>
-      <c r="B44" s="293" t="s">
-        <v>131</v>
-      </c>
-      <c r="C44" s="340"/>
-      <c r="D44" s="340"/>
-      <c r="E44" s="340"/>
-      <c r="F44" s="351"/>
-      <c r="G44" s="308"/>
+      <c r="B44" s="292" t="s">
+        <v>130</v>
+      </c>
+      <c r="C44" s="339"/>
+      <c r="D44" s="339"/>
+      <c r="E44" s="339"/>
+      <c r="F44" s="350"/>
+      <c r="G44" s="307"/>
       <c r="H44" s="193"/>
       <c r="I44" s="193"/>
     </row>
     <row r="45" spans="1:9" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A45" s="193"/>
-      <c r="B45" s="431" t="s">
-        <v>422</v>
-      </c>
-      <c r="C45" s="432"/>
+      <c r="B45" s="430" t="s">
+        <v>421</v>
+      </c>
+      <c r="C45" s="431"/>
       <c r="D45" s="218">
         <v>84</v>
       </c>
       <c r="E45" s="243"/>
       <c r="F45" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="G45" s="308">
+        <v>131</v>
+      </c>
+      <c r="G45" s="307">
         <f>IF(ISNUMBER(E45),E45,D45)</f>
         <v>84</v>
       </c>
       <c r="H45" s="199" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I45" s="254"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="193"/>
       <c r="B46" s="246" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C46" s="247"/>
       <c r="D46" s="247"/>
@@ -22032,10 +22029,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E2" s="106" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="106"/>
@@ -22045,7 +22042,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C4" s="89"/>
       <c r="D4" s="89"/>
@@ -22059,7 +22056,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" s="54">
         <v>1</v>
@@ -22071,7 +22068,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7" s="102" t="str">
         <f>IF(Anbieter1=0,"",Anbieter1)</f>
@@ -22091,14 +22088,14 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C9" s="102"/>
       <c r="F9" s="125"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C10" s="102" t="str">
         <f>IF(Hersteller1=0,"",Hersteller1)</f>
@@ -22109,7 +22106,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C11" s="102" t="str">
         <f>IF(Modell1=0,"",Modell1)</f>
@@ -22120,7 +22117,7 @@
     </row>
     <row r="12" spans="1:7" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="56" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C12" s="102" t="str">
         <f>IF(Zusatzinfo1=0,"",Zusatzinfo1)</f>
@@ -22131,7 +22128,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" s="57" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="102" t="str">
         <f>IF(Antriebsart1=0,"",Antriebsart1)</f>
@@ -22142,7 +22139,7 @@
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="107"/>
       <c r="B14" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="102" t="str">
         <f>IF(Energie1=0,"",Energie1)</f>
@@ -22159,7 +22156,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B16" s="154" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -22173,9 +22170,9 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B18" s="72" t="s">
-        <v>140</v>
-      </c>
-      <c r="C18" s="288">
+        <v>139</v>
+      </c>
+      <c r="C18" s="287">
         <f>0.0057*(ReichwPHEV1/23)^3-0.0838*(ReichwPHEV1/23)^2+0.4261*(ReichwPHEV1/23)+ 0.1633</f>
         <v>0.1633</v>
       </c>
@@ -22184,35 +22181,35 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C19" s="289">
+        <v>140</v>
+      </c>
+      <c r="C19" s="288">
         <f>Verbrauch1/(1-0.9*C18)</f>
         <v>0</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F19" s="125"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>142</v>
-      </c>
-      <c r="C20" s="290">
+        <v>141</v>
+      </c>
+      <c r="C20" s="289">
         <f>VerbEl_WLTP1/C18</f>
         <v>0</v>
       </c>
       <c r="D20" s="184" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F20" s="125"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" s="186" t="s">
-        <v>143</v>
-      </c>
-      <c r="C21" s="291">
+        <v>142</v>
+      </c>
+      <c r="C21" s="290">
         <f>0.0021*(ReichwPHEV1/23)^3-0.0358*(ReichwPHEV1/23)^2+0.2607*(ReichwPHEV1/23)- 0.0267</f>
         <v>-2.6700000000000002E-2</v>
       </c>
@@ -22220,30 +22217,30 @@
       <c r="F21" s="125"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="440" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="439" t="s">
-        <v>144</v>
-      </c>
-      <c r="C22" s="292">
+      <c r="A22" s="439" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="438" t="s">
+        <v>143</v>
+      </c>
+      <c r="C22" s="291">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
       <c r="D22" s="185" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F22" s="125"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="440"/>
-      <c r="B23" s="409"/>
-      <c r="C23" s="292">
+      <c r="A23" s="439"/>
+      <c r="B23" s="408"/>
+      <c r="C23" s="291">
         <f>C20*C21</f>
         <v>0</v>
       </c>
       <c r="D23" s="183" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F23" s="125"/>
     </row>
@@ -22254,7 +22251,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B25" s="154" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C25" s="89"/>
       <c r="D25" s="89"/>
@@ -22265,7 +22262,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C27" s="61"/>
       <c r="D27" s="60"/>
@@ -22273,39 +22270,39 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C28" s="279">
+        <v>145</v>
+      </c>
+      <c r="C28" s="278">
         <f>IF(Antriebsart1="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie1,EnKostList,6,FALSE),0)*IF(Antriebsart1="Plug-In-Hybrid (PHEV)",VerbPHEV1,Verbrauch1)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F28" s="125"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C29" s="279">
+        <v>49</v>
+      </c>
+      <c r="C29" s="278">
         <f>IF(Antriebsart1="Verbrenner",0,VLOOKUP("Strom",EnKostList,6,FALSE)*IF(Antriebsart1="Plug-In-Hybrid (PHEV)",VerbElPHEV1,VerbEl_WLTP1)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="C30" s="280">
+        <v>85</v>
+      </c>
+      <c r="C30" s="279">
         <f>SUM(C28:C29)</f>
         <v>0</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="14.4" thickTop="1" x14ac:dyDescent="0.25">
@@ -22314,7 +22311,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C32" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie1)</f>
@@ -22325,63 +22322,63 @@
     </row>
     <row r="33" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B33" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C33" s="279">
+        <v>148</v>
+      </c>
+      <c r="C33" s="278">
         <f>IF(Antriebsart1="Plug-In-Hybrid (PHEV)",VerbPHEV1*VLOOKUP(Energie1,CO2List,2,FALSE)/100,CO2_1)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F33" s="107"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C34" s="279">
+        <v>125</v>
+      </c>
+      <c r="C34" s="278">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C35" s="279">
+        <v>150</v>
+      </c>
+      <c r="C35" s="278">
         <f>IF(Energie1="Strom",0,NOX_1*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36" s="279">
+        <v>69</v>
+      </c>
+      <c r="C36" s="278">
         <f>IF(Energie1="Strom",0,Partikel1*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="C37" s="280">
+        <v>85</v>
+      </c>
+      <c r="C37" s="279">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
       <c r="D37" s="64" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="14.4" thickTop="1" x14ac:dyDescent="0.25">
@@ -22389,7 +22386,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B39" s="60" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C39" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie1,IF(Antriebsart1="Plug-In-Hybrid (PHEV)","+Strom",""))</f>
@@ -22399,32 +22396,32 @@
     </row>
     <row r="40" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C40" s="279">
+        <v>148</v>
+      </c>
+      <c r="C40" s="278">
         <f>IFERROR(IF(Antriebsart1="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP1/100*Fahrleistung/1000000,IF(Antriebsart1="Verbrenner",VLOOKUP(Energie1,CO2List,3,FALSE)*Verbrauch1/100*Fahrleistung/1000000,VLOOKUP(Energie1,CO2List,3,FALSE)*VerbPHEV1/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV1/100*Fahrleistung/1000000)),0)</f>
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F40" s="107"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C41" s="279">
+        <v>152</v>
+      </c>
+      <c r="C41" s="278">
         <f>C40*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B43" s="154" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C43" s="89"/>
       <c r="D43" s="89"/>
@@ -22438,53 +22435,53 @@
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="107"/>
       <c r="B45" s="90" t="s">
+        <v>154</v>
+      </c>
+      <c r="C45" s="134" t="s">
         <v>155</v>
       </c>
-      <c r="C45" s="134" t="s">
-        <v>156</v>
-      </c>
       <c r="D45" s="62"/>
     </row>
     <row r="46" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="383" t="s">
-        <v>12</v>
-      </c>
-      <c r="B46" s="437" t="s">
-        <v>149</v>
-      </c>
-      <c r="C46" s="281">
+      <c r="A46" s="369" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" s="436" t="s">
+        <v>148</v>
+      </c>
+      <c r="C46" s="280">
         <f>IF(OR(Antriebsart1="Vollelektrisch (BEV)",Antriebsart1="Plug-In-Hybrid (PHEV)"),Batterie1*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
       <c r="D46" s="131" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E46" s="127"/>
       <c r="F46" s="107"/>
     </row>
     <row r="47" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="383"/>
-      <c r="B47" s="438"/>
-      <c r="C47" s="281" t="e">
+      <c r="A47" s="369"/>
+      <c r="B47" s="437"/>
+      <c r="C47" s="280" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D47" s="130" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E47" s="127"/>
       <c r="F47" s="107"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C48" s="279" t="e">
+        <v>158</v>
+      </c>
+      <c r="C48" s="278" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -22503,135 +22500,135 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B54" s="68" t="s">
-        <v>161</v>
-      </c>
-      <c r="C54" s="282">
+        <v>160</v>
+      </c>
+      <c r="C54" s="281">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis1,0),Gesamtpreis1*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl1,0))</f>
         <v>0</v>
       </c>
       <c r="D54" s="68" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F54" s="58"/>
     </row>
     <row r="55" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A55" s="305" t="s">
-        <v>12</v>
+      <c r="A55" s="304" t="s">
+        <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="C55" s="283">
+        <v>452</v>
+      </c>
+      <c r="C55" s="282">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis1-Gesamtpreis1*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>0</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F55" s="58"/>
     </row>
     <row r="56" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C56" s="283">
+        <v>81</v>
+      </c>
+      <c r="C56" s="282">
         <f>C30*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F56" s="58"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C57" s="283">
+        <v>161</v>
+      </c>
+      <c r="C57" s="282">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F57" s="58"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C58" s="283">
+        <v>152</v>
+      </c>
+      <c r="C58" s="282">
         <f>C41*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B59" s="329" t="s">
-        <v>85</v>
-      </c>
-      <c r="C59" s="330" t="e">
+      <c r="B59" s="328" t="s">
+        <v>84</v>
+      </c>
+      <c r="C59" s="329" t="e">
         <f>C48*Haltedauer</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D59" s="329" t="s">
-        <v>60</v>
+      <c r="D59" s="328" t="s">
+        <v>59</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="383" t="s">
-        <v>12</v>
-      </c>
-      <c r="B60" s="327" t="str">
+      <c r="A60" s="369" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x)</f>
         <v/>
       </c>
-      <c r="C60" s="328" t="str">
+      <c r="C60" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x1*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D60" s="327" t="str">
+      <c r="D60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", "EUR")</f>
         <v/>
       </c>
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="383"/>
-      <c r="B61" s="327" t="str">
+      <c r="A61" s="369"/>
+      <c r="B61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
       </c>
-      <c r="C61" s="328" t="str">
+      <c r="C61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y1*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D61" s="327" t="str">
+      <c r="D61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", "EUR")</f>
         <v/>
       </c>
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="383"/>
-      <c r="B62" s="327" t="str">
+      <c r="A62" s="369"/>
+      <c r="B62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
       </c>
-      <c r="C62" s="328" t="str">
+      <c r="C62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z1*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D62" s="327" t="str">
+      <c r="D62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", "EUR")</f>
         <v/>
       </c>
@@ -22639,14 +22636,14 @@
     </row>
     <row r="63" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="C63" s="284" t="e">
+        <v>85</v>
+      </c>
+      <c r="C63" s="283" t="e">
         <f>SUM(C54:C62)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D63" s="64" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F63" s="58"/>
     </row>
@@ -22655,26 +22652,26 @@
     </row>
     <row r="65" spans="2:4" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B65" s="68" t="s">
-        <v>163</v>
-      </c>
-      <c r="C65" s="285" t="e">
+        <v>162</v>
+      </c>
+      <c r="C65" s="284" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D65" s="68" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="66" spans="2:4" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B66" s="72" t="s">
-        <v>91</v>
-      </c>
-      <c r="C66" s="286">
+        <v>90</v>
+      </c>
+      <c r="C66" s="285">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D66" s="72" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -22724,10 +22721,10 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E2" s="106" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2" s="125"/>
     </row>
@@ -22737,7 +22734,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -22753,7 +22750,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" s="54">
         <v>2</v>
@@ -22766,7 +22763,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7" s="102" t="str">
         <f>IF(Anbieter2=0,"",Anbieter2)</f>
@@ -22788,7 +22785,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C9" s="102"/>
       <c r="E9" s="125"/>
@@ -22796,7 +22793,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C10" s="102" t="str">
         <f>IF(Hersteller2=0,"",Hersteller2)</f>
@@ -22808,7 +22805,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C11" s="102" t="str">
         <f>IF(Modell2=0,"",Modell2)</f>
@@ -22820,7 +22817,7 @@
     </row>
     <row r="12" spans="1:6" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="56" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C12" s="102" t="str">
         <f>IF(Zusatzinfo2=0,"",Zusatzinfo2)</f>
@@ -22832,7 +22829,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B13" s="57" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="102" t="str">
         <f>IF(Antriebsart2=0,"",Antriebsart2)</f>
@@ -22843,7 +22840,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="102" t="str">
         <f>IF(Energie2=0,"",Energie2)</f>
@@ -22859,7 +22856,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B16" s="154" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -22875,9 +22872,9 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B18" s="72" t="s">
-        <v>140</v>
-      </c>
-      <c r="C18" s="288">
+        <v>139</v>
+      </c>
+      <c r="C18" s="287">
         <f>0.0057*(ReichwPHEV2/23)^3-0.0838*(ReichwPHEV2/23)^2+0.4261*(ReichwPHEV2/23)+ 0.1633</f>
         <v>0.1633</v>
       </c>
@@ -22887,37 +22884,37 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C19" s="289">
+        <v>140</v>
+      </c>
+      <c r="C19" s="288">
         <f>Verbrauch2/(1-0.9*C18)</f>
         <v>0</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E19" s="125"/>
       <c r="F19" s="125"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>142</v>
-      </c>
-      <c r="C20" s="290">
+        <v>141</v>
+      </c>
+      <c r="C20" s="289">
         <f>VerbEl_WLTP2/C18</f>
         <v>0</v>
       </c>
       <c r="D20" s="184" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E20" s="125"/>
       <c r="F20" s="125"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" s="186" t="s">
-        <v>143</v>
-      </c>
-      <c r="C21" s="291">
+        <v>142</v>
+      </c>
+      <c r="C21" s="290">
         <f>0.0021*(ReichwPHEV2/23)^3-0.0358*(ReichwPHEV2/23)^2+0.2607*(ReichwPHEV2/23)- 0.0267</f>
         <v>-2.6700000000000002E-2</v>
       </c>
@@ -22926,31 +22923,31 @@
       <c r="F21" s="125"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="440" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="439" t="s">
-        <v>144</v>
-      </c>
-      <c r="C22" s="292">
+      <c r="A22" s="439" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="438" t="s">
+        <v>143</v>
+      </c>
+      <c r="C22" s="291">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
       <c r="D22" s="185" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E22" s="125"/>
       <c r="F22" s="125"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="440"/>
-      <c r="B23" s="409"/>
-      <c r="C23" s="292">
+      <c r="A23" s="439"/>
+      <c r="B23" s="408"/>
+      <c r="C23" s="291">
         <f>C20*C21</f>
         <v>0</v>
       </c>
       <c r="D23" s="183" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E23" s="125"/>
       <c r="F23" s="125"/>
@@ -22962,7 +22959,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B25" s="154" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -22975,7 +22972,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C27" s="61"/>
       <c r="D27" s="60"/>
@@ -22984,42 +22981,42 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C28" s="279">
+        <v>145</v>
+      </c>
+      <c r="C28" s="278">
         <f>IF(Antriebsart2="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie2,EnKostList,6,FALSE),0)*IF(Antriebsart2="Plug-In-Hybrid (PHEV)",VerbPHEV2,Verbrauch2)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E28" s="125"/>
       <c r="F28" s="125"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C29" s="279">
+        <v>49</v>
+      </c>
+      <c r="C29" s="278">
         <f>IF(Antriebsart2="Verbrenner",0,VLOOKUP("Strom",EnKostList,6,FALSE)*IF(Antriebsart2="Plug-In-Hybrid (PHEV)",VerbElPHEV2,VerbEl_WLTP2)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E29" s="125"/>
       <c r="F29" s="125"/>
     </row>
     <row r="30" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="C30" s="280">
+        <v>85</v>
+      </c>
+      <c r="C30" s="279">
         <f>SUM(C28:C29)</f>
         <v>0</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E30" s="125"/>
       <c r="F30" s="125"/>
@@ -23032,7 +23029,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C32" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie2)</f>
@@ -23044,70 +23041,70 @@
     </row>
     <row r="33" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B33" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C33" s="279">
+        <v>148</v>
+      </c>
+      <c r="C33" s="278">
         <f>IF(Antriebsart2="Plug-In-Hybrid (PHEV)",VerbPHEV2*VLOOKUP(Energie2,CO2List,2,FALSE)/100,CO2_2)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E33" s="125"/>
       <c r="F33" s="125"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C34" s="279">
+        <v>125</v>
+      </c>
+      <c r="C34" s="278">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E34" s="125"/>
       <c r="F34" s="125"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C35" s="287">
+        <v>150</v>
+      </c>
+      <c r="C35" s="286">
         <f>IF(Energie2="Strom",0,NOX_2*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
       <c r="D35" s="65" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E35" s="125"/>
       <c r="F35" s="125"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B36" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36" s="287">
+        <v>69</v>
+      </c>
+      <c r="C36" s="286">
         <f>IF(Energie2="Strom",0,Partikel2*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
       <c r="D36" s="65" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E36" s="125"/>
       <c r="F36" s="125"/>
     </row>
     <row r="37" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="C37" s="280">
+        <v>85</v>
+      </c>
+      <c r="C37" s="279">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
       <c r="D37" s="64" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E37" s="125"/>
       <c r="F37" s="125"/>
@@ -23120,7 +23117,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B39" s="60" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C39" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie2,IF(Antriebsart2="Plug-In-Hybrid (PHEV)","+Strom",""))</f>
@@ -23132,28 +23129,28 @@
     </row>
     <row r="40" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C40" s="279">
+        <v>148</v>
+      </c>
+      <c r="C40" s="278">
         <f>IFERROR(IF(Antriebsart2="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP2/100*Fahrleistung/1000000,IF(Antriebsart2="Verbrenner",VLOOKUP(Energie2,CO2List,3,FALSE)*Verbrauch2/100*Fahrleistung/1000000,VLOOKUP(Energie2,CO2List,3,FALSE)*VerbPHEV2/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV2/100*Fahrleistung/1000000)),0)</f>
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E40" s="125"/>
       <c r="F40" s="125"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C41" s="279">
+        <v>152</v>
+      </c>
+      <c r="C41" s="278">
         <f>C40*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E41" s="125"/>
       <c r="F41" s="125"/>
@@ -23164,7 +23161,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B43" s="154" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -23181,55 +23178,55 @@
     <row r="45" spans="1:6" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="107"/>
       <c r="B45" s="90" t="s">
+        <v>154</v>
+      </c>
+      <c r="C45" s="134" t="s">
         <v>155</v>
-      </c>
-      <c r="C45" s="134" t="s">
-        <v>156</v>
       </c>
       <c r="D45" s="62"/>
       <c r="E45" s="125"/>
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="383" t="s">
-        <v>12</v>
-      </c>
-      <c r="B46" s="437" t="s">
-        <v>149</v>
-      </c>
-      <c r="C46" s="281">
+      <c r="A46" s="369" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" s="436" t="s">
+        <v>148</v>
+      </c>
+      <c r="C46" s="280">
         <f>IF(OR(Antriebsart2="Vollelektrisch (BEV)",Antriebsart2="Plug-In-Hybrid (PHEV)"),Batterie2*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
       <c r="D46" s="131" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E46" s="127"/>
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="383"/>
-      <c r="B47" s="438"/>
-      <c r="C47" s="281" t="e">
+      <c r="A47" s="369"/>
+      <c r="B47" s="437"/>
+      <c r="C47" s="280" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D47" s="130" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E47" s="127"/>
       <c r="F47" s="125"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C48" s="279" t="e">
+        <v>158</v>
+      </c>
+      <c r="C48" s="278" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E48" s="125"/>
       <c r="F48" s="125"/>
@@ -23253,138 +23250,138 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="70" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="68" t="s">
-        <v>161</v>
-      </c>
-      <c r="C54" s="282">
+        <v>160</v>
+      </c>
+      <c r="C54" s="281">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis2,0),Gesamtpreis2*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl2,0))</f>
         <v>0</v>
       </c>
       <c r="D54" s="68" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E54" s="69"/>
       <c r="F54" s="58"/>
     </row>
     <row r="55" spans="1:6" s="71" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A55" s="305" t="s">
-        <v>12</v>
+      <c r="A55" s="304" t="s">
+        <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="C55" s="283">
+        <v>452</v>
+      </c>
+      <c r="C55" s="282">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis2-Gesamtpreis2*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>0</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E55" s="125"/>
       <c r="F55" s="73"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C56" s="283">
+        <v>81</v>
+      </c>
+      <c r="C56" s="282">
         <f>C30*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F56" s="73"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C57" s="283">
+        <v>161</v>
+      </c>
+      <c r="C57" s="282">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F57" s="58"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C58" s="283">
+        <v>152</v>
+      </c>
+      <c r="C58" s="282">
         <f>C41*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B59" s="329" t="s">
-        <v>85</v>
-      </c>
-      <c r="C59" s="330" t="e">
+      <c r="B59" s="328" t="s">
+        <v>84</v>
+      </c>
+      <c r="C59" s="329" t="e">
         <f>C48*Haltedauer</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D59" s="329" t="s">
-        <v>60</v>
+      <c r="D59" s="328" t="s">
+        <v>59</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="383" t="s">
-        <v>12</v>
-      </c>
-      <c r="B60" s="327" t="str">
+      <c r="A60" s="369" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x)</f>
         <v/>
       </c>
-      <c r="C60" s="328" t="str">
+      <c r="C60" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x2*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D60" s="327" t="str">
+      <c r="D60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", "EUR")</f>
         <v/>
       </c>
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="383"/>
-      <c r="B61" s="327" t="str">
+      <c r="A61" s="369"/>
+      <c r="B61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
       </c>
-      <c r="C61" s="328" t="str">
+      <c r="C61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y2*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D61" s="327" t="str">
+      <c r="D61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", "EUR")</f>
         <v/>
       </c>
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="383"/>
-      <c r="B62" s="327" t="str">
+      <c r="A62" s="369"/>
+      <c r="B62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
       </c>
-      <c r="C62" s="328" t="str">
+      <c r="C62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z2*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D62" s="327" t="str">
+      <c r="D62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", "EUR")</f>
         <v/>
       </c>
@@ -23392,14 +23389,14 @@
     </row>
     <row r="63" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="C63" s="284" t="e">
+        <v>85</v>
+      </c>
+      <c r="C63" s="283" t="e">
         <f>SUM(C54:C62)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D63" s="64" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E63" s="14"/>
       <c r="F63" s="58"/>
@@ -23414,26 +23411,26 @@
     </row>
     <row r="65" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B65" s="68" t="s">
-        <v>163</v>
-      </c>
-      <c r="C65" s="285" t="e">
+        <v>162</v>
+      </c>
+      <c r="C65" s="284" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D65" s="68" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="66" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B66" s="72" t="s">
-        <v>91</v>
-      </c>
-      <c r="C66" s="286">
+        <v>90</v>
+      </c>
+      <c r="C66" s="285">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D66" s="72" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E66" s="71"/>
     </row>
@@ -23484,10 +23481,10 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E2" s="106" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2" s="125"/>
     </row>
@@ -23497,7 +23494,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -23513,7 +23510,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" s="54">
         <v>3</v>
@@ -23526,7 +23523,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7" s="102" t="str">
         <f>IF(Anbieter3=0,"",Anbieter3)</f>
@@ -23548,7 +23545,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C9" s="102"/>
       <c r="E9" s="125"/>
@@ -23556,7 +23553,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C10" s="102" t="str">
         <f>IF(Hersteller3=0,"",Hersteller3)</f>
@@ -23568,7 +23565,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C11" s="102" t="str">
         <f>IF(Modell3=0,"",Modell3)</f>
@@ -23580,7 +23577,7 @@
     </row>
     <row r="12" spans="1:6" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="56" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C12" s="102" t="str">
         <f>IF(Zusatzinfo3=0,"",Zusatzinfo3)</f>
@@ -23592,7 +23589,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B13" s="57" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="102" t="str">
         <f>IF(Antriebsart3=0,"",Antriebsart3)</f>
@@ -23603,7 +23600,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="102" t="str">
         <f>IF(Energie3=0,"",Energie3)</f>
@@ -23619,7 +23616,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B16" s="154" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -23635,9 +23632,9 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B18" s="72" t="s">
-        <v>140</v>
-      </c>
-      <c r="C18" s="288">
+        <v>139</v>
+      </c>
+      <c r="C18" s="287">
         <f>0.0057*(ReichwPHEV3/23)^3-0.0838*(ReichwPHEV3/23)^2+0.4261*(ReichwPHEV3/23)+ 0.1633</f>
         <v>0.1633</v>
       </c>
@@ -23647,37 +23644,37 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C19" s="289">
+        <v>140</v>
+      </c>
+      <c r="C19" s="288">
         <f>Verbrauch3/(1-0.9*C18)</f>
         <v>0</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E19" s="125"/>
       <c r="F19" s="125"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>142</v>
-      </c>
-      <c r="C20" s="290">
+        <v>141</v>
+      </c>
+      <c r="C20" s="289">
         <f>VerbEl_WLTP3/C18</f>
         <v>0</v>
       </c>
       <c r="D20" s="184" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E20" s="125"/>
       <c r="F20" s="125"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" s="186" t="s">
-        <v>143</v>
-      </c>
-      <c r="C21" s="291">
+        <v>142</v>
+      </c>
+      <c r="C21" s="290">
         <f>0.0021*(ReichwPHEV3/23)^3-0.0358*(ReichwPHEV3/23)^2+0.2607*(ReichwPHEV3/23)- 0.0267</f>
         <v>-2.6700000000000002E-2</v>
       </c>
@@ -23686,31 +23683,31 @@
       <c r="F21" s="125"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="440" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="439" t="s">
-        <v>144</v>
-      </c>
-      <c r="C22" s="292">
+      <c r="A22" s="439" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="438" t="s">
+        <v>143</v>
+      </c>
+      <c r="C22" s="291">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
       <c r="D22" s="185" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E22" s="125"/>
       <c r="F22" s="125"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="440"/>
-      <c r="B23" s="409"/>
-      <c r="C23" s="292">
+      <c r="A23" s="439"/>
+      <c r="B23" s="408"/>
+      <c r="C23" s="291">
         <f>C20*C21</f>
         <v>0</v>
       </c>
       <c r="D23" s="183" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E23" s="125"/>
       <c r="F23" s="125"/>
@@ -23722,7 +23719,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B25" s="154" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -23735,7 +23732,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C27" s="61"/>
       <c r="D27" s="60"/>
@@ -23744,42 +23741,42 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C28" s="279">
+        <v>145</v>
+      </c>
+      <c r="C28" s="278">
         <f>IF(Antriebsart3="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie3,EnKostList,6,FALSE),0)*IF(Antriebsart3="Plug-In-Hybrid (PHEV)",VerbPHEV3,Verbrauch3)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E28" s="125"/>
       <c r="F28" s="125"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C29" s="279">
+        <v>49</v>
+      </c>
+      <c r="C29" s="278">
         <f>IF(Antriebsart3="Verbrenner",0,VLOOKUP("Strom",EnKostList,6,FALSE)*IF(Antriebsart3="Plug-In-Hybrid (PHEV)",VerbElPHEV3,VerbEl_WLTP3)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E29" s="125"/>
       <c r="F29" s="125"/>
     </row>
     <row r="30" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="C30" s="280">
+        <v>85</v>
+      </c>
+      <c r="C30" s="279">
         <f>SUM(C28:C29)</f>
         <v>0</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E30" s="125"/>
       <c r="F30" s="125"/>
@@ -23792,7 +23789,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C32" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie3)</f>
@@ -23804,70 +23801,70 @@
     </row>
     <row r="33" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B33" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C33" s="279">
+        <v>148</v>
+      </c>
+      <c r="C33" s="278">
         <f>IF(Antriebsart3="Plug-In-Hybrid (PHEV)",VerbPHEV3*VLOOKUP(Energie3,CO2List,2,FALSE)/100,CO2_3)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E33" s="125"/>
       <c r="F33" s="125"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C34" s="279">
+        <v>125</v>
+      </c>
+      <c r="C34" s="278">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E34" s="125"/>
       <c r="F34" s="125"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C35" s="287">
+        <v>150</v>
+      </c>
+      <c r="C35" s="286">
         <f>IF(Energie3="Strom",0,NOX_3*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
       <c r="D35" s="65" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E35" s="125"/>
       <c r="F35" s="125"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B36" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36" s="287">
+        <v>69</v>
+      </c>
+      <c r="C36" s="286">
         <f>IF(Energie3="Strom",0,Partikel3*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
       <c r="D36" s="65" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E36" s="125"/>
       <c r="F36" s="125"/>
     </row>
     <row r="37" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="C37" s="280">
+        <v>85</v>
+      </c>
+      <c r="C37" s="279">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
       <c r="D37" s="64" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E37" s="125"/>
       <c r="F37" s="125"/>
@@ -23880,7 +23877,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B39" s="60" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C39" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie3,IF(Antriebsart3="Plug-In-Hybrid (PHEV)","+Strom",""))</f>
@@ -23892,28 +23889,28 @@
     </row>
     <row r="40" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C40" s="279">
+        <v>148</v>
+      </c>
+      <c r="C40" s="278">
         <f>IFERROR(IF(Antriebsart3="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP3/100*Fahrleistung/1000000,IF(Antriebsart3="Verbrenner",VLOOKUP(Energie3,CO2List,3,FALSE)*Verbrauch3/100*Fahrleistung/1000000,VLOOKUP(Energie3,CO2List,3,FALSE)*VerbPHEV3/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV3/100*Fahrleistung/1000000)),0)</f>
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E40" s="125"/>
       <c r="F40" s="125"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C41" s="279">
+        <v>152</v>
+      </c>
+      <c r="C41" s="278">
         <f>C40*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E41" s="125"/>
       <c r="F41" s="125"/>
@@ -23924,7 +23921,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B43" s="154" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -23941,55 +23938,55 @@
     <row r="45" spans="1:6" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="107"/>
       <c r="B45" s="90" t="s">
+        <v>154</v>
+      </c>
+      <c r="C45" s="134" t="s">
         <v>155</v>
-      </c>
-      <c r="C45" s="134" t="s">
-        <v>156</v>
       </c>
       <c r="D45" s="62"/>
       <c r="E45" s="125"/>
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="383" t="s">
-        <v>12</v>
-      </c>
-      <c r="B46" s="437" t="s">
-        <v>149</v>
-      </c>
-      <c r="C46" s="281">
+      <c r="A46" s="369" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" s="436" t="s">
+        <v>148</v>
+      </c>
+      <c r="C46" s="280">
         <f>IF(OR(Antriebsart3="Vollelektrisch (BEV)",Antriebsart3="Plug-In-Hybrid (PHEV)"),Batterie3*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
       <c r="D46" s="131" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E46" s="127"/>
       <c r="F46" s="133"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="383"/>
-      <c r="B47" s="438"/>
-      <c r="C47" s="281" t="e">
+      <c r="A47" s="369"/>
+      <c r="B47" s="437"/>
+      <c r="C47" s="280" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D47" s="130" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E47" s="127"/>
       <c r="F47" s="133"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C48" s="279" t="e">
+        <v>158</v>
+      </c>
+      <c r="C48" s="278" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E48" s="125"/>
       <c r="F48" s="125"/>
@@ -24013,138 +24010,138 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="70" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="68" t="s">
-        <v>161</v>
-      </c>
-      <c r="C54" s="282">
+        <v>160</v>
+      </c>
+      <c r="C54" s="281">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis3,0),Gesamtpreis3*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl3,0))</f>
         <v>0</v>
       </c>
       <c r="D54" s="68" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E54" s="69"/>
       <c r="F54" s="58"/>
     </row>
     <row r="55" spans="1:6" s="71" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A55" s="305" t="s">
-        <v>12</v>
+      <c r="A55" s="304" t="s">
+        <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="C55" s="283">
+        <v>452</v>
+      </c>
+      <c r="C55" s="282">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis3-Gesamtpreis3*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>0</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E55" s="125"/>
       <c r="F55" s="73"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C56" s="283">
+        <v>81</v>
+      </c>
+      <c r="C56" s="282">
         <f>C30*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F56" s="73"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C57" s="283">
+        <v>161</v>
+      </c>
+      <c r="C57" s="282">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F57" s="58"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C58" s="283">
+        <v>152</v>
+      </c>
+      <c r="C58" s="282">
         <f>C41*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B59" s="327" t="s">
-        <v>85</v>
-      </c>
-      <c r="C59" s="328" t="e">
+      <c r="B59" s="326" t="s">
+        <v>84</v>
+      </c>
+      <c r="C59" s="327" t="e">
         <f>C48*Haltedauer</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D59" s="327" t="s">
-        <v>60</v>
+      <c r="D59" s="326" t="s">
+        <v>59</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="383" t="s">
-        <v>12</v>
-      </c>
-      <c r="B60" s="327" t="str">
+      <c r="A60" s="369" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x)</f>
         <v/>
       </c>
-      <c r="C60" s="328" t="str">
+      <c r="C60" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x3*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D60" s="327" t="str">
+      <c r="D60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", "EUR")</f>
         <v/>
       </c>
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="383"/>
-      <c r="B61" s="327" t="str">
+      <c r="A61" s="369"/>
+      <c r="B61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
       </c>
-      <c r="C61" s="328" t="str">
+      <c r="C61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y3*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D61" s="327" t="str">
+      <c r="D61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", "EUR")</f>
         <v/>
       </c>
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="383"/>
-      <c r="B62" s="327" t="str">
+      <c r="A62" s="369"/>
+      <c r="B62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
       </c>
-      <c r="C62" s="328" t="str">
+      <c r="C62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z3*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D62" s="327" t="str">
+      <c r="D62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", "EUR")</f>
         <v/>
       </c>
@@ -24152,14 +24149,14 @@
     </row>
     <row r="63" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="C63" s="284" t="e">
+        <v>85</v>
+      </c>
+      <c r="C63" s="283" t="e">
         <f>SUM(C54:C62)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D63" s="64" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E63" s="14"/>
       <c r="F63" s="58"/>
@@ -24174,26 +24171,26 @@
     </row>
     <row r="65" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B65" s="68" t="s">
-        <v>163</v>
-      </c>
-      <c r="C65" s="285" t="e">
+        <v>162</v>
+      </c>
+      <c r="C65" s="284" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D65" s="68" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="66" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B66" s="72" t="s">
-        <v>91</v>
-      </c>
-      <c r="C66" s="286">
+        <v>90</v>
+      </c>
+      <c r="C66" s="285">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D66" s="72" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E66" s="71"/>
     </row>
@@ -24222,6 +24219,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" xsi:nil="true"/>
@@ -24230,15 +24236,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -24471,6 +24468,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92A2CDCF-36F6-4C30-8F9B-D45880CB8E7E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{651615EB-DE44-4BF4-BD1E-846AB7A3DA36}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -24483,14 +24488,6 @@
     <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92A2CDCF-36F6-4C30-8F9B-D45880CB8E7E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
